--- a/artfynd/A 41611-2025 artfynd.xlsx
+++ b/artfynd/A 41611-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128493883</v>
+        <v>128493877</v>
       </c>
       <c r="B2" t="n">
-        <v>80223</v>
+        <v>96823</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6463</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>631861</v>
+        <v>631706</v>
       </c>
       <c r="R2" t="n">
-        <v>6661676</v>
+        <v>6661848</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128493877</v>
+        <v>128493883</v>
       </c>
       <c r="B3" t="n">
-        <v>96823</v>
+        <v>80223</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>6463</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>631706</v>
+        <v>631861</v>
       </c>
       <c r="R3" t="n">
-        <v>6661848</v>
+        <v>6661676</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -1471,32 +1471,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128493875</v>
+        <v>128493915</v>
       </c>
       <c r="B10" t="n">
-        <v>96823</v>
+        <v>96066</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>53</v>
+        <v>2170</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>631869</v>
+        <v>631915</v>
       </c>
       <c r="R10" t="n">
-        <v>6661711</v>
+        <v>6661808</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1568,45 +1568,49 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128493915</v>
+        <v>128493893</v>
       </c>
       <c r="B11" t="n">
-        <v>96066</v>
+        <v>98571</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2170</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>631915</v>
+        <v>632068</v>
       </c>
       <c r="R11" t="n">
-        <v>6661808</v>
+        <v>6661949</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1641,12 +1645,18 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ca 20 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1665,49 +1675,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128493893</v>
+        <v>128493875</v>
       </c>
       <c r="B12" t="n">
-        <v>98571</v>
+        <v>96823</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>632068</v>
+        <v>631869</v>
       </c>
       <c r="R12" t="n">
-        <v>6661949</v>
+        <v>6661711</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1742,18 +1748,12 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ca 20 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2170,49 +2170,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128493894</v>
+        <v>128493914</v>
       </c>
       <c r="B17" t="n">
-        <v>98571</v>
+        <v>96066</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>2170</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>631994</v>
+        <v>632016</v>
       </c>
       <c r="R17" t="n">
-        <v>6661866</v>
+        <v>6661935</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2247,18 +2243,12 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>mer än 40 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2374,45 +2364,49 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128493914</v>
+        <v>128493894</v>
       </c>
       <c r="B19" t="n">
-        <v>96066</v>
+        <v>98571</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2170</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>632016</v>
+        <v>631994</v>
       </c>
       <c r="R19" t="n">
-        <v>6661935</v>
+        <v>6661866</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2447,12 +2441,18 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>mer än 40 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -3160,32 +3160,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128493906</v>
+        <v>128493872</v>
       </c>
       <c r="B27" t="n">
-        <v>105609</v>
+        <v>96823</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221144</v>
+        <v>53</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3195,10 +3195,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>631754</v>
+        <v>632001</v>
       </c>
       <c r="R27" t="n">
-        <v>6661814</v>
+        <v>6661954</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3257,7 +3257,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128493872</v>
+        <v>128493876</v>
       </c>
       <c r="B28" t="n">
         <v>96823</v>
@@ -3292,10 +3292,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>632001</v>
+        <v>631854</v>
       </c>
       <c r="R28" t="n">
-        <v>6661954</v>
+        <v>6661710</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3354,32 +3354,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128493876</v>
+        <v>128493906</v>
       </c>
       <c r="B29" t="n">
-        <v>96823</v>
+        <v>105609</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>53</v>
+        <v>221144</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3389,10 +3389,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>631854</v>
+        <v>631754</v>
       </c>
       <c r="R29" t="n">
-        <v>6661710</v>
+        <v>6661814</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3451,48 +3451,52 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128493881</v>
+        <v>128493890</v>
       </c>
       <c r="B30" t="n">
-        <v>57845</v>
+        <v>98571</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>631713</v>
+        <v>631513</v>
       </c>
       <c r="R30" t="n">
-        <v>6661820</v>
+        <v>6661886</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3524,12 +3528,18 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ca 40 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3548,52 +3558,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128493890</v>
+        <v>128493881</v>
       </c>
       <c r="B31" t="n">
-        <v>98571</v>
+        <v>57845</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>631513</v>
+        <v>631713</v>
       </c>
       <c r="R31" t="n">
-        <v>6661886</v>
+        <v>6661820</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3625,18 +3631,12 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ca 40 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3655,10 +3655,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128493918</v>
+        <v>128493874</v>
       </c>
       <c r="B32" t="n">
-        <v>92760</v>
+        <v>96823</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3666,21 +3666,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4368</v>
+        <v>53</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3690,10 +3690,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>631638</v>
+        <v>631878</v>
       </c>
       <c r="R32" t="n">
-        <v>6661884</v>
+        <v>6661711</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3752,10 +3752,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128493874</v>
+        <v>128493918</v>
       </c>
       <c r="B33" t="n">
-        <v>96823</v>
+        <v>92760</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3763,21 +3763,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>53</v>
+        <v>4368</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3787,10 +3787,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>631878</v>
+        <v>631638</v>
       </c>
       <c r="R33" t="n">
-        <v>6661711</v>
+        <v>6661884</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3946,32 +3946,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128493897</v>
+        <v>128493907</v>
       </c>
       <c r="B35" t="n">
-        <v>98571</v>
+        <v>105609</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3981,10 +3981,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>631658</v>
+        <v>631741</v>
       </c>
       <c r="R35" t="n">
-        <v>6661890</v>
+        <v>6661845</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ett fåtal bladrosetter</t>
+          <t>Mer än 20 bladrosetter</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4048,32 +4048,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128493907</v>
+        <v>128493897</v>
       </c>
       <c r="B36" t="n">
-        <v>105609</v>
+        <v>98571</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4083,10 +4083,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>631741</v>
+        <v>631658</v>
       </c>
       <c r="R36" t="n">
-        <v>6661845</v>
+        <v>6661890</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4123,7 +4123,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Mer än 20 bladrosetter</t>
+          <t>Ett fåtal bladrosetter</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4460,49 +4460,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128493895</v>
+        <v>128493878</v>
       </c>
       <c r="B40" t="n">
-        <v>98571</v>
+        <v>96823</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>631908</v>
+        <v>631686</v>
       </c>
       <c r="R40" t="n">
-        <v>6661782</v>
+        <v>6661895</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4537,18 +4533,12 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Mer än 50  bladrosetter</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4567,45 +4557,49 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128493878</v>
+        <v>128493895</v>
       </c>
       <c r="B41" t="n">
-        <v>96823</v>
+        <v>98571</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>631686</v>
+        <v>631908</v>
       </c>
       <c r="R41" t="n">
-        <v>6661895</v>
+        <v>6661782</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4640,12 +4634,18 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Mer än 50  bladrosetter</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 41611-2025 artfynd.xlsx
+++ b/artfynd/A 41611-2025 artfynd.xlsx
@@ -1568,49 +1568,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128493893</v>
+        <v>128493875</v>
       </c>
       <c r="B11" t="n">
-        <v>98571</v>
+        <v>96823</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>632068</v>
+        <v>631869</v>
       </c>
       <c r="R11" t="n">
-        <v>6661949</v>
+        <v>6661711</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1645,18 +1641,12 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ca 20 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1675,45 +1665,49 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128493875</v>
+        <v>128493893</v>
       </c>
       <c r="B12" t="n">
-        <v>96823</v>
+        <v>98571</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>631869</v>
+        <v>632068</v>
       </c>
       <c r="R12" t="n">
-        <v>6661711</v>
+        <v>6661949</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1748,12 +1742,18 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ca 20 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2063,7 +2063,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128493902</v>
+        <v>128493894</v>
       </c>
       <c r="B16" t="n">
         <v>98571</v>
@@ -2102,10 +2102,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>632008</v>
+        <v>631994</v>
       </c>
       <c r="R16" t="n">
-        <v>6661933</v>
+        <v>6661866</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2364,7 +2364,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128493894</v>
+        <v>128493902</v>
       </c>
       <c r="B19" t="n">
         <v>98571</v>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>631994</v>
+        <v>632008</v>
       </c>
       <c r="R19" t="n">
-        <v>6661866</v>
+        <v>6661933</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2471,45 +2471,49 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128493916</v>
+        <v>128493892</v>
       </c>
       <c r="B20" t="n">
-        <v>92742</v>
+        <v>98571</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>631758</v>
+        <v>632048</v>
       </c>
       <c r="R20" t="n">
-        <v>6661855</v>
+        <v>6661860</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2544,12 +2548,18 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ca 20 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2568,49 +2578,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128493892</v>
+        <v>128493916</v>
       </c>
       <c r="B21" t="n">
-        <v>98571</v>
+        <v>92742</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>632048</v>
+        <v>631758</v>
       </c>
       <c r="R21" t="n">
-        <v>6661860</v>
+        <v>6661855</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2645,18 +2651,12 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ca 20 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3451,52 +3451,48 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128493890</v>
+        <v>128493881</v>
       </c>
       <c r="B30" t="n">
-        <v>98571</v>
+        <v>57845</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>631513</v>
+        <v>631713</v>
       </c>
       <c r="R30" t="n">
-        <v>6661886</v>
+        <v>6661820</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3528,18 +3524,12 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ca 40 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3558,48 +3548,52 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128493881</v>
+        <v>128493890</v>
       </c>
       <c r="B31" t="n">
-        <v>57845</v>
+        <v>98571</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>631713</v>
+        <v>631513</v>
       </c>
       <c r="R31" t="n">
-        <v>6661820</v>
+        <v>6661886</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3631,12 +3625,18 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ca 40 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3946,32 +3946,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128493907</v>
+        <v>128493897</v>
       </c>
       <c r="B35" t="n">
-        <v>105609</v>
+        <v>98571</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3981,10 +3981,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>631741</v>
+        <v>631658</v>
       </c>
       <c r="R35" t="n">
-        <v>6661845</v>
+        <v>6661890</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Mer än 20 bladrosetter</t>
+          <t>Ett fåtal bladrosetter</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4048,32 +4048,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128493897</v>
+        <v>128493907</v>
       </c>
       <c r="B36" t="n">
-        <v>98571</v>
+        <v>105609</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4083,10 +4083,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>631658</v>
+        <v>631741</v>
       </c>
       <c r="R36" t="n">
-        <v>6661890</v>
+        <v>6661845</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4123,7 +4123,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ett fåtal bladrosetter</t>
+          <t>Mer än 20 bladrosetter</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 41611-2025 artfynd.xlsx
+++ b/artfynd/A 41611-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128493877</v>
+        <v>128493904</v>
       </c>
       <c r="B2" t="n">
-        <v>96823</v>
+        <v>98579</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>631706</v>
+        <v>631707</v>
       </c>
       <c r="R2" t="n">
-        <v>6661848</v>
+        <v>6661837</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>12 bladrosetter</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,32 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128493883</v>
+        <v>128493901</v>
       </c>
       <c r="B3" t="n">
-        <v>80223</v>
+        <v>98579</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>631861</v>
+        <v>632054</v>
       </c>
       <c r="R3" t="n">
-        <v>6661676</v>
+        <v>6661938</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -843,6 +848,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Mer än 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,32 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128493904</v>
+        <v>128493877</v>
       </c>
       <c r="B4" t="n">
-        <v>98571</v>
+        <v>96829</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>631707</v>
+        <v>631706</v>
       </c>
       <c r="R4" t="n">
-        <v>6661837</v>
+        <v>6661848</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -940,11 +950,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>12 bladrosetter</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,32 +976,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128493901</v>
+        <v>128493883</v>
       </c>
       <c r="B5" t="n">
-        <v>98571</v>
+        <v>80227</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>632054</v>
+        <v>631861</v>
       </c>
       <c r="R5" t="n">
-        <v>6661938</v>
+        <v>6661676</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1042,11 +1047,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Mer än 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1076,7 +1076,7 @@
         <v>128493909</v>
       </c>
       <c r="B6" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>128493898</v>
       </c>
       <c r="B7" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>128493899</v>
       </c>
       <c r="B8" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>128493900</v>
       </c>
       <c r="B9" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>128493915</v>
       </c>
       <c r="B10" t="n">
-        <v>96066</v>
+        <v>96072</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>128493875</v>
       </c>
       <c r="B11" t="n">
-        <v>96823</v>
+        <v>96829</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>128493893</v>
       </c>
       <c r="B12" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>128493920</v>
       </c>
       <c r="B13" t="n">
-        <v>100753</v>
+        <v>100761</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>128493913</v>
       </c>
       <c r="B14" t="n">
-        <v>96066</v>
+        <v>96072</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>128493919</v>
       </c>
       <c r="B15" t="n">
-        <v>92760</v>
+        <v>92766</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2063,49 +2063,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128493894</v>
+        <v>128493914</v>
       </c>
       <c r="B16" t="n">
-        <v>98571</v>
+        <v>96072</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>2170</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>631994</v>
+        <v>632016</v>
       </c>
       <c r="R16" t="n">
-        <v>6661866</v>
+        <v>6661935</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2140,18 +2136,12 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>mer än 40 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2170,32 +2160,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128493914</v>
+        <v>128493882</v>
       </c>
       <c r="B17" t="n">
-        <v>96066</v>
+        <v>91478</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2170</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2205,10 +2195,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>632016</v>
+        <v>631713</v>
       </c>
       <c r="R17" t="n">
-        <v>6661935</v>
+        <v>6661819</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2267,45 +2257,49 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128493882</v>
+        <v>128493902</v>
       </c>
       <c r="B18" t="n">
-        <v>91472</v>
+        <v>98579</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>631713</v>
+        <v>632008</v>
       </c>
       <c r="R18" t="n">
-        <v>6661819</v>
+        <v>6661933</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2340,12 +2334,18 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>mer än 40 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2364,10 +2364,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128493902</v>
+        <v>128493894</v>
       </c>
       <c r="B19" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>632008</v>
+        <v>631994</v>
       </c>
       <c r="R19" t="n">
-        <v>6661933</v>
+        <v>6661866</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2471,49 +2471,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128493892</v>
+        <v>128493916</v>
       </c>
       <c r="B20" t="n">
-        <v>98571</v>
+        <v>92748</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>632048</v>
+        <v>631758</v>
       </c>
       <c r="R20" t="n">
-        <v>6661860</v>
+        <v>6661855</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2548,18 +2544,12 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ca 20 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2578,45 +2568,49 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128493916</v>
+        <v>128493892</v>
       </c>
       <c r="B21" t="n">
-        <v>92742</v>
+        <v>98579</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>631758</v>
+        <v>632048</v>
       </c>
       <c r="R21" t="n">
-        <v>6661855</v>
+        <v>6661860</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2651,12 +2645,18 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ca 20 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2678,7 +2678,7 @@
         <v>128493879</v>
       </c>
       <c r="B22" t="n">
-        <v>91452</v>
+        <v>91458</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2775,7 +2775,7 @@
         <v>128493884</v>
       </c>
       <c r="B23" t="n">
-        <v>80148</v>
+        <v>80152</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2869,32 +2869,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128493885</v>
+        <v>128493871</v>
       </c>
       <c r="B24" t="n">
-        <v>57682</v>
+        <v>101665</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>221235</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2904,10 +2904,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>631983</v>
+        <v>631816</v>
       </c>
       <c r="R24" t="n">
-        <v>6661724</v>
+        <v>6661751</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2966,32 +2966,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128493871</v>
+        <v>128493885</v>
       </c>
       <c r="B25" t="n">
-        <v>101657</v>
+        <v>57686</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221235</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3001,10 +3001,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>631816</v>
+        <v>631983</v>
       </c>
       <c r="R25" t="n">
-        <v>6661751</v>
+        <v>6661724</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3066,7 +3066,7 @@
         <v>128493905</v>
       </c>
       <c r="B26" t="n">
-        <v>92217</v>
+        <v>92223</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>128493872</v>
       </c>
       <c r="B27" t="n">
-        <v>96823</v>
+        <v>96829</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
         <v>128493876</v>
       </c>
       <c r="B28" t="n">
-        <v>96823</v>
+        <v>96829</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
         <v>128493906</v>
       </c>
       <c r="B29" t="n">
-        <v>105609</v>
+        <v>105621</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
         <v>128493881</v>
       </c>
       <c r="B30" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3551,7 +3551,7 @@
         <v>128493890</v>
       </c>
       <c r="B31" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>128493874</v>
       </c>
       <c r="B32" t="n">
-        <v>96823</v>
+        <v>96829</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
         <v>128493918</v>
       </c>
       <c r="B33" t="n">
-        <v>92760</v>
+        <v>92766</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>128493873</v>
       </c>
       <c r="B34" t="n">
-        <v>96823</v>
+        <v>96829</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3946,32 +3946,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128493897</v>
+        <v>128493907</v>
       </c>
       <c r="B35" t="n">
-        <v>98571</v>
+        <v>105621</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3981,10 +3981,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>631658</v>
+        <v>631741</v>
       </c>
       <c r="R35" t="n">
-        <v>6661890</v>
+        <v>6661845</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ett fåtal bladrosetter</t>
+          <t>Mer än 20 bladrosetter</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4048,32 +4048,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128493907</v>
+        <v>128493897</v>
       </c>
       <c r="B36" t="n">
-        <v>105609</v>
+        <v>98579</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4083,10 +4083,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>631741</v>
+        <v>631658</v>
       </c>
       <c r="R36" t="n">
-        <v>6661845</v>
+        <v>6661890</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4123,7 +4123,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Mer än 20 bladrosetter</t>
+          <t>Ett fåtal bladrosetter</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4153,7 +4153,7 @@
         <v>128493896</v>
       </c>
       <c r="B37" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         <v>128493903</v>
       </c>
       <c r="B38" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4359,10 +4359,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128493917</v>
+        <v>128493878</v>
       </c>
       <c r="B39" t="n">
-        <v>92760</v>
+        <v>96829</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4370,37 +4370,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4368</v>
+        <v>53</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>631806</v>
+        <v>631686</v>
       </c>
       <c r="R39" t="n">
-        <v>6661784</v>
+        <v>6661895</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4441,7 +4438,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4460,10 +4456,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128493878</v>
+        <v>128493917</v>
       </c>
       <c r="B40" t="n">
-        <v>96823</v>
+        <v>92766</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4471,34 +4467,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>53</v>
+        <v>4368</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>631686</v>
+        <v>631806</v>
       </c>
       <c r="R40" t="n">
-        <v>6661895</v>
+        <v>6661784</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4539,6 +4538,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4560,7 +4560,7 @@
         <v>128493895</v>
       </c>
       <c r="B41" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 41611-2025 artfynd.xlsx
+++ b/artfynd/A 41611-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128493904</v>
+        <v>128493877</v>
       </c>
       <c r="B2" t="n">
-        <v>98579</v>
+        <v>96835</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>631707</v>
+        <v>631706</v>
       </c>
       <c r="R2" t="n">
-        <v>6661837</v>
+        <v>6661848</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>12 bladrosetter</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128493901</v>
+        <v>128493883</v>
       </c>
       <c r="B3" t="n">
-        <v>98579</v>
+        <v>80227</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>632054</v>
+        <v>631861</v>
       </c>
       <c r="R3" t="n">
-        <v>6661938</v>
+        <v>6661676</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -848,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Mer än 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128493877</v>
+        <v>128493904</v>
       </c>
       <c r="B4" t="n">
-        <v>96829</v>
+        <v>98585</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>631706</v>
+        <v>631707</v>
       </c>
       <c r="R4" t="n">
-        <v>6661848</v>
+        <v>6661837</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -950,6 +940,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>12 bladrosetter</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,32 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128493883</v>
+        <v>128493901</v>
       </c>
       <c r="B5" t="n">
-        <v>80227</v>
+        <v>98585</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>631861</v>
+        <v>632054</v>
       </c>
       <c r="R5" t="n">
-        <v>6661676</v>
+        <v>6661938</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1047,6 +1042,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Mer än 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1173,7 +1173,7 @@
         <v>128493898</v>
       </c>
       <c r="B7" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>128493899</v>
       </c>
       <c r="B8" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>128493900</v>
       </c>
       <c r="B9" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1471,32 +1471,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128493915</v>
+        <v>128493875</v>
       </c>
       <c r="B10" t="n">
-        <v>96072</v>
+        <v>96835</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2170</v>
+        <v>53</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>631915</v>
+        <v>631869</v>
       </c>
       <c r="R10" t="n">
-        <v>6661808</v>
+        <v>6661711</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1568,32 +1568,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128493875</v>
+        <v>128493915</v>
       </c>
       <c r="B11" t="n">
-        <v>96829</v>
+        <v>96078</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>53</v>
+        <v>2170</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1603,10 +1603,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>631869</v>
+        <v>631915</v>
       </c>
       <c r="R11" t="n">
-        <v>6661711</v>
+        <v>6661808</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1668,7 +1668,7 @@
         <v>128493893</v>
       </c>
       <c r="B12" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>128493920</v>
       </c>
       <c r="B13" t="n">
-        <v>100761</v>
+        <v>100768</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1869,32 +1869,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128493913</v>
+        <v>128493919</v>
       </c>
       <c r="B14" t="n">
-        <v>96072</v>
+        <v>92772</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2170</v>
+        <v>4368</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1904,10 +1904,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>631960</v>
+        <v>631760</v>
       </c>
       <c r="R14" t="n">
-        <v>6661631</v>
+        <v>6661857</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1966,32 +1966,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128493919</v>
+        <v>128493913</v>
       </c>
       <c r="B15" t="n">
-        <v>92766</v>
+        <v>96078</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4368</v>
+        <v>2170</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2001,10 +2001,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>631760</v>
+        <v>631960</v>
       </c>
       <c r="R15" t="n">
-        <v>6661857</v>
+        <v>6661631</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2066,7 +2066,7 @@
         <v>128493914</v>
       </c>
       <c r="B16" t="n">
-        <v>96072</v>
+        <v>96078</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2163,7 +2163,7 @@
         <v>128493882</v>
       </c>
       <c r="B17" t="n">
-        <v>91478</v>
+        <v>91484</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         <v>128493902</v>
       </c>
       <c r="B18" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>128493894</v>
       </c>
       <c r="B19" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2471,45 +2471,49 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128493916</v>
+        <v>128493892</v>
       </c>
       <c r="B20" t="n">
-        <v>92748</v>
+        <v>98585</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>631758</v>
+        <v>632048</v>
       </c>
       <c r="R20" t="n">
-        <v>6661855</v>
+        <v>6661860</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2544,12 +2548,18 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ca 20 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2568,49 +2578,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128493892</v>
+        <v>128493916</v>
       </c>
       <c r="B21" t="n">
-        <v>98579</v>
+        <v>92754</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>632048</v>
+        <v>631758</v>
       </c>
       <c r="R21" t="n">
-        <v>6661860</v>
+        <v>6661855</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2645,18 +2651,12 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ca 20 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2675,32 +2675,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128493879</v>
+        <v>128493884</v>
       </c>
       <c r="B22" t="n">
-        <v>91458</v>
+        <v>80152</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2710,10 +2710,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>631703</v>
+        <v>631861</v>
       </c>
       <c r="R22" t="n">
-        <v>6661853</v>
+        <v>6661676</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2772,32 +2772,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128493884</v>
+        <v>128493879</v>
       </c>
       <c r="B23" t="n">
-        <v>80152</v>
+        <v>91464</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2807,10 +2807,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>631861</v>
+        <v>631703</v>
       </c>
       <c r="R23" t="n">
-        <v>6661676</v>
+        <v>6661853</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2869,32 +2869,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128493871</v>
+        <v>128493885</v>
       </c>
       <c r="B24" t="n">
-        <v>101665</v>
+        <v>57686</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221235</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2904,10 +2904,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>631816</v>
+        <v>631983</v>
       </c>
       <c r="R24" t="n">
-        <v>6661751</v>
+        <v>6661724</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2966,32 +2966,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128493885</v>
+        <v>128493871</v>
       </c>
       <c r="B25" t="n">
-        <v>57686</v>
+        <v>101673</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>221235</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3001,10 +3001,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>631983</v>
+        <v>631816</v>
       </c>
       <c r="R25" t="n">
-        <v>6661724</v>
+        <v>6661751</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3066,7 +3066,7 @@
         <v>128493905</v>
       </c>
       <c r="B26" t="n">
-        <v>92223</v>
+        <v>92229</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>128493872</v>
       </c>
       <c r="B27" t="n">
-        <v>96829</v>
+        <v>96835</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
         <v>128493876</v>
       </c>
       <c r="B28" t="n">
-        <v>96829</v>
+        <v>96835</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
         <v>128493906</v>
       </c>
       <c r="B29" t="n">
-        <v>105621</v>
+        <v>105630</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3451,48 +3451,52 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128493881</v>
+        <v>128493890</v>
       </c>
       <c r="B30" t="n">
-        <v>57849</v>
+        <v>98585</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>631713</v>
+        <v>631513</v>
       </c>
       <c r="R30" t="n">
-        <v>6661820</v>
+        <v>6661886</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3524,12 +3528,18 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ca 40 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3548,52 +3558,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128493890</v>
+        <v>128493881</v>
       </c>
       <c r="B31" t="n">
-        <v>98579</v>
+        <v>57849</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>631513</v>
+        <v>631713</v>
       </c>
       <c r="R31" t="n">
-        <v>6661886</v>
+        <v>6661820</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3625,18 +3631,12 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ca 40 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3658,7 +3658,7 @@
         <v>128493874</v>
       </c>
       <c r="B32" t="n">
-        <v>96829</v>
+        <v>96835</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
         <v>128493918</v>
       </c>
       <c r="B33" t="n">
-        <v>92766</v>
+        <v>92772</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>128493873</v>
       </c>
       <c r="B34" t="n">
-        <v>96829</v>
+        <v>96835</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3946,32 +3946,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128493907</v>
+        <v>128493897</v>
       </c>
       <c r="B35" t="n">
-        <v>105621</v>
+        <v>98585</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3981,10 +3981,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>631741</v>
+        <v>631658</v>
       </c>
       <c r="R35" t="n">
-        <v>6661845</v>
+        <v>6661890</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Mer än 20 bladrosetter</t>
+          <t>Ett fåtal bladrosetter</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4048,32 +4048,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128493897</v>
+        <v>128493907</v>
       </c>
       <c r="B36" t="n">
-        <v>98579</v>
+        <v>105630</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4083,10 +4083,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>631658</v>
+        <v>631741</v>
       </c>
       <c r="R36" t="n">
-        <v>6661890</v>
+        <v>6661845</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4123,7 +4123,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ett fåtal bladrosetter</t>
+          <t>Mer än 20 bladrosetter</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4153,7 +4153,7 @@
         <v>128493896</v>
       </c>
       <c r="B37" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         <v>128493903</v>
       </c>
       <c r="B38" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4359,10 +4359,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128493878</v>
+        <v>128493917</v>
       </c>
       <c r="B39" t="n">
-        <v>96829</v>
+        <v>92772</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4370,34 +4370,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>53</v>
+        <v>4368</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>631686</v>
+        <v>631806</v>
       </c>
       <c r="R39" t="n">
-        <v>6661895</v>
+        <v>6661784</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4438,6 +4441,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4456,10 +4460,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128493917</v>
+        <v>128493878</v>
       </c>
       <c r="B40" t="n">
-        <v>92766</v>
+        <v>96835</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4467,37 +4471,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4368</v>
+        <v>53</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>631806</v>
+        <v>631686</v>
       </c>
       <c r="R40" t="n">
-        <v>6661784</v>
+        <v>6661895</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4538,7 +4539,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4560,7 +4560,7 @@
         <v>128493895</v>
       </c>
       <c r="B41" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 41611-2025 artfynd.xlsx
+++ b/artfynd/A 41611-2025 artfynd.xlsx
@@ -2675,32 +2675,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128493884</v>
+        <v>128493879</v>
       </c>
       <c r="B22" t="n">
-        <v>80152</v>
+        <v>91464</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2710,10 +2710,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>631861</v>
+        <v>631703</v>
       </c>
       <c r="R22" t="n">
-        <v>6661676</v>
+        <v>6661853</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2772,32 +2772,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128493879</v>
+        <v>128493884</v>
       </c>
       <c r="B23" t="n">
-        <v>91464</v>
+        <v>80152</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2807,10 +2807,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>631703</v>
+        <v>631861</v>
       </c>
       <c r="R23" t="n">
-        <v>6661853</v>
+        <v>6661676</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>

--- a/artfynd/A 41611-2025 artfynd.xlsx
+++ b/artfynd/A 41611-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128493877</v>
       </c>
       <c r="B2" t="n">
-        <v>96835</v>
+        <v>96837</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128493883</v>
       </c>
       <c r="B3" t="n">
-        <v>80227</v>
+        <v>80229</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128493904</v>
       </c>
       <c r="B4" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>128493901</v>
       </c>
       <c r="B5" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>128493909</v>
       </c>
       <c r="B6" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>128493898</v>
       </c>
       <c r="B7" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>128493899</v>
       </c>
       <c r="B8" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>128493900</v>
       </c>
       <c r="B9" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>128493875</v>
       </c>
       <c r="B10" t="n">
-        <v>96835</v>
+        <v>96837</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>128493915</v>
       </c>
       <c r="B11" t="n">
-        <v>96078</v>
+        <v>96080</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>128493893</v>
       </c>
       <c r="B12" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>128493920</v>
       </c>
       <c r="B13" t="n">
-        <v>100768</v>
+        <v>100773</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1869,32 +1869,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128493919</v>
+        <v>128493913</v>
       </c>
       <c r="B14" t="n">
-        <v>92772</v>
+        <v>96080</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4368</v>
+        <v>2170</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1904,10 +1904,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>631760</v>
+        <v>631960</v>
       </c>
       <c r="R14" t="n">
-        <v>6661857</v>
+        <v>6661631</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1966,32 +1966,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128493913</v>
+        <v>128493919</v>
       </c>
       <c r="B15" t="n">
-        <v>96078</v>
+        <v>92774</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2170</v>
+        <v>4368</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2001,10 +2001,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>631960</v>
+        <v>631760</v>
       </c>
       <c r="R15" t="n">
-        <v>6661631</v>
+        <v>6661857</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2063,32 +2063,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128493914</v>
+        <v>128493882</v>
       </c>
       <c r="B16" t="n">
-        <v>96078</v>
+        <v>91486</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2170</v>
+        <v>5442</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2098,10 +2098,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>632016</v>
+        <v>631713</v>
       </c>
       <c r="R16" t="n">
-        <v>6661935</v>
+        <v>6661819</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2160,45 +2160,49 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128493882</v>
+        <v>128493902</v>
       </c>
       <c r="B17" t="n">
-        <v>91484</v>
+        <v>98588</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>631713</v>
+        <v>632008</v>
       </c>
       <c r="R17" t="n">
-        <v>6661819</v>
+        <v>6661933</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2233,12 +2237,18 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>mer än 40 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2257,10 +2267,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128493902</v>
+        <v>128493894</v>
       </c>
       <c r="B18" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2296,10 +2306,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>632008</v>
+        <v>631994</v>
       </c>
       <c r="R18" t="n">
-        <v>6661933</v>
+        <v>6661866</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2364,49 +2374,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128493894</v>
+        <v>128493914</v>
       </c>
       <c r="B19" t="n">
-        <v>98585</v>
+        <v>96080</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>2170</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>631994</v>
+        <v>632016</v>
       </c>
       <c r="R19" t="n">
-        <v>6661866</v>
+        <v>6661935</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2441,18 +2447,12 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>mer än 40 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2471,49 +2471,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128493892</v>
+        <v>128493916</v>
       </c>
       <c r="B20" t="n">
-        <v>98585</v>
+        <v>92756</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>632048</v>
+        <v>631758</v>
       </c>
       <c r="R20" t="n">
-        <v>6661860</v>
+        <v>6661855</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2548,18 +2544,12 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ca 20 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2578,45 +2568,49 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128493916</v>
+        <v>128493892</v>
       </c>
       <c r="B21" t="n">
-        <v>92754</v>
+        <v>98588</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>631758</v>
+        <v>632048</v>
       </c>
       <c r="R21" t="n">
-        <v>6661855</v>
+        <v>6661860</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2651,12 +2645,18 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ca 20 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2678,7 +2678,7 @@
         <v>128493879</v>
       </c>
       <c r="B22" t="n">
-        <v>91464</v>
+        <v>91466</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2775,7 +2775,7 @@
         <v>128493884</v>
       </c>
       <c r="B23" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>128493871</v>
       </c>
       <c r="B25" t="n">
-        <v>101673</v>
+        <v>101678</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
         <v>128493905</v>
       </c>
       <c r="B26" t="n">
-        <v>92229</v>
+        <v>92231</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>128493872</v>
       </c>
       <c r="B27" t="n">
-        <v>96835</v>
+        <v>96837</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
         <v>128493876</v>
       </c>
       <c r="B28" t="n">
-        <v>96835</v>
+        <v>96837</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
         <v>128493906</v>
       </c>
       <c r="B29" t="n">
-        <v>105630</v>
+        <v>105642</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
         <v>128493890</v>
       </c>
       <c r="B30" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>128493874</v>
       </c>
       <c r="B32" t="n">
-        <v>96835</v>
+        <v>96837</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
         <v>128493918</v>
       </c>
       <c r="B33" t="n">
-        <v>92772</v>
+        <v>92774</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>128493873</v>
       </c>
       <c r="B34" t="n">
-        <v>96835</v>
+        <v>96837</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         <v>128493897</v>
       </c>
       <c r="B35" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4051,7 +4051,7 @@
         <v>128493907</v>
       </c>
       <c r="B36" t="n">
-        <v>105630</v>
+        <v>105642</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>128493896</v>
       </c>
       <c r="B37" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         <v>128493903</v>
       </c>
       <c r="B38" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4359,10 +4359,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128493917</v>
+        <v>128493878</v>
       </c>
       <c r="B39" t="n">
-        <v>92772</v>
+        <v>96837</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4370,37 +4370,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4368</v>
+        <v>53</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>631806</v>
+        <v>631686</v>
       </c>
       <c r="R39" t="n">
-        <v>6661784</v>
+        <v>6661895</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4441,7 +4438,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4460,10 +4456,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128493878</v>
+        <v>128493917</v>
       </c>
       <c r="B40" t="n">
-        <v>96835</v>
+        <v>92774</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4471,34 +4467,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>53</v>
+        <v>4368</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>631686</v>
+        <v>631806</v>
       </c>
       <c r="R40" t="n">
-        <v>6661895</v>
+        <v>6661784</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4539,6 +4538,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4560,7 +4560,7 @@
         <v>128493895</v>
       </c>
       <c r="B41" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 41611-2025 artfynd.xlsx
+++ b/artfynd/A 41611-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>128493904</v>
       </c>
       <c r="B4" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>128493901</v>
       </c>
       <c r="B5" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>128493898</v>
       </c>
       <c r="B7" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>128493899</v>
       </c>
       <c r="B8" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>128493900</v>
       </c>
       <c r="B9" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>128493893</v>
       </c>
       <c r="B12" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>128493920</v>
       </c>
       <c r="B13" t="n">
-        <v>100773</v>
+        <v>100779</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1869,32 +1869,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128493913</v>
+        <v>128493919</v>
       </c>
       <c r="B14" t="n">
-        <v>96080</v>
+        <v>92774</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2170</v>
+        <v>4368</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1904,10 +1904,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>631960</v>
+        <v>631760</v>
       </c>
       <c r="R14" t="n">
-        <v>6661631</v>
+        <v>6661857</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1966,32 +1966,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128493919</v>
+        <v>128493913</v>
       </c>
       <c r="B15" t="n">
-        <v>92774</v>
+        <v>96080</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4368</v>
+        <v>2170</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2001,10 +2001,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>631760</v>
+        <v>631960</v>
       </c>
       <c r="R15" t="n">
-        <v>6661857</v>
+        <v>6661631</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2063,45 +2063,49 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128493882</v>
+        <v>128493902</v>
       </c>
       <c r="B16" t="n">
-        <v>91486</v>
+        <v>98591</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>631713</v>
+        <v>632008</v>
       </c>
       <c r="R16" t="n">
-        <v>6661819</v>
+        <v>6661933</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2136,12 +2140,18 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>mer än 40 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2160,10 +2170,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128493902</v>
+        <v>128493894</v>
       </c>
       <c r="B17" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2199,10 +2209,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>632008</v>
+        <v>631994</v>
       </c>
       <c r="R17" t="n">
-        <v>6661933</v>
+        <v>6661866</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2267,49 +2277,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128493894</v>
+        <v>128493882</v>
       </c>
       <c r="B18" t="n">
-        <v>98588</v>
+        <v>91486</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>631994</v>
+        <v>631713</v>
       </c>
       <c r="R18" t="n">
-        <v>6661866</v>
+        <v>6661819</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2344,18 +2350,12 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>mer än 40 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2471,45 +2471,49 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128493916</v>
+        <v>128493892</v>
       </c>
       <c r="B20" t="n">
-        <v>92756</v>
+        <v>98591</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>631758</v>
+        <v>632048</v>
       </c>
       <c r="R20" t="n">
-        <v>6661855</v>
+        <v>6661860</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2544,12 +2548,18 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ca 20 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2568,49 +2578,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128493892</v>
+        <v>128493916</v>
       </c>
       <c r="B21" t="n">
-        <v>98588</v>
+        <v>92756</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>632048</v>
+        <v>631758</v>
       </c>
       <c r="R21" t="n">
-        <v>6661860</v>
+        <v>6661855</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2645,18 +2651,12 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ca 20 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2969,7 +2969,7 @@
         <v>128493871</v>
       </c>
       <c r="B25" t="n">
-        <v>101678</v>
+        <v>101684</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
         <v>128493906</v>
       </c>
       <c r="B29" t="n">
-        <v>105642</v>
+        <v>105651</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3451,52 +3451,48 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128493890</v>
+        <v>128493881</v>
       </c>
       <c r="B30" t="n">
-        <v>98588</v>
+        <v>57849</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>631513</v>
+        <v>631713</v>
       </c>
       <c r="R30" t="n">
-        <v>6661886</v>
+        <v>6661820</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3528,18 +3524,12 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ca 40 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3558,48 +3548,52 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128493881</v>
+        <v>128493890</v>
       </c>
       <c r="B31" t="n">
-        <v>57849</v>
+        <v>98591</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>631713</v>
+        <v>631513</v>
       </c>
       <c r="R31" t="n">
-        <v>6661820</v>
+        <v>6661886</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3631,12 +3625,18 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ca 40 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3949,7 +3949,7 @@
         <v>128493897</v>
       </c>
       <c r="B35" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4051,7 +4051,7 @@
         <v>128493907</v>
       </c>
       <c r="B36" t="n">
-        <v>105642</v>
+        <v>105651</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>128493896</v>
       </c>
       <c r="B37" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         <v>128493903</v>
       </c>
       <c r="B38" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         <v>128493895</v>
       </c>
       <c r="B41" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 41611-2025 artfynd.xlsx
+++ b/artfynd/A 41611-2025 artfynd.xlsx
@@ -2277,32 +2277,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128493882</v>
+        <v>128493914</v>
       </c>
       <c r="B18" t="n">
-        <v>91486</v>
+        <v>96080</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5442</v>
+        <v>2170</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2312,10 +2312,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>631713</v>
+        <v>632016</v>
       </c>
       <c r="R18" t="n">
-        <v>6661819</v>
+        <v>6661935</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2374,32 +2374,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128493914</v>
+        <v>128493882</v>
       </c>
       <c r="B19" t="n">
-        <v>96080</v>
+        <v>91486</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2170</v>
+        <v>5442</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2409,10 +2409,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>632016</v>
+        <v>631713</v>
       </c>
       <c r="R19" t="n">
-        <v>6661935</v>
+        <v>6661819</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2578,32 +2578,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128493916</v>
+        <v>128493879</v>
       </c>
       <c r="B21" t="n">
-        <v>92756</v>
+        <v>91466</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2613,10 +2613,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>631758</v>
+        <v>631703</v>
       </c>
       <c r="R21" t="n">
-        <v>6661855</v>
+        <v>6661853</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2675,32 +2675,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128493879</v>
+        <v>128493884</v>
       </c>
       <c r="B22" t="n">
-        <v>91466</v>
+        <v>80154</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2710,10 +2710,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>631703</v>
+        <v>631861</v>
       </c>
       <c r="R22" t="n">
-        <v>6661853</v>
+        <v>6661676</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2772,32 +2772,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128493884</v>
+        <v>128493885</v>
       </c>
       <c r="B23" t="n">
-        <v>80154</v>
+        <v>57686</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229497</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2807,10 +2807,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>631861</v>
+        <v>631983</v>
       </c>
       <c r="R23" t="n">
-        <v>6661676</v>
+        <v>6661724</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2869,32 +2869,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128493885</v>
+        <v>128493871</v>
       </c>
       <c r="B24" t="n">
-        <v>57686</v>
+        <v>101684</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>221235</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2904,10 +2904,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>631983</v>
+        <v>631816</v>
       </c>
       <c r="R24" t="n">
-        <v>6661724</v>
+        <v>6661751</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2966,32 +2966,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128493871</v>
+        <v>128493905</v>
       </c>
       <c r="B25" t="n">
-        <v>101684</v>
+        <v>92231</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221235</v>
+        <v>366</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3001,10 +3001,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>631816</v>
+        <v>631756</v>
       </c>
       <c r="R25" t="n">
-        <v>6661751</v>
+        <v>6661847</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3063,10 +3063,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128493905</v>
+        <v>128493872</v>
       </c>
       <c r="B26" t="n">
-        <v>92231</v>
+        <v>96837</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3074,21 +3074,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>366</v>
+        <v>53</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3098,10 +3098,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>631756</v>
+        <v>632001</v>
       </c>
       <c r="R26" t="n">
-        <v>6661847</v>
+        <v>6661954</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3160,7 +3160,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128493872</v>
+        <v>128493876</v>
       </c>
       <c r="B27" t="n">
         <v>96837</v>
@@ -3195,10 +3195,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>632001</v>
+        <v>631854</v>
       </c>
       <c r="R27" t="n">
-        <v>6661954</v>
+        <v>6661710</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3257,32 +3257,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128493876</v>
+        <v>128493906</v>
       </c>
       <c r="B28" t="n">
-        <v>96837</v>
+        <v>105651</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>53</v>
+        <v>221144</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3292,10 +3292,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>631854</v>
+        <v>631754</v>
       </c>
       <c r="R28" t="n">
-        <v>6661710</v>
+        <v>6661814</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3354,45 +3354,49 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128493906</v>
+        <v>128493890</v>
       </c>
       <c r="B29" t="n">
-        <v>105651</v>
+        <v>98591</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>631754</v>
+        <v>631513</v>
       </c>
       <c r="R29" t="n">
-        <v>6661814</v>
+        <v>6661886</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3427,12 +3431,18 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ca 40 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3548,49 +3558,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128493890</v>
+        <v>128493874</v>
       </c>
       <c r="B31" t="n">
-        <v>98591</v>
+        <v>96837</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>631513</v>
+        <v>631878</v>
       </c>
       <c r="R31" t="n">
-        <v>6661886</v>
+        <v>6661711</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3625,18 +3631,12 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ca 40 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3655,10 +3655,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128493874</v>
+        <v>128493918</v>
       </c>
       <c r="B32" t="n">
-        <v>96837</v>
+        <v>92774</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3666,21 +3666,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>53</v>
+        <v>4368</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3690,10 +3690,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>631878</v>
+        <v>631638</v>
       </c>
       <c r="R32" t="n">
-        <v>6661711</v>
+        <v>6661884</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3752,10 +3752,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128493918</v>
+        <v>128493873</v>
       </c>
       <c r="B33" t="n">
-        <v>92774</v>
+        <v>96837</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3763,21 +3763,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4368</v>
+        <v>53</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3787,10 +3787,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>631638</v>
+        <v>631892</v>
       </c>
       <c r="R33" t="n">
-        <v>6661884</v>
+        <v>6661706</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3849,32 +3849,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128493873</v>
+        <v>128493907</v>
       </c>
       <c r="B34" t="n">
-        <v>96837</v>
+        <v>105651</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>53</v>
+        <v>221144</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3884,10 +3884,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>631892</v>
+        <v>631741</v>
       </c>
       <c r="R34" t="n">
-        <v>6661706</v>
+        <v>6661845</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -3920,6 +3920,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Mer än 20 bladrosetter</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4048,45 +4053,49 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128493907</v>
+        <v>128493896</v>
       </c>
       <c r="B36" t="n">
-        <v>105651</v>
+        <v>98591</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>631741</v>
+        <v>631651</v>
       </c>
       <c r="R36" t="n">
-        <v>6661845</v>
+        <v>6661849</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4123,7 +4132,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Mer än 20 bladrosetter</t>
+          <t>Ett fåtal bladrosetter</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4132,6 +4141,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4150,7 +4160,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128493896</v>
+        <v>128493903</v>
       </c>
       <c r="B37" t="n">
         <v>98591</v>
@@ -4179,20 +4189,16 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>631651</v>
+        <v>631869</v>
       </c>
       <c r="R37" t="n">
-        <v>6661849</v>
+        <v>6661711</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4229,7 +4235,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ett fåtal bladrosetter</t>
+          <t>Mer ön 40 bladrosetter</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4238,7 +4244,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4257,32 +4262,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128493903</v>
+        <v>128493878</v>
       </c>
       <c r="B38" t="n">
-        <v>98591</v>
+        <v>96837</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4292,10 +4297,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>631869</v>
+        <v>631686</v>
       </c>
       <c r="R38" t="n">
-        <v>6661711</v>
+        <v>6661895</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4328,11 +4333,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Mer ön 40 bladrosetter</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4359,10 +4359,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128493878</v>
+        <v>128493917</v>
       </c>
       <c r="B39" t="n">
-        <v>96837</v>
+        <v>92774</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4370,34 +4370,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>53</v>
+        <v>4368</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>631686</v>
+        <v>631806</v>
       </c>
       <c r="R39" t="n">
-        <v>6661895</v>
+        <v>6661784</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4438,6 +4441,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4456,37 +4460,38 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128493917</v>
+        <v>128493895</v>
       </c>
       <c r="B40" t="n">
-        <v>92774</v>
+        <v>98591</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4368</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4494,10 +4499,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>631806</v>
+        <v>631908</v>
       </c>
       <c r="R40" t="n">
-        <v>6661784</v>
+        <v>6661782</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4530,6 +4535,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Mer än 50  bladrosetter</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4557,38 +4567,37 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128493895</v>
+        <v>128493916</v>
       </c>
       <c r="B41" t="n">
-        <v>98591</v>
+        <v>92768</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4596,10 +4605,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>631908</v>
+        <v>631758</v>
       </c>
       <c r="R41" t="n">
-        <v>6661782</v>
+        <v>6661855</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4632,11 +4641,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Mer än 50  bladrosetter</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 41611-2025 artfynd.xlsx
+++ b/artfynd/A 41611-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128493877</v>
+        <v>128493883</v>
       </c>
       <c r="B2" t="n">
-        <v>96837</v>
+        <v>80229</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>53</v>
+        <v>6463</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>631706</v>
+        <v>631861</v>
       </c>
       <c r="R2" t="n">
-        <v>6661848</v>
+        <v>6661676</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128493883</v>
+        <v>128493877</v>
       </c>
       <c r="B3" t="n">
-        <v>80229</v>
+        <v>96838</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6463</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>631861</v>
+        <v>631706</v>
       </c>
       <c r="R3" t="n">
-        <v>6661676</v>
+        <v>6661848</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -872,7 +872,7 @@
         <v>128493904</v>
       </c>
       <c r="B4" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>128493901</v>
       </c>
       <c r="B5" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>128493898</v>
       </c>
       <c r="B7" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>128493899</v>
       </c>
       <c r="B8" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>128493900</v>
       </c>
       <c r="B9" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1471,32 +1471,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128493875</v>
+        <v>128493915</v>
       </c>
       <c r="B10" t="n">
-        <v>96837</v>
+        <v>96081</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>53</v>
+        <v>2170</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>631869</v>
+        <v>631915</v>
       </c>
       <c r="R10" t="n">
-        <v>6661711</v>
+        <v>6661808</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1568,32 +1568,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128493915</v>
+        <v>128493875</v>
       </c>
       <c r="B11" t="n">
-        <v>96080</v>
+        <v>96838</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2170</v>
+        <v>53</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1603,10 +1603,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>631915</v>
+        <v>631869</v>
       </c>
       <c r="R11" t="n">
-        <v>6661808</v>
+        <v>6661711</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1668,7 +1668,7 @@
         <v>128493893</v>
       </c>
       <c r="B12" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>128493920</v>
       </c>
       <c r="B13" t="n">
-        <v>100779</v>
+        <v>100780</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1869,32 +1869,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128493919</v>
+        <v>128493913</v>
       </c>
       <c r="B14" t="n">
-        <v>92774</v>
+        <v>96081</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4368</v>
+        <v>2170</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1904,10 +1904,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>631760</v>
+        <v>631960</v>
       </c>
       <c r="R14" t="n">
-        <v>6661857</v>
+        <v>6661631</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1966,32 +1966,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128493913</v>
+        <v>128493919</v>
       </c>
       <c r="B15" t="n">
-        <v>96080</v>
+        <v>92775</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2170</v>
+        <v>4368</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2001,10 +2001,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>631960</v>
+        <v>631760</v>
       </c>
       <c r="R15" t="n">
-        <v>6661631</v>
+        <v>6661857</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2063,49 +2063,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128493902</v>
+        <v>128493914</v>
       </c>
       <c r="B16" t="n">
-        <v>98591</v>
+        <v>96081</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>2170</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>632008</v>
+        <v>632016</v>
       </c>
       <c r="R16" t="n">
-        <v>6661933</v>
+        <v>6661935</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2140,18 +2136,12 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>mer än 40 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2170,49 +2160,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128493894</v>
+        <v>128493882</v>
       </c>
       <c r="B17" t="n">
-        <v>98591</v>
+        <v>91487</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>631994</v>
+        <v>631713</v>
       </c>
       <c r="R17" t="n">
-        <v>6661866</v>
+        <v>6661819</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2247,18 +2233,12 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>mer än 40 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2277,45 +2257,49 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128493914</v>
+        <v>128493902</v>
       </c>
       <c r="B18" t="n">
-        <v>96080</v>
+        <v>98592</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2170</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>632016</v>
+        <v>632008</v>
       </c>
       <c r="R18" t="n">
-        <v>6661935</v>
+        <v>6661933</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2350,12 +2334,18 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>mer än 40 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2374,45 +2364,49 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128493882</v>
+        <v>128493894</v>
       </c>
       <c r="B19" t="n">
-        <v>91486</v>
+        <v>98592</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>631713</v>
+        <v>631994</v>
       </c>
       <c r="R19" t="n">
-        <v>6661819</v>
+        <v>6661866</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2447,12 +2441,18 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>mer än 40 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2474,7 +2474,7 @@
         <v>128493892</v>
       </c>
       <c r="B20" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
         <v>128493879</v>
       </c>
       <c r="B21" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2872,7 +2872,7 @@
         <v>128493871</v>
       </c>
       <c r="B24" t="n">
-        <v>101684</v>
+        <v>101685</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>128493905</v>
       </c>
       <c r="B25" t="n">
-        <v>92231</v>
+        <v>92232</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
         <v>128493872</v>
       </c>
       <c r="B26" t="n">
-        <v>96837</v>
+        <v>96838</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>128493876</v>
       </c>
       <c r="B27" t="n">
-        <v>96837</v>
+        <v>96838</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
         <v>128493906</v>
       </c>
       <c r="B28" t="n">
-        <v>105651</v>
+        <v>105654</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3354,52 +3354,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128493890</v>
+        <v>128493881</v>
       </c>
       <c r="B29" t="n">
-        <v>98591</v>
+        <v>57849</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>631513</v>
+        <v>631713</v>
       </c>
       <c r="R29" t="n">
-        <v>6661886</v>
+        <v>6661820</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3431,18 +3427,12 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ca 40 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3461,48 +3451,52 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128493881</v>
+        <v>128493890</v>
       </c>
       <c r="B30" t="n">
-        <v>57849</v>
+        <v>98592</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>631713</v>
+        <v>631513</v>
       </c>
       <c r="R30" t="n">
-        <v>6661820</v>
+        <v>6661886</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3534,12 +3528,18 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ca 40 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3561,7 +3561,7 @@
         <v>128493874</v>
       </c>
       <c r="B31" t="n">
-        <v>96837</v>
+        <v>96838</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>128493918</v>
       </c>
       <c r="B32" t="n">
-        <v>92774</v>
+        <v>92775</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
         <v>128493873</v>
       </c>
       <c r="B33" t="n">
-        <v>96837</v>
+        <v>96838</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3849,32 +3849,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128493907</v>
+        <v>128493897</v>
       </c>
       <c r="B34" t="n">
-        <v>105651</v>
+        <v>98592</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3884,10 +3884,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>631741</v>
+        <v>631658</v>
       </c>
       <c r="R34" t="n">
-        <v>6661845</v>
+        <v>6661890</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -3924,7 +3924,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Mer än 20 bladrosetter</t>
+          <t>Ett fåtal bladrosetter</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3951,32 +3951,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128493897</v>
+        <v>128493907</v>
       </c>
       <c r="B35" t="n">
-        <v>98591</v>
+        <v>105654</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3986,10 +3986,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>631658</v>
+        <v>631741</v>
       </c>
       <c r="R35" t="n">
-        <v>6661890</v>
+        <v>6661845</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4026,7 +4026,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ett fåtal bladrosetter</t>
+          <t>Mer än 20 bladrosetter</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4056,7 +4056,7 @@
         <v>128493896</v>
       </c>
       <c r="B36" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>128493903</v>
       </c>
       <c r="B37" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4262,10 +4262,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128493878</v>
+        <v>128493917</v>
       </c>
       <c r="B38" t="n">
-        <v>96837</v>
+        <v>92775</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4273,34 +4273,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>53</v>
+        <v>4368</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>631686</v>
+        <v>631806</v>
       </c>
       <c r="R38" t="n">
-        <v>6661895</v>
+        <v>6661784</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4341,6 +4344,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4359,10 +4363,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128493917</v>
+        <v>128493878</v>
       </c>
       <c r="B39" t="n">
-        <v>92774</v>
+        <v>96838</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4370,37 +4374,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4368</v>
+        <v>53</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>631806</v>
+        <v>631686</v>
       </c>
       <c r="R39" t="n">
-        <v>6661784</v>
+        <v>6661895</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4441,7 +4442,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4463,7 +4463,7 @@
         <v>128493895</v>
       </c>
       <c r="B40" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
         <v>128493916</v>
       </c>
       <c r="B41" t="n">
-        <v>92768</v>
+        <v>92769</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 41611-2025 artfynd.xlsx
+++ b/artfynd/A 41611-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY41"/>
+  <dimension ref="A1:AY53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128493883</v>
+        <v>128493877</v>
       </c>
       <c r="B2" t="n">
-        <v>80229</v>
+        <v>96865</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6463</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>631861</v>
+        <v>631706</v>
       </c>
       <c r="R2" t="n">
-        <v>6661676</v>
+        <v>6661848</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128493877</v>
+        <v>128493883</v>
       </c>
       <c r="B3" t="n">
-        <v>96838</v>
+        <v>80256</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>6463</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>631706</v>
+        <v>631861</v>
       </c>
       <c r="R3" t="n">
-        <v>6661848</v>
+        <v>6661676</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -872,7 +872,7 @@
         <v>128493904</v>
       </c>
       <c r="B4" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>128493901</v>
       </c>
       <c r="B5" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>128493909</v>
       </c>
       <c r="B6" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>128493898</v>
       </c>
       <c r="B7" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>128493899</v>
       </c>
       <c r="B8" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>128493900</v>
       </c>
       <c r="B9" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1471,32 +1471,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128493915</v>
+        <v>128493875</v>
       </c>
       <c r="B10" t="n">
-        <v>96081</v>
+        <v>96865</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2170</v>
+        <v>53</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>631915</v>
+        <v>631869</v>
       </c>
       <c r="R10" t="n">
-        <v>6661808</v>
+        <v>6661711</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1568,32 +1568,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128493875</v>
+        <v>128493915</v>
       </c>
       <c r="B11" t="n">
-        <v>96838</v>
+        <v>96108</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>53</v>
+        <v>2170</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1603,10 +1603,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>631869</v>
+        <v>631915</v>
       </c>
       <c r="R11" t="n">
-        <v>6661711</v>
+        <v>6661808</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1668,7 +1668,7 @@
         <v>128493893</v>
       </c>
       <c r="B12" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>128493920</v>
       </c>
       <c r="B13" t="n">
-        <v>100780</v>
+        <v>100807</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1869,32 +1869,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128493913</v>
+        <v>128493919</v>
       </c>
       <c r="B14" t="n">
-        <v>96081</v>
+        <v>92802</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2170</v>
+        <v>4368</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1904,10 +1904,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>631960</v>
+        <v>631760</v>
       </c>
       <c r="R14" t="n">
-        <v>6661631</v>
+        <v>6661857</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1966,32 +1966,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128493919</v>
+        <v>128493913</v>
       </c>
       <c r="B15" t="n">
-        <v>92775</v>
+        <v>96108</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4368</v>
+        <v>2170</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2001,10 +2001,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>631760</v>
+        <v>631960</v>
       </c>
       <c r="R15" t="n">
-        <v>6661857</v>
+        <v>6661631</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2066,7 +2066,7 @@
         <v>128493914</v>
       </c>
       <c r="B16" t="n">
-        <v>96081</v>
+        <v>96108</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2163,7 +2163,7 @@
         <v>128493882</v>
       </c>
       <c r="B17" t="n">
-        <v>91487</v>
+        <v>91514</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2257,10 +2257,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128493902</v>
+        <v>128493894</v>
       </c>
       <c r="B18" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2296,10 +2296,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>632008</v>
+        <v>631994</v>
       </c>
       <c r="R18" t="n">
-        <v>6661933</v>
+        <v>6661866</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2364,10 +2364,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128493894</v>
+        <v>128493902</v>
       </c>
       <c r="B19" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>631994</v>
+        <v>632008</v>
       </c>
       <c r="R19" t="n">
-        <v>6661866</v>
+        <v>6661933</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2474,7 +2474,7 @@
         <v>128493892</v>
       </c>
       <c r="B20" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
         <v>128493879</v>
       </c>
       <c r="B21" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2678,7 +2678,7 @@
         <v>128493884</v>
       </c>
       <c r="B22" t="n">
-        <v>80154</v>
+        <v>80181</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2775,7 +2775,7 @@
         <v>128493885</v>
       </c>
       <c r="B23" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2872,7 +2872,7 @@
         <v>128493871</v>
       </c>
       <c r="B24" t="n">
-        <v>101685</v>
+        <v>101712</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>128493905</v>
       </c>
       <c r="B25" t="n">
-        <v>92232</v>
+        <v>92259</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3063,32 +3063,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128493872</v>
+        <v>128493906</v>
       </c>
       <c r="B26" t="n">
-        <v>96838</v>
+        <v>105682</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>53</v>
+        <v>221144</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3098,10 +3098,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>632001</v>
+        <v>631754</v>
       </c>
       <c r="R26" t="n">
-        <v>6661954</v>
+        <v>6661814</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3160,10 +3160,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128493876</v>
+        <v>128493872</v>
       </c>
       <c r="B27" t="n">
-        <v>96838</v>
+        <v>96865</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3195,10 +3195,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>631854</v>
+        <v>632001</v>
       </c>
       <c r="R27" t="n">
-        <v>6661710</v>
+        <v>6661954</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3257,32 +3257,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128493906</v>
+        <v>128493876</v>
       </c>
       <c r="B28" t="n">
-        <v>105654</v>
+        <v>96865</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221144</v>
+        <v>53</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3292,10 +3292,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>631754</v>
+        <v>631854</v>
       </c>
       <c r="R28" t="n">
-        <v>6661814</v>
+        <v>6661710</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3357,7 +3357,7 @@
         <v>128493881</v>
       </c>
       <c r="B29" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
         <v>128493890</v>
       </c>
       <c r="B30" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3558,10 +3558,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128493874</v>
+        <v>128493918</v>
       </c>
       <c r="B31" t="n">
-        <v>96838</v>
+        <v>92802</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3569,21 +3569,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>53</v>
+        <v>4368</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3593,10 +3593,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>631878</v>
+        <v>631638</v>
       </c>
       <c r="R31" t="n">
-        <v>6661711</v>
+        <v>6661884</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3655,10 +3655,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128493918</v>
+        <v>128493874</v>
       </c>
       <c r="B32" t="n">
-        <v>92775</v>
+        <v>96865</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3666,21 +3666,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4368</v>
+        <v>53</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3690,10 +3690,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>631638</v>
+        <v>631878</v>
       </c>
       <c r="R32" t="n">
-        <v>6661884</v>
+        <v>6661711</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3755,7 +3755,7 @@
         <v>128493873</v>
       </c>
       <c r="B33" t="n">
-        <v>96838</v>
+        <v>96865</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>128493897</v>
       </c>
       <c r="B34" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>128493907</v>
       </c>
       <c r="B35" t="n">
-        <v>105654</v>
+        <v>105682</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         <v>128493896</v>
       </c>
       <c r="B36" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>128493903</v>
       </c>
       <c r="B37" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         <v>128493917</v>
       </c>
       <c r="B38" t="n">
-        <v>92775</v>
+        <v>92802</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4366,7 +4366,7 @@
         <v>128493878</v>
       </c>
       <c r="B39" t="n">
-        <v>96838</v>
+        <v>96865</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4463,7 +4463,7 @@
         <v>128493895</v>
       </c>
       <c r="B40" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
         <v>128493916</v>
       </c>
       <c r="B41" t="n">
-        <v>92769</v>
+        <v>92796</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4666,6 +4666,1184 @@
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>128792098</v>
+      </c>
+      <c r="B42" t="n">
+        <v>91459</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Risboskogen, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>631595</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6661875</v>
+      </c>
+      <c r="S42" t="n">
+        <v>15</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>128792102</v>
+      </c>
+      <c r="B43" t="n">
+        <v>98619</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Risboskogen, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>631659</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6661876</v>
+      </c>
+      <c r="S43" t="n">
+        <v>15</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>20 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>128792112</v>
+      </c>
+      <c r="B44" t="n">
+        <v>92802</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>4368</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Dofttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Hydnellum suaveolens</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Risboskogen, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>631814</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6661721</v>
+      </c>
+      <c r="S44" t="n">
+        <v>15</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>128792106</v>
+      </c>
+      <c r="B45" t="n">
+        <v>96061</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>210</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Risboskogen, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>631759</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6661865</v>
+      </c>
+      <c r="S45" t="n">
+        <v>15</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>30 kapslar</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>128792097</v>
+      </c>
+      <c r="B46" t="n">
+        <v>96865</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>53</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Risboskogen, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>631595</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6661875</v>
+      </c>
+      <c r="S46" t="n">
+        <v>15</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>128792111</v>
+      </c>
+      <c r="B47" t="n">
+        <v>92818</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Risboskogen, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>631758</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6661861</v>
+      </c>
+      <c r="S47" t="n">
+        <v>15</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>128792108</v>
+      </c>
+      <c r="B48" t="n">
+        <v>91512</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Risboskogen, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>631589</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6661792</v>
+      </c>
+      <c r="S48" t="n">
+        <v>15</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>128792104</v>
+      </c>
+      <c r="B49" t="n">
+        <v>92786</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>788</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Gul taggsvamp</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Hydnellum geogenium</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Risboskogen, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>631748</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6661858</v>
+      </c>
+      <c r="S49" t="n">
+        <v>15</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>128792114</v>
+      </c>
+      <c r="B50" t="n">
+        <v>100807</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Risboskogen, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>631859</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6661778</v>
+      </c>
+      <c r="S50" t="n">
+        <v>15</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>128792093</v>
+      </c>
+      <c r="B51" t="n">
+        <v>5197</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Risboskogen, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>631577</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6661796</v>
+      </c>
+      <c r="S51" t="n">
+        <v>15</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>128792110</v>
+      </c>
+      <c r="B52" t="n">
+        <v>96108</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>2170</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Flagellkvastmossa</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Dicranum flagellare</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Risboskogen, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>631612</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6661879</v>
+      </c>
+      <c r="S52" t="n">
+        <v>15</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>128792113</v>
+      </c>
+      <c r="B53" t="n">
+        <v>100807</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Risboskogen, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>631820</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6661766</v>
+      </c>
+      <c r="S53" t="n">
+        <v>15</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41611-2025 artfynd.xlsx
+++ b/artfynd/A 41611-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128493877</v>
+        <v>128493904</v>
       </c>
       <c r="B2" t="n">
-        <v>96865</v>
+        <v>98619</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>631706</v>
+        <v>631707</v>
       </c>
       <c r="R2" t="n">
-        <v>6661848</v>
+        <v>6661837</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>12 bladrosetter</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,32 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128493883</v>
+        <v>128493901</v>
       </c>
       <c r="B3" t="n">
-        <v>80256</v>
+        <v>98619</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>631861</v>
+        <v>632054</v>
       </c>
       <c r="R3" t="n">
-        <v>6661676</v>
+        <v>6661938</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -843,6 +848,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Mer än 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,32 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128493904</v>
+        <v>128493877</v>
       </c>
       <c r="B4" t="n">
-        <v>98619</v>
+        <v>96865</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>631707</v>
+        <v>631706</v>
       </c>
       <c r="R4" t="n">
-        <v>6661837</v>
+        <v>6661848</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -940,11 +950,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>12 bladrosetter</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,32 +976,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128493901</v>
+        <v>128493883</v>
       </c>
       <c r="B5" t="n">
-        <v>98619</v>
+        <v>80256</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>632054</v>
+        <v>631861</v>
       </c>
       <c r="R5" t="n">
-        <v>6661938</v>
+        <v>6661676</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1042,11 +1047,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Mer än 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1869,32 +1869,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128493919</v>
+        <v>128493913</v>
       </c>
       <c r="B14" t="n">
-        <v>92802</v>
+        <v>96108</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4368</v>
+        <v>2170</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1904,10 +1904,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>631760</v>
+        <v>631960</v>
       </c>
       <c r="R14" t="n">
-        <v>6661857</v>
+        <v>6661631</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1966,32 +1966,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128493913</v>
+        <v>128493919</v>
       </c>
       <c r="B15" t="n">
-        <v>96108</v>
+        <v>92802</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2170</v>
+        <v>4368</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2001,10 +2001,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>631960</v>
+        <v>631760</v>
       </c>
       <c r="R15" t="n">
-        <v>6661631</v>
+        <v>6661857</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2772,32 +2772,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128493885</v>
+        <v>128493871</v>
       </c>
       <c r="B23" t="n">
-        <v>57713</v>
+        <v>101712</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>221235</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2807,10 +2807,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>631983</v>
+        <v>631816</v>
       </c>
       <c r="R23" t="n">
-        <v>6661724</v>
+        <v>6661751</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2869,32 +2869,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128493871</v>
+        <v>128493885</v>
       </c>
       <c r="B24" t="n">
-        <v>101712</v>
+        <v>57713</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221235</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2904,10 +2904,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>631816</v>
+        <v>631983</v>
       </c>
       <c r="R24" t="n">
-        <v>6661751</v>
+        <v>6661724</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3063,32 +3063,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128493906</v>
+        <v>128493872</v>
       </c>
       <c r="B26" t="n">
-        <v>105682</v>
+        <v>96865</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221144</v>
+        <v>53</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3098,10 +3098,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>631754</v>
+        <v>632001</v>
       </c>
       <c r="R26" t="n">
-        <v>6661814</v>
+        <v>6661954</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3160,7 +3160,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128493872</v>
+        <v>128493876</v>
       </c>
       <c r="B27" t="n">
         <v>96865</v>
@@ -3195,10 +3195,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>632001</v>
+        <v>631854</v>
       </c>
       <c r="R27" t="n">
-        <v>6661954</v>
+        <v>6661710</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3257,32 +3257,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128493876</v>
+        <v>128493906</v>
       </c>
       <c r="B28" t="n">
-        <v>96865</v>
+        <v>105682</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>53</v>
+        <v>221144</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3292,10 +3292,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>631854</v>
+        <v>631754</v>
       </c>
       <c r="R28" t="n">
-        <v>6661710</v>
+        <v>6661814</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3849,32 +3849,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128493897</v>
+        <v>128493907</v>
       </c>
       <c r="B34" t="n">
-        <v>98619</v>
+        <v>105682</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3884,10 +3884,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>631658</v>
+        <v>631741</v>
       </c>
       <c r="R34" t="n">
-        <v>6661890</v>
+        <v>6661845</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -3924,7 +3924,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ett fåtal bladrosetter</t>
+          <t>Mer än 20 bladrosetter</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3951,32 +3951,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128493907</v>
+        <v>128493897</v>
       </c>
       <c r="B35" t="n">
-        <v>105682</v>
+        <v>98619</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3986,10 +3986,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>631741</v>
+        <v>631658</v>
       </c>
       <c r="R35" t="n">
-        <v>6661845</v>
+        <v>6661890</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4026,7 +4026,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Mer än 20 bladrosetter</t>
+          <t>Ett fåtal bladrosetter</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5458,10 +5458,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128792114</v>
+        <v>128792093</v>
       </c>
       <c r="B50" t="n">
-        <v>100807</v>
+        <v>5197</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5469,21 +5469,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5493,10 +5493,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>631859</v>
+        <v>631577</v>
       </c>
       <c r="R50" t="n">
-        <v>6661778</v>
+        <v>6661796</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5555,10 +5555,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128792093</v>
+        <v>128792114</v>
       </c>
       <c r="B51" t="n">
-        <v>5197</v>
+        <v>100807</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5566,21 +5566,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5590,10 +5590,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>631577</v>
+        <v>631859</v>
       </c>
       <c r="R51" t="n">
-        <v>6661796</v>
+        <v>6661778</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>

--- a/artfynd/A 41611-2025 artfynd.xlsx
+++ b/artfynd/A 41611-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128493904</v>
+        <v>128493877</v>
       </c>
       <c r="B2" t="n">
-        <v>98619</v>
+        <v>96871</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>631707</v>
+        <v>631706</v>
       </c>
       <c r="R2" t="n">
-        <v>6661837</v>
+        <v>6661848</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>12 bladrosetter</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128493901</v>
+        <v>128493883</v>
       </c>
       <c r="B3" t="n">
-        <v>98619</v>
+        <v>80260</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>632054</v>
+        <v>631861</v>
       </c>
       <c r="R3" t="n">
-        <v>6661938</v>
+        <v>6661676</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -848,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Mer än 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128493877</v>
+        <v>128493904</v>
       </c>
       <c r="B4" t="n">
-        <v>96865</v>
+        <v>98625</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>631706</v>
+        <v>631707</v>
       </c>
       <c r="R4" t="n">
-        <v>6661848</v>
+        <v>6661837</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -950,6 +940,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>12 bladrosetter</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,32 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128493883</v>
+        <v>128493901</v>
       </c>
       <c r="B5" t="n">
-        <v>80256</v>
+        <v>98625</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>631861</v>
+        <v>632054</v>
       </c>
       <c r="R5" t="n">
-        <v>6661676</v>
+        <v>6661938</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1047,6 +1042,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Mer än 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1076,7 +1076,7 @@
         <v>128493909</v>
       </c>
       <c r="B6" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>128493898</v>
       </c>
       <c r="B7" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>128493899</v>
       </c>
       <c r="B8" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>128493900</v>
       </c>
       <c r="B9" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1471,32 +1471,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128493875</v>
+        <v>128493915</v>
       </c>
       <c r="B10" t="n">
-        <v>96865</v>
+        <v>96114</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>53</v>
+        <v>2170</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>631869</v>
+        <v>631915</v>
       </c>
       <c r="R10" t="n">
-        <v>6661711</v>
+        <v>6661808</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1568,45 +1568,49 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128493915</v>
+        <v>128493893</v>
       </c>
       <c r="B11" t="n">
-        <v>96108</v>
+        <v>98625</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2170</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>631915</v>
+        <v>632068</v>
       </c>
       <c r="R11" t="n">
-        <v>6661808</v>
+        <v>6661949</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1641,12 +1645,18 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ca 20 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1665,49 +1675,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128493893</v>
+        <v>128493875</v>
       </c>
       <c r="B12" t="n">
-        <v>98619</v>
+        <v>96871</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>632068</v>
+        <v>631869</v>
       </c>
       <c r="R12" t="n">
-        <v>6661949</v>
+        <v>6661711</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1742,18 +1748,12 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ca 20 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1775,7 +1775,7 @@
         <v>128493920</v>
       </c>
       <c r="B13" t="n">
-        <v>100807</v>
+        <v>100813</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>128493913</v>
       </c>
       <c r="B14" t="n">
-        <v>96108</v>
+        <v>96114</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>128493919</v>
       </c>
       <c r="B15" t="n">
-        <v>92802</v>
+        <v>92807</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2063,32 +2063,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128493914</v>
+        <v>128493882</v>
       </c>
       <c r="B16" t="n">
-        <v>96108</v>
+        <v>91519</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2170</v>
+        <v>5442</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2098,10 +2098,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>632016</v>
+        <v>631713</v>
       </c>
       <c r="R16" t="n">
-        <v>6661935</v>
+        <v>6661819</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2160,32 +2160,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128493882</v>
+        <v>128493914</v>
       </c>
       <c r="B17" t="n">
-        <v>91514</v>
+        <v>96114</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5442</v>
+        <v>2170</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2195,10 +2195,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>631713</v>
+        <v>632016</v>
       </c>
       <c r="R17" t="n">
-        <v>6661819</v>
+        <v>6661935</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2257,10 +2257,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128493894</v>
+        <v>128493902</v>
       </c>
       <c r="B18" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2296,10 +2296,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>631994</v>
+        <v>632008</v>
       </c>
       <c r="R18" t="n">
-        <v>6661866</v>
+        <v>6661933</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2364,10 +2364,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128493902</v>
+        <v>128493894</v>
       </c>
       <c r="B19" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>632008</v>
+        <v>631994</v>
       </c>
       <c r="R19" t="n">
-        <v>6661933</v>
+        <v>6661866</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2474,7 +2474,7 @@
         <v>128493892</v>
       </c>
       <c r="B20" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
         <v>128493879</v>
       </c>
       <c r="B21" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2678,7 +2678,7 @@
         <v>128493884</v>
       </c>
       <c r="B22" t="n">
-        <v>80181</v>
+        <v>80185</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2772,32 +2772,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128493871</v>
+        <v>128493885</v>
       </c>
       <c r="B23" t="n">
-        <v>101712</v>
+        <v>57713</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221235</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2807,10 +2807,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>631816</v>
+        <v>631983</v>
       </c>
       <c r="R23" t="n">
-        <v>6661751</v>
+        <v>6661724</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2869,32 +2869,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128493885</v>
+        <v>128493871</v>
       </c>
       <c r="B24" t="n">
-        <v>57713</v>
+        <v>101718</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>221235</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2904,10 +2904,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>631983</v>
+        <v>631816</v>
       </c>
       <c r="R24" t="n">
-        <v>6661724</v>
+        <v>6661751</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2969,7 +2969,7 @@
         <v>128493905</v>
       </c>
       <c r="B25" t="n">
-        <v>92259</v>
+        <v>92264</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
         <v>128493872</v>
       </c>
       <c r="B26" t="n">
-        <v>96865</v>
+        <v>96871</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>128493876</v>
       </c>
       <c r="B27" t="n">
-        <v>96865</v>
+        <v>96871</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
         <v>128493906</v>
       </c>
       <c r="B28" t="n">
-        <v>105682</v>
+        <v>105688</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
         <v>128493890</v>
       </c>
       <c r="B30" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3558,10 +3558,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128493918</v>
+        <v>128493874</v>
       </c>
       <c r="B31" t="n">
-        <v>92802</v>
+        <v>96871</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3569,21 +3569,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4368</v>
+        <v>53</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3593,10 +3593,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>631638</v>
+        <v>631878</v>
       </c>
       <c r="R31" t="n">
-        <v>6661884</v>
+        <v>6661711</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3655,10 +3655,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128493874</v>
+        <v>128493918</v>
       </c>
       <c r="B32" t="n">
-        <v>96865</v>
+        <v>92807</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3666,21 +3666,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>53</v>
+        <v>4368</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3690,10 +3690,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>631878</v>
+        <v>631638</v>
       </c>
       <c r="R32" t="n">
-        <v>6661711</v>
+        <v>6661884</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3755,7 +3755,7 @@
         <v>128493873</v>
       </c>
       <c r="B33" t="n">
-        <v>96865</v>
+        <v>96871</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3849,32 +3849,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128493907</v>
+        <v>128493897</v>
       </c>
       <c r="B34" t="n">
-        <v>105682</v>
+        <v>98625</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3884,10 +3884,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>631741</v>
+        <v>631658</v>
       </c>
       <c r="R34" t="n">
-        <v>6661845</v>
+        <v>6661890</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -3924,7 +3924,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Mer än 20 bladrosetter</t>
+          <t>Ett fåtal bladrosetter</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3951,32 +3951,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128493897</v>
+        <v>128493907</v>
       </c>
       <c r="B35" t="n">
-        <v>98619</v>
+        <v>105688</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3986,10 +3986,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>631658</v>
+        <v>631741</v>
       </c>
       <c r="R35" t="n">
-        <v>6661890</v>
+        <v>6661845</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4026,7 +4026,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ett fåtal bladrosetter</t>
+          <t>Mer än 20 bladrosetter</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4056,7 +4056,7 @@
         <v>128493896</v>
       </c>
       <c r="B36" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>128493903</v>
       </c>
       <c r="B37" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4262,10 +4262,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128493917</v>
+        <v>128493878</v>
       </c>
       <c r="B38" t="n">
-        <v>92802</v>
+        <v>96871</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4273,37 +4273,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4368</v>
+        <v>53</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>631806</v>
+        <v>631686</v>
       </c>
       <c r="R38" t="n">
-        <v>6661784</v>
+        <v>6661895</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4344,7 +4341,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4363,10 +4359,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128493878</v>
+        <v>128493917</v>
       </c>
       <c r="B39" t="n">
-        <v>96865</v>
+        <v>92807</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4374,34 +4370,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>53</v>
+        <v>4368</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>631686</v>
+        <v>631806</v>
       </c>
       <c r="R39" t="n">
-        <v>6661895</v>
+        <v>6661784</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4442,6 +4441,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4463,7 +4463,7 @@
         <v>128493895</v>
       </c>
       <c r="B40" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
         <v>128493916</v>
       </c>
       <c r="B41" t="n">
-        <v>92796</v>
+        <v>92801</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4671,7 +4671,7 @@
         <v>128792098</v>
       </c>
       <c r="B42" t="n">
-        <v>91459</v>
+        <v>91464</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4768,7 +4768,7 @@
         <v>128792102</v>
       </c>
       <c r="B43" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4867,32 +4867,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128792112</v>
+        <v>128792106</v>
       </c>
       <c r="B44" t="n">
-        <v>92802</v>
+        <v>96067</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4368</v>
+        <v>210</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4902,10 +4902,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>631814</v>
+        <v>631759</v>
       </c>
       <c r="R44" t="n">
-        <v>6661721</v>
+        <v>6661865</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4938,6 +4938,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>30 kapslar</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4964,32 +4969,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128792106</v>
+        <v>128792112</v>
       </c>
       <c r="B45" t="n">
-        <v>96061</v>
+        <v>92807</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>210</v>
+        <v>4368</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4999,10 +5004,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>631759</v>
+        <v>631814</v>
       </c>
       <c r="R45" t="n">
-        <v>6661865</v>
+        <v>6661721</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5035,11 +5040,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>30 kapslar</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5069,7 +5069,7 @@
         <v>128792097</v>
       </c>
       <c r="B46" t="n">
-        <v>96865</v>
+        <v>96871</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5166,7 +5166,7 @@
         <v>128792111</v>
       </c>
       <c r="B47" t="n">
-        <v>92818</v>
+        <v>92823</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         <v>128792108</v>
       </c>
       <c r="B48" t="n">
-        <v>91512</v>
+        <v>91517</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5364,7 +5364,7 @@
         <v>128792104</v>
       </c>
       <c r="B49" t="n">
-        <v>92786</v>
+        <v>92791</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5458,10 +5458,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128792093</v>
+        <v>128792114</v>
       </c>
       <c r="B50" t="n">
-        <v>5197</v>
+        <v>100813</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5469,21 +5469,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5493,10 +5493,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>631577</v>
+        <v>631859</v>
       </c>
       <c r="R50" t="n">
-        <v>6661796</v>
+        <v>6661778</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5555,10 +5555,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128792114</v>
+        <v>128792093</v>
       </c>
       <c r="B51" t="n">
-        <v>100807</v>
+        <v>5197</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5566,21 +5566,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5590,10 +5590,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>631859</v>
+        <v>631577</v>
       </c>
       <c r="R51" t="n">
-        <v>6661778</v>
+        <v>6661796</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5655,7 +5655,7 @@
         <v>128792110</v>
       </c>
       <c r="B52" t="n">
-        <v>96108</v>
+        <v>96114</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5752,7 +5752,7 @@
         <v>128792113</v>
       </c>
       <c r="B53" t="n">
-        <v>100807</v>
+        <v>100813</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 41611-2025 artfynd.xlsx
+++ b/artfynd/A 41611-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128493877</v>
+        <v>128493904</v>
       </c>
       <c r="B2" t="n">
-        <v>96871</v>
+        <v>98632</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>631706</v>
+        <v>631707</v>
       </c>
       <c r="R2" t="n">
-        <v>6661848</v>
+        <v>6661837</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>12 bladrosetter</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,32 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128493883</v>
+        <v>128493901</v>
       </c>
       <c r="B3" t="n">
-        <v>80260</v>
+        <v>98632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>631861</v>
+        <v>632054</v>
       </c>
       <c r="R3" t="n">
-        <v>6661676</v>
+        <v>6661938</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -843,6 +848,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Mer än 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,32 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128493904</v>
+        <v>128493877</v>
       </c>
       <c r="B4" t="n">
-        <v>98625</v>
+        <v>96878</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>631707</v>
+        <v>631706</v>
       </c>
       <c r="R4" t="n">
-        <v>6661837</v>
+        <v>6661848</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -940,11 +950,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>12 bladrosetter</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,32 +976,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128493901</v>
+        <v>128493883</v>
       </c>
       <c r="B5" t="n">
-        <v>98625</v>
+        <v>80260</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>632054</v>
+        <v>631861</v>
       </c>
       <c r="R5" t="n">
-        <v>6661938</v>
+        <v>6661676</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1042,11 +1047,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Mer än 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1173,7 +1173,7 @@
         <v>128493898</v>
       </c>
       <c r="B7" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>128493899</v>
       </c>
       <c r="B8" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>128493900</v>
       </c>
       <c r="B9" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>128493915</v>
       </c>
       <c r="B10" t="n">
-        <v>96114</v>
+        <v>96121</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1568,49 +1568,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128493893</v>
+        <v>128493875</v>
       </c>
       <c r="B11" t="n">
-        <v>98625</v>
+        <v>96878</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>632068</v>
+        <v>631869</v>
       </c>
       <c r="R11" t="n">
-        <v>6661949</v>
+        <v>6661711</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1645,18 +1641,12 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ca 20 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1675,45 +1665,49 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128493875</v>
+        <v>128493893</v>
       </c>
       <c r="B12" t="n">
-        <v>96871</v>
+        <v>98632</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>631869</v>
+        <v>632068</v>
       </c>
       <c r="R12" t="n">
-        <v>6661711</v>
+        <v>6661949</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1748,12 +1742,18 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ca 20 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1775,7 +1775,7 @@
         <v>128493920</v>
       </c>
       <c r="B13" t="n">
-        <v>100813</v>
+        <v>100820</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1869,32 +1869,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128493913</v>
+        <v>128493919</v>
       </c>
       <c r="B14" t="n">
-        <v>96114</v>
+        <v>92812</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2170</v>
+        <v>4368</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1904,10 +1904,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>631960</v>
+        <v>631760</v>
       </c>
       <c r="R14" t="n">
-        <v>6661631</v>
+        <v>6661857</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1966,32 +1966,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128493919</v>
+        <v>128493913</v>
       </c>
       <c r="B15" t="n">
-        <v>92807</v>
+        <v>96121</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4368</v>
+        <v>2170</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2001,10 +2001,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>631760</v>
+        <v>631960</v>
       </c>
       <c r="R15" t="n">
-        <v>6661857</v>
+        <v>6661631</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2063,32 +2063,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128493882</v>
+        <v>128493914</v>
       </c>
       <c r="B16" t="n">
-        <v>91519</v>
+        <v>96121</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5442</v>
+        <v>2170</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2098,10 +2098,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>631713</v>
+        <v>632016</v>
       </c>
       <c r="R16" t="n">
-        <v>6661819</v>
+        <v>6661935</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2160,45 +2160,49 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128493914</v>
+        <v>128493894</v>
       </c>
       <c r="B17" t="n">
-        <v>96114</v>
+        <v>98632</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2170</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>632016</v>
+        <v>631994</v>
       </c>
       <c r="R17" t="n">
-        <v>6661935</v>
+        <v>6661866</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2233,12 +2237,18 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>mer än 40 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2260,7 +2270,7 @@
         <v>128493902</v>
       </c>
       <c r="B18" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2364,49 +2374,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128493894</v>
+        <v>128493882</v>
       </c>
       <c r="B19" t="n">
-        <v>98625</v>
+        <v>91524</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>631994</v>
+        <v>631713</v>
       </c>
       <c r="R19" t="n">
-        <v>6661866</v>
+        <v>6661819</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2441,18 +2447,12 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>mer än 40 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2474,7 +2474,7 @@
         <v>128493892</v>
       </c>
       <c r="B20" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2578,32 +2578,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128493879</v>
+        <v>128493884</v>
       </c>
       <c r="B21" t="n">
-        <v>91499</v>
+        <v>80185</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2613,10 +2613,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>631703</v>
+        <v>631861</v>
       </c>
       <c r="R21" t="n">
-        <v>6661853</v>
+        <v>6661676</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2675,32 +2675,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128493884</v>
+        <v>128493879</v>
       </c>
       <c r="B22" t="n">
-        <v>80185</v>
+        <v>91504</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2710,10 +2710,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>631861</v>
+        <v>631703</v>
       </c>
       <c r="R22" t="n">
-        <v>6661676</v>
+        <v>6661853</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2872,7 +2872,7 @@
         <v>128493871</v>
       </c>
       <c r="B24" t="n">
-        <v>101718</v>
+        <v>101725</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>128493905</v>
       </c>
       <c r="B25" t="n">
-        <v>92264</v>
+        <v>92269</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3063,32 +3063,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128493872</v>
+        <v>128493906</v>
       </c>
       <c r="B26" t="n">
-        <v>96871</v>
+        <v>105695</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>53</v>
+        <v>221144</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3098,10 +3098,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>632001</v>
+        <v>631754</v>
       </c>
       <c r="R26" t="n">
-        <v>6661954</v>
+        <v>6661814</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3160,10 +3160,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128493876</v>
+        <v>128493872</v>
       </c>
       <c r="B27" t="n">
-        <v>96871</v>
+        <v>96878</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3195,10 +3195,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>631854</v>
+        <v>632001</v>
       </c>
       <c r="R27" t="n">
-        <v>6661710</v>
+        <v>6661954</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3257,32 +3257,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128493906</v>
+        <v>128493876</v>
       </c>
       <c r="B28" t="n">
-        <v>105688</v>
+        <v>96878</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221144</v>
+        <v>53</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3292,10 +3292,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>631754</v>
+        <v>631854</v>
       </c>
       <c r="R28" t="n">
-        <v>6661814</v>
+        <v>6661710</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3454,7 +3454,7 @@
         <v>128493890</v>
       </c>
       <c r="B30" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3558,10 +3558,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128493874</v>
+        <v>128493918</v>
       </c>
       <c r="B31" t="n">
-        <v>96871</v>
+        <v>92812</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3569,21 +3569,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>53</v>
+        <v>4368</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3593,10 +3593,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>631878</v>
+        <v>631638</v>
       </c>
       <c r="R31" t="n">
-        <v>6661711</v>
+        <v>6661884</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3655,10 +3655,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128493918</v>
+        <v>128493874</v>
       </c>
       <c r="B32" t="n">
-        <v>92807</v>
+        <v>96878</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3666,21 +3666,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4368</v>
+        <v>53</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3690,10 +3690,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>631638</v>
+        <v>631878</v>
       </c>
       <c r="R32" t="n">
-        <v>6661884</v>
+        <v>6661711</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3755,7 +3755,7 @@
         <v>128493873</v>
       </c>
       <c r="B33" t="n">
-        <v>96871</v>
+        <v>96878</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3849,32 +3849,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128493897</v>
+        <v>128493907</v>
       </c>
       <c r="B34" t="n">
-        <v>98625</v>
+        <v>105695</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3884,10 +3884,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>631658</v>
+        <v>631741</v>
       </c>
       <c r="R34" t="n">
-        <v>6661890</v>
+        <v>6661845</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -3924,7 +3924,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ett fåtal bladrosetter</t>
+          <t>Mer än 20 bladrosetter</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3951,32 +3951,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128493907</v>
+        <v>128493897</v>
       </c>
       <c r="B35" t="n">
-        <v>105688</v>
+        <v>98632</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3986,10 +3986,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>631741</v>
+        <v>631658</v>
       </c>
       <c r="R35" t="n">
-        <v>6661845</v>
+        <v>6661890</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4026,7 +4026,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Mer än 20 bladrosetter</t>
+          <t>Ett fåtal bladrosetter</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4056,7 +4056,7 @@
         <v>128493896</v>
       </c>
       <c r="B36" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>128493903</v>
       </c>
       <c r="B37" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4262,45 +4262,49 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128493878</v>
+        <v>128493895</v>
       </c>
       <c r="B38" t="n">
-        <v>96871</v>
+        <v>98632</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>631686</v>
+        <v>631908</v>
       </c>
       <c r="R38" t="n">
-        <v>6661895</v>
+        <v>6661782</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4335,12 +4339,18 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Mer än 50  bladrosetter</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4362,7 +4372,7 @@
         <v>128493917</v>
       </c>
       <c r="B39" t="n">
-        <v>92807</v>
+        <v>92812</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4460,49 +4470,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128493895</v>
+        <v>128493878</v>
       </c>
       <c r="B40" t="n">
-        <v>98625</v>
+        <v>96878</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>631908</v>
+        <v>631686</v>
       </c>
       <c r="R40" t="n">
-        <v>6661782</v>
+        <v>6661895</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4537,18 +4543,12 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Mer än 50  bladrosetter</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4570,7 +4570,7 @@
         <v>128493916</v>
       </c>
       <c r="B41" t="n">
-        <v>92801</v>
+        <v>92806</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4671,7 +4671,7 @@
         <v>128792098</v>
       </c>
       <c r="B42" t="n">
-        <v>91464</v>
+        <v>91469</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4768,7 +4768,7 @@
         <v>128792102</v>
       </c>
       <c r="B43" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4867,32 +4867,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128792106</v>
+        <v>128792112</v>
       </c>
       <c r="B44" t="n">
-        <v>96067</v>
+        <v>92812</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>210</v>
+        <v>4368</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4902,10 +4902,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>631759</v>
+        <v>631814</v>
       </c>
       <c r="R44" t="n">
-        <v>6661865</v>
+        <v>6661721</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4938,11 +4938,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>30 kapslar</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4969,32 +4964,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128792112</v>
+        <v>128792106</v>
       </c>
       <c r="B45" t="n">
-        <v>92807</v>
+        <v>96074</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4368</v>
+        <v>210</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5004,10 +4999,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>631814</v>
+        <v>631759</v>
       </c>
       <c r="R45" t="n">
-        <v>6661721</v>
+        <v>6661865</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5040,6 +5035,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>30 kapslar</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5069,7 +5069,7 @@
         <v>128792097</v>
       </c>
       <c r="B46" t="n">
-        <v>96871</v>
+        <v>96878</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5166,7 +5166,7 @@
         <v>128792111</v>
       </c>
       <c r="B47" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         <v>128792108</v>
       </c>
       <c r="B48" t="n">
-        <v>91517</v>
+        <v>91522</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5361,32 +5361,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128792104</v>
+        <v>128792114</v>
       </c>
       <c r="B49" t="n">
-        <v>92791</v>
+        <v>100820</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>788</v>
+        <v>222498</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5396,10 +5396,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>631748</v>
+        <v>631859</v>
       </c>
       <c r="R49" t="n">
-        <v>6661858</v>
+        <v>6661778</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5458,32 +5458,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128792114</v>
+        <v>128792104</v>
       </c>
       <c r="B50" t="n">
-        <v>100813</v>
+        <v>92796</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222498</v>
+        <v>788</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5493,10 +5493,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>631859</v>
+        <v>631748</v>
       </c>
       <c r="R50" t="n">
-        <v>6661778</v>
+        <v>6661858</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5655,7 +5655,7 @@
         <v>128792110</v>
       </c>
       <c r="B52" t="n">
-        <v>96114</v>
+        <v>96121</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5752,7 +5752,7 @@
         <v>128792113</v>
       </c>
       <c r="B53" t="n">
-        <v>100813</v>
+        <v>100820</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 41611-2025 artfynd.xlsx
+++ b/artfynd/A 41611-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128493904</v>
+        <v>128493883</v>
       </c>
       <c r="B2" t="n">
-        <v>98632</v>
+        <v>80260</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>631707</v>
+        <v>631861</v>
       </c>
       <c r="R2" t="n">
-        <v>6661837</v>
+        <v>6661676</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>12 bladrosetter</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128493901</v>
+        <v>128493904</v>
       </c>
       <c r="B3" t="n">
         <v>98632</v>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>632054</v>
+        <v>631707</v>
       </c>
       <c r="R3" t="n">
-        <v>6661938</v>
+        <v>6661837</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -852,7 +847,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Mer än 10 bladrosetter</t>
+          <t>12 bladrosetter</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,32 +874,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128493877</v>
+        <v>128493901</v>
       </c>
       <c r="B4" t="n">
-        <v>96878</v>
+        <v>98632</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>631706</v>
+        <v>632054</v>
       </c>
       <c r="R4" t="n">
-        <v>6661848</v>
+        <v>6661938</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -950,6 +945,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Mer än 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,32 +976,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128493883</v>
+        <v>128493877</v>
       </c>
       <c r="B5" t="n">
-        <v>80260</v>
+        <v>96878</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6463</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>631861</v>
+        <v>631706</v>
       </c>
       <c r="R5" t="n">
-        <v>6661676</v>
+        <v>6661848</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1869,32 +1869,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128493919</v>
+        <v>128493913</v>
       </c>
       <c r="B14" t="n">
-        <v>92812</v>
+        <v>96121</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4368</v>
+        <v>2170</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1904,10 +1904,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>631760</v>
+        <v>631960</v>
       </c>
       <c r="R14" t="n">
-        <v>6661857</v>
+        <v>6661631</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1966,32 +1966,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128493913</v>
+        <v>128493919</v>
       </c>
       <c r="B15" t="n">
-        <v>96121</v>
+        <v>92812</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2170</v>
+        <v>4368</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2001,10 +2001,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>631960</v>
+        <v>631760</v>
       </c>
       <c r="R15" t="n">
-        <v>6661631</v>
+        <v>6661857</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2063,32 +2063,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128493914</v>
+        <v>128493882</v>
       </c>
       <c r="B16" t="n">
-        <v>96121</v>
+        <v>91524</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2170</v>
+        <v>5442</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2098,10 +2098,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>632016</v>
+        <v>631713</v>
       </c>
       <c r="R16" t="n">
-        <v>6661935</v>
+        <v>6661819</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2160,49 +2160,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128493894</v>
+        <v>128493914</v>
       </c>
       <c r="B17" t="n">
-        <v>98632</v>
+        <v>96121</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>2170</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>631994</v>
+        <v>632016</v>
       </c>
       <c r="R17" t="n">
-        <v>6661866</v>
+        <v>6661935</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2237,18 +2233,12 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>mer än 40 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2374,45 +2364,49 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128493882</v>
+        <v>128493894</v>
       </c>
       <c r="B19" t="n">
-        <v>91524</v>
+        <v>98632</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>631713</v>
+        <v>631994</v>
       </c>
       <c r="R19" t="n">
-        <v>6661819</v>
+        <v>6661866</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2447,12 +2441,18 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>mer än 40 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2772,32 +2772,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128493885</v>
+        <v>128493871</v>
       </c>
       <c r="B23" t="n">
-        <v>57713</v>
+        <v>101725</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>221235</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2807,10 +2807,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>631983</v>
+        <v>631816</v>
       </c>
       <c r="R23" t="n">
-        <v>6661724</v>
+        <v>6661751</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2869,32 +2869,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128493871</v>
+        <v>128493885</v>
       </c>
       <c r="B24" t="n">
-        <v>101725</v>
+        <v>57713</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221235</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2904,10 +2904,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>631816</v>
+        <v>631983</v>
       </c>
       <c r="R24" t="n">
-        <v>6661751</v>
+        <v>6661724</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -4262,49 +4262,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128493895</v>
+        <v>128493878</v>
       </c>
       <c r="B38" t="n">
-        <v>98632</v>
+        <v>96878</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>631908</v>
+        <v>631686</v>
       </c>
       <c r="R38" t="n">
-        <v>6661782</v>
+        <v>6661895</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4339,18 +4335,12 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Mer än 50  bladrosetter</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4369,37 +4359,38 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128493917</v>
+        <v>128493895</v>
       </c>
       <c r="B39" t="n">
-        <v>92812</v>
+        <v>98632</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4368</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4407,10 +4398,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>631806</v>
+        <v>631908</v>
       </c>
       <c r="R39" t="n">
-        <v>6661784</v>
+        <v>6661782</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4443,6 +4434,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Mer än 50  bladrosetter</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4470,10 +4466,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128493878</v>
+        <v>128493917</v>
       </c>
       <c r="B40" t="n">
-        <v>96878</v>
+        <v>92812</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4481,34 +4477,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>53</v>
+        <v>4368</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>631686</v>
+        <v>631806</v>
       </c>
       <c r="R40" t="n">
-        <v>6661895</v>
+        <v>6661784</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4549,6 +4548,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4867,32 +4867,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128792112</v>
+        <v>128792106</v>
       </c>
       <c r="B44" t="n">
-        <v>92812</v>
+        <v>96074</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4368</v>
+        <v>210</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4902,10 +4902,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>631814</v>
+        <v>631759</v>
       </c>
       <c r="R44" t="n">
-        <v>6661721</v>
+        <v>6661865</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4938,6 +4938,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>30 kapslar</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4964,32 +4969,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128792106</v>
+        <v>128792112</v>
       </c>
       <c r="B45" t="n">
-        <v>96074</v>
+        <v>92812</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>210</v>
+        <v>4368</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4999,10 +5004,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>631759</v>
+        <v>631814</v>
       </c>
       <c r="R45" t="n">
-        <v>6661865</v>
+        <v>6661721</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5035,11 +5040,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>30 kapslar</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5361,32 +5361,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128792114</v>
+        <v>128792104</v>
       </c>
       <c r="B49" t="n">
-        <v>100820</v>
+        <v>92796</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>222498</v>
+        <v>788</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5396,10 +5396,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>631859</v>
+        <v>631748</v>
       </c>
       <c r="R49" t="n">
-        <v>6661778</v>
+        <v>6661858</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5458,32 +5458,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128792104</v>
+        <v>128792093</v>
       </c>
       <c r="B50" t="n">
-        <v>92796</v>
+        <v>5197</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>788</v>
+        <v>105930</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5493,10 +5493,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>631748</v>
+        <v>631577</v>
       </c>
       <c r="R50" t="n">
-        <v>6661858</v>
+        <v>6661796</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5555,10 +5555,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128792093</v>
+        <v>128792114</v>
       </c>
       <c r="B51" t="n">
-        <v>5197</v>
+        <v>100820</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5566,21 +5566,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5590,10 +5590,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>631577</v>
+        <v>631859</v>
       </c>
       <c r="R51" t="n">
-        <v>6661796</v>
+        <v>6661778</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>

--- a/artfynd/A 41611-2025 artfynd.xlsx
+++ b/artfynd/A 41611-2025 artfynd.xlsx
@@ -1471,32 +1471,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128493915</v>
+        <v>128493875</v>
       </c>
       <c r="B10" t="n">
-        <v>96121</v>
+        <v>96878</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2170</v>
+        <v>53</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>631915</v>
+        <v>631869</v>
       </c>
       <c r="R10" t="n">
-        <v>6661808</v>
+        <v>6661711</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1568,45 +1568,49 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128493875</v>
+        <v>128493893</v>
       </c>
       <c r="B11" t="n">
-        <v>96878</v>
+        <v>98632</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>631869</v>
+        <v>632068</v>
       </c>
       <c r="R11" t="n">
-        <v>6661711</v>
+        <v>6661949</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1641,12 +1645,18 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ca 20 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1665,49 +1675,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128493893</v>
+        <v>128493915</v>
       </c>
       <c r="B12" t="n">
-        <v>98632</v>
+        <v>96121</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>2170</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>632068</v>
+        <v>631915</v>
       </c>
       <c r="R12" t="n">
-        <v>6661949</v>
+        <v>6661808</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1742,18 +1748,12 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ca 20 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2578,32 +2578,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128493884</v>
+        <v>128493879</v>
       </c>
       <c r="B21" t="n">
-        <v>80185</v>
+        <v>91504</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2613,10 +2613,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>631861</v>
+        <v>631703</v>
       </c>
       <c r="R21" t="n">
-        <v>6661676</v>
+        <v>6661853</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2675,32 +2675,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128493879</v>
+        <v>128493884</v>
       </c>
       <c r="B22" t="n">
-        <v>91504</v>
+        <v>80185</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2710,10 +2710,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>631703</v>
+        <v>631861</v>
       </c>
       <c r="R22" t="n">
-        <v>6661853</v>
+        <v>6661676</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -4262,45 +4262,49 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128493878</v>
+        <v>128493895</v>
       </c>
       <c r="B38" t="n">
-        <v>96878</v>
+        <v>98632</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>631686</v>
+        <v>631908</v>
       </c>
       <c r="R38" t="n">
-        <v>6661895</v>
+        <v>6661782</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4335,12 +4339,18 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Mer än 50  bladrosetter</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4359,38 +4369,37 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128493895</v>
+        <v>128493917</v>
       </c>
       <c r="B39" t="n">
-        <v>98632</v>
+        <v>92812</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>4368</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4398,10 +4407,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>631908</v>
+        <v>631806</v>
       </c>
       <c r="R39" t="n">
-        <v>6661782</v>
+        <v>6661784</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4434,11 +4443,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Mer än 50  bladrosetter</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4466,10 +4470,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128493917</v>
+        <v>128493878</v>
       </c>
       <c r="B40" t="n">
-        <v>92812</v>
+        <v>96878</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4477,37 +4481,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4368</v>
+        <v>53</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>631806</v>
+        <v>631686</v>
       </c>
       <c r="R40" t="n">
-        <v>6661784</v>
+        <v>6661895</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4548,7 +4549,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4867,32 +4867,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128792106</v>
+        <v>128792112</v>
       </c>
       <c r="B44" t="n">
-        <v>96074</v>
+        <v>92812</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>210</v>
+        <v>4368</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4902,10 +4902,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>631759</v>
+        <v>631814</v>
       </c>
       <c r="R44" t="n">
-        <v>6661865</v>
+        <v>6661721</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4938,11 +4938,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>30 kapslar</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4969,32 +4964,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128792112</v>
+        <v>128792106</v>
       </c>
       <c r="B45" t="n">
-        <v>92812</v>
+        <v>96074</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4368</v>
+        <v>210</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5004,10 +4999,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>631814</v>
+        <v>631759</v>
       </c>
       <c r="R45" t="n">
-        <v>6661721</v>
+        <v>6661865</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5040,6 +5035,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>30 kapslar</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5458,10 +5458,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128792093</v>
+        <v>128792114</v>
       </c>
       <c r="B50" t="n">
-        <v>5197</v>
+        <v>100820</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5469,21 +5469,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5493,10 +5493,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>631577</v>
+        <v>631859</v>
       </c>
       <c r="R50" t="n">
-        <v>6661796</v>
+        <v>6661778</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5555,10 +5555,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128792114</v>
+        <v>128792093</v>
       </c>
       <c r="B51" t="n">
-        <v>100820</v>
+        <v>5197</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5566,21 +5566,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5590,10 +5590,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>631859</v>
+        <v>631577</v>
       </c>
       <c r="R51" t="n">
-        <v>6661778</v>
+        <v>6661796</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>

--- a/artfynd/A 41611-2025 artfynd.xlsx
+++ b/artfynd/A 41611-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128493883</v>
+        <v>128493904</v>
       </c>
       <c r="B2" t="n">
-        <v>80260</v>
+        <v>98636</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>631861</v>
+        <v>631707</v>
       </c>
       <c r="R2" t="n">
-        <v>6661676</v>
+        <v>6661837</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>12 bladrosetter</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,32 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128493904</v>
+        <v>128493883</v>
       </c>
       <c r="B3" t="n">
-        <v>98632</v>
+        <v>80264</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>631707</v>
+        <v>631861</v>
       </c>
       <c r="R3" t="n">
-        <v>6661837</v>
+        <v>6661676</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -843,11 +848,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>12 bladrosetter</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,7 +877,7 @@
         <v>128493901</v>
       </c>
       <c r="B4" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>128493877</v>
       </c>
       <c r="B5" t="n">
-        <v>96878</v>
+        <v>96882</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>128493909</v>
       </c>
       <c r="B6" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>128493898</v>
       </c>
       <c r="B7" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>128493899</v>
       </c>
       <c r="B8" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>128493900</v>
       </c>
       <c r="B9" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>128493875</v>
       </c>
       <c r="B10" t="n">
-        <v>96878</v>
+        <v>96882</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1568,49 +1568,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128493893</v>
+        <v>128493915</v>
       </c>
       <c r="B11" t="n">
-        <v>98632</v>
+        <v>96125</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>2170</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>632068</v>
+        <v>631915</v>
       </c>
       <c r="R11" t="n">
-        <v>6661949</v>
+        <v>6661808</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1645,18 +1641,12 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ca 20 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1675,45 +1665,49 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128493915</v>
+        <v>128493893</v>
       </c>
       <c r="B12" t="n">
-        <v>96121</v>
+        <v>98636</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2170</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>631915</v>
+        <v>632068</v>
       </c>
       <c r="R12" t="n">
-        <v>6661808</v>
+        <v>6661949</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1748,12 +1742,18 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ca 20 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1775,7 +1775,7 @@
         <v>128493920</v>
       </c>
       <c r="B13" t="n">
-        <v>100820</v>
+        <v>100824</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>128493913</v>
       </c>
       <c r="B14" t="n">
-        <v>96121</v>
+        <v>96125</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>128493919</v>
       </c>
       <c r="B15" t="n">
-        <v>92812</v>
+        <v>92816</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2063,32 +2063,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128493882</v>
+        <v>128493914</v>
       </c>
       <c r="B16" t="n">
-        <v>91524</v>
+        <v>96125</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5442</v>
+        <v>2170</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2098,10 +2098,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>631713</v>
+        <v>632016</v>
       </c>
       <c r="R16" t="n">
-        <v>6661819</v>
+        <v>6661935</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2160,32 +2160,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128493914</v>
+        <v>128493882</v>
       </c>
       <c r="B17" t="n">
-        <v>96121</v>
+        <v>91528</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2170</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2195,10 +2195,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>632016</v>
+        <v>631713</v>
       </c>
       <c r="R17" t="n">
-        <v>6661935</v>
+        <v>6661819</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2260,7 +2260,7 @@
         <v>128493902</v>
       </c>
       <c r="B18" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>128493894</v>
       </c>
       <c r="B19" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>128493892</v>
       </c>
       <c r="B20" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2578,32 +2578,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128493879</v>
+        <v>128493884</v>
       </c>
       <c r="B21" t="n">
-        <v>91504</v>
+        <v>80189</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2613,10 +2613,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>631703</v>
+        <v>631861</v>
       </c>
       <c r="R21" t="n">
-        <v>6661853</v>
+        <v>6661676</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2675,32 +2675,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128493884</v>
+        <v>128493879</v>
       </c>
       <c r="B22" t="n">
-        <v>80185</v>
+        <v>91508</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2710,10 +2710,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>631861</v>
+        <v>631703</v>
       </c>
       <c r="R22" t="n">
-        <v>6661676</v>
+        <v>6661853</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2772,32 +2772,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128493871</v>
+        <v>128493885</v>
       </c>
       <c r="B23" t="n">
-        <v>101725</v>
+        <v>57717</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221235</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2807,10 +2807,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>631816</v>
+        <v>631983</v>
       </c>
       <c r="R23" t="n">
-        <v>6661751</v>
+        <v>6661724</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2869,32 +2869,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128493885</v>
+        <v>128493871</v>
       </c>
       <c r="B24" t="n">
-        <v>57713</v>
+        <v>101729</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>221235</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2904,10 +2904,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>631983</v>
+        <v>631816</v>
       </c>
       <c r="R24" t="n">
-        <v>6661724</v>
+        <v>6661751</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2969,7 +2969,7 @@
         <v>128493905</v>
       </c>
       <c r="B25" t="n">
-        <v>92269</v>
+        <v>92273</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3063,32 +3063,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128493906</v>
+        <v>128493872</v>
       </c>
       <c r="B26" t="n">
-        <v>105695</v>
+        <v>96882</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221144</v>
+        <v>53</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3098,10 +3098,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>631754</v>
+        <v>632001</v>
       </c>
       <c r="R26" t="n">
-        <v>6661814</v>
+        <v>6661954</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3160,10 +3160,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128493872</v>
+        <v>128493876</v>
       </c>
       <c r="B27" t="n">
-        <v>96878</v>
+        <v>96882</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3195,10 +3195,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>632001</v>
+        <v>631854</v>
       </c>
       <c r="R27" t="n">
-        <v>6661954</v>
+        <v>6661710</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3257,32 +3257,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128493876</v>
+        <v>128493906</v>
       </c>
       <c r="B28" t="n">
-        <v>96878</v>
+        <v>105699</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>53</v>
+        <v>221144</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3292,10 +3292,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>631854</v>
+        <v>631754</v>
       </c>
       <c r="R28" t="n">
-        <v>6661710</v>
+        <v>6661814</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3357,7 +3357,7 @@
         <v>128493881</v>
       </c>
       <c r="B29" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
         <v>128493890</v>
       </c>
       <c r="B30" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3558,10 +3558,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128493918</v>
+        <v>128493874</v>
       </c>
       <c r="B31" t="n">
-        <v>92812</v>
+        <v>96882</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3569,21 +3569,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4368</v>
+        <v>53</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3593,10 +3593,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>631638</v>
+        <v>631878</v>
       </c>
       <c r="R31" t="n">
-        <v>6661884</v>
+        <v>6661711</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3655,10 +3655,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128493874</v>
+        <v>128493918</v>
       </c>
       <c r="B32" t="n">
-        <v>96878</v>
+        <v>92816</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3666,21 +3666,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>53</v>
+        <v>4368</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3690,10 +3690,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>631878</v>
+        <v>631638</v>
       </c>
       <c r="R32" t="n">
-        <v>6661711</v>
+        <v>6661884</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3755,7 +3755,7 @@
         <v>128493873</v>
       </c>
       <c r="B33" t="n">
-        <v>96878</v>
+        <v>96882</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>128493907</v>
       </c>
       <c r="B34" t="n">
-        <v>105695</v>
+        <v>105699</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>128493897</v>
       </c>
       <c r="B35" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         <v>128493896</v>
       </c>
       <c r="B36" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>128493903</v>
       </c>
       <c r="B37" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4262,38 +4262,37 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128493895</v>
+        <v>128493917</v>
       </c>
       <c r="B38" t="n">
-        <v>98632</v>
+        <v>92816</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>4368</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4301,10 +4300,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>631908</v>
+        <v>631806</v>
       </c>
       <c r="R38" t="n">
-        <v>6661782</v>
+        <v>6661784</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4337,11 +4336,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Mer än 50  bladrosetter</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4369,37 +4363,38 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128493917</v>
+        <v>128493895</v>
       </c>
       <c r="B39" t="n">
-        <v>92812</v>
+        <v>98636</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4368</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4407,10 +4402,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>631806</v>
+        <v>631908</v>
       </c>
       <c r="R39" t="n">
-        <v>6661784</v>
+        <v>6661782</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4443,6 +4438,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Mer än 50  bladrosetter</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4473,7 +4473,7 @@
         <v>128493878</v>
       </c>
       <c r="B40" t="n">
-        <v>96878</v>
+        <v>96882</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
         <v>128493916</v>
       </c>
       <c r="B41" t="n">
-        <v>92806</v>
+        <v>92810</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4671,7 +4671,7 @@
         <v>128792098</v>
       </c>
       <c r="B42" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4768,7 +4768,7 @@
         <v>128792102</v>
       </c>
       <c r="B43" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>128792112</v>
       </c>
       <c r="B44" t="n">
-        <v>92812</v>
+        <v>92816</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4967,7 +4967,7 @@
         <v>128792106</v>
       </c>
       <c r="B45" t="n">
-        <v>96074</v>
+        <v>96078</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5069,7 +5069,7 @@
         <v>128792097</v>
       </c>
       <c r="B46" t="n">
-        <v>96878</v>
+        <v>96882</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5166,7 +5166,7 @@
         <v>128792111</v>
       </c>
       <c r="B47" t="n">
-        <v>92830</v>
+        <v>92834</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         <v>128792108</v>
       </c>
       <c r="B48" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5361,32 +5361,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128792104</v>
+        <v>128792093</v>
       </c>
       <c r="B49" t="n">
-        <v>92796</v>
+        <v>5197</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>788</v>
+        <v>105930</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5396,10 +5396,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>631748</v>
+        <v>631577</v>
       </c>
       <c r="R49" t="n">
-        <v>6661858</v>
+        <v>6661796</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5458,32 +5458,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128792114</v>
+        <v>128792104</v>
       </c>
       <c r="B50" t="n">
-        <v>100820</v>
+        <v>92800</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222498</v>
+        <v>788</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5493,10 +5493,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>631859</v>
+        <v>631748</v>
       </c>
       <c r="R50" t="n">
-        <v>6661778</v>
+        <v>6661858</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5555,10 +5555,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128792093</v>
+        <v>128792114</v>
       </c>
       <c r="B51" t="n">
-        <v>5197</v>
+        <v>100824</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5566,21 +5566,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5590,10 +5590,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>631577</v>
+        <v>631859</v>
       </c>
       <c r="R51" t="n">
-        <v>6661796</v>
+        <v>6661778</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5655,7 +5655,7 @@
         <v>128792110</v>
       </c>
       <c r="B52" t="n">
-        <v>96121</v>
+        <v>96125</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5752,7 +5752,7 @@
         <v>128792113</v>
       </c>
       <c r="B53" t="n">
-        <v>100820</v>
+        <v>100824</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 41611-2025 artfynd.xlsx
+++ b/artfynd/A 41611-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128493904</v>
+        <v>128493877</v>
       </c>
       <c r="B2" t="n">
-        <v>98636</v>
+        <v>96882</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>631707</v>
+        <v>631706</v>
       </c>
       <c r="R2" t="n">
-        <v>6661837</v>
+        <v>6661848</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>12 bladrosetter</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -874,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128493901</v>
+        <v>128493904</v>
       </c>
       <c r="B4" t="n">
         <v>98636</v>
@@ -909,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>632054</v>
+        <v>631707</v>
       </c>
       <c r="R4" t="n">
-        <v>6661938</v>
+        <v>6661837</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -949,7 +944,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Mer än 10 bladrosetter</t>
+          <t>12 bladrosetter</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,32 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128493877</v>
+        <v>128493901</v>
       </c>
       <c r="B5" t="n">
-        <v>96882</v>
+        <v>98636</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>631706</v>
+        <v>632054</v>
       </c>
       <c r="R5" t="n">
-        <v>6661848</v>
+        <v>6661938</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1047,6 +1042,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Mer än 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1170,7 +1170,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128493898</v>
+        <v>128493899</v>
       </c>
       <c r="B7" t="n">
         <v>98636</v>
@@ -1199,17 +1199,13 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>631979</v>
+        <v>631997</v>
       </c>
       <c r="R7" t="n">
         <v>6661713</v>
@@ -1247,18 +1243,12 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Mer än 30 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1277,7 +1267,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128493899</v>
+        <v>128493900</v>
       </c>
       <c r="B8" t="n">
         <v>98636</v>
@@ -1312,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>631997</v>
+        <v>632030</v>
       </c>
       <c r="R8" t="n">
-        <v>6661713</v>
+        <v>6661779</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1374,7 +1364,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128493900</v>
+        <v>128493898</v>
       </c>
       <c r="B9" t="n">
         <v>98636</v>
@@ -1403,16 +1393,20 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>632030</v>
+        <v>631979</v>
       </c>
       <c r="R9" t="n">
-        <v>6661779</v>
+        <v>6661713</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1447,12 +1441,18 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Mer än 30 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1471,45 +1471,49 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128493875</v>
+        <v>128493893</v>
       </c>
       <c r="B10" t="n">
-        <v>96882</v>
+        <v>98636</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>631869</v>
+        <v>632068</v>
       </c>
       <c r="R10" t="n">
-        <v>6661711</v>
+        <v>6661949</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1544,12 +1548,18 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ca 20 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1665,49 +1675,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128493893</v>
+        <v>128493875</v>
       </c>
       <c r="B12" t="n">
-        <v>98636</v>
+        <v>96882</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>632068</v>
+        <v>631869</v>
       </c>
       <c r="R12" t="n">
-        <v>6661949</v>
+        <v>6661711</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1742,18 +1748,12 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ca 20 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2160,45 +2160,49 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128493882</v>
+        <v>128493902</v>
       </c>
       <c r="B17" t="n">
-        <v>91528</v>
+        <v>98636</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>631713</v>
+        <v>632008</v>
       </c>
       <c r="R17" t="n">
-        <v>6661819</v>
+        <v>6661933</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2233,12 +2237,18 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>mer än 40 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2257,7 +2267,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128493902</v>
+        <v>128493894</v>
       </c>
       <c r="B18" t="n">
         <v>98636</v>
@@ -2296,10 +2306,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>632008</v>
+        <v>631994</v>
       </c>
       <c r="R18" t="n">
-        <v>6661933</v>
+        <v>6661866</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2364,49 +2374,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128493894</v>
+        <v>128493882</v>
       </c>
       <c r="B19" t="n">
-        <v>98636</v>
+        <v>91528</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>631994</v>
+        <v>631713</v>
       </c>
       <c r="R19" t="n">
-        <v>6661866</v>
+        <v>6661819</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2441,18 +2447,12 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>mer än 40 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2772,32 +2772,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128493885</v>
+        <v>128493871</v>
       </c>
       <c r="B23" t="n">
-        <v>57717</v>
+        <v>101729</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>221235</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2807,10 +2807,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>631983</v>
+        <v>631816</v>
       </c>
       <c r="R23" t="n">
-        <v>6661724</v>
+        <v>6661751</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2869,32 +2869,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128493871</v>
+        <v>128493885</v>
       </c>
       <c r="B24" t="n">
-        <v>101729</v>
+        <v>57717</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221235</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2904,10 +2904,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>631816</v>
+        <v>631983</v>
       </c>
       <c r="R24" t="n">
-        <v>6661751</v>
+        <v>6661724</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3558,10 +3558,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128493874</v>
+        <v>128493918</v>
       </c>
       <c r="B31" t="n">
-        <v>96882</v>
+        <v>92816</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3569,21 +3569,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>53</v>
+        <v>4368</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3593,10 +3593,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>631878</v>
+        <v>631638</v>
       </c>
       <c r="R31" t="n">
-        <v>6661711</v>
+        <v>6661884</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3655,10 +3655,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128493918</v>
+        <v>128493874</v>
       </c>
       <c r="B32" t="n">
-        <v>92816</v>
+        <v>96882</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3666,21 +3666,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4368</v>
+        <v>53</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3690,10 +3690,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>631638</v>
+        <v>631878</v>
       </c>
       <c r="R32" t="n">
-        <v>6661884</v>
+        <v>6661711</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4262,10 +4262,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128493917</v>
+        <v>128493878</v>
       </c>
       <c r="B38" t="n">
-        <v>92816</v>
+        <v>96882</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4273,37 +4273,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4368</v>
+        <v>53</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>631806</v>
+        <v>631686</v>
       </c>
       <c r="R38" t="n">
-        <v>6661784</v>
+        <v>6661895</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4344,7 +4341,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4363,38 +4359,37 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128493895</v>
+        <v>128493917</v>
       </c>
       <c r="B39" t="n">
-        <v>98636</v>
+        <v>92816</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>4368</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4402,10 +4397,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>631908</v>
+        <v>631806</v>
       </c>
       <c r="R39" t="n">
-        <v>6661782</v>
+        <v>6661784</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4438,11 +4433,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Mer än 50  bladrosetter</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4470,45 +4460,49 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128493878</v>
+        <v>128493895</v>
       </c>
       <c r="B40" t="n">
-        <v>96882</v>
+        <v>98636</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>631686</v>
+        <v>631908</v>
       </c>
       <c r="R40" t="n">
-        <v>6661895</v>
+        <v>6661782</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4543,12 +4537,18 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Mer än 50  bladrosetter</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4867,32 +4867,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128792112</v>
+        <v>128792106</v>
       </c>
       <c r="B44" t="n">
-        <v>92816</v>
+        <v>96078</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4368</v>
+        <v>210</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4902,10 +4902,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>631814</v>
+        <v>631759</v>
       </c>
       <c r="R44" t="n">
-        <v>6661721</v>
+        <v>6661865</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4938,6 +4938,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>30 kapslar</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4964,32 +4969,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128792106</v>
+        <v>128792112</v>
       </c>
       <c r="B45" t="n">
-        <v>96078</v>
+        <v>92816</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>210</v>
+        <v>4368</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4999,10 +5004,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>631759</v>
+        <v>631814</v>
       </c>
       <c r="R45" t="n">
-        <v>6661865</v>
+        <v>6661721</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5035,11 +5040,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>30 kapslar</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5361,32 +5361,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128792093</v>
+        <v>128792104</v>
       </c>
       <c r="B49" t="n">
-        <v>5197</v>
+        <v>92800</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>105930</v>
+        <v>788</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5396,10 +5396,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>631577</v>
+        <v>631748</v>
       </c>
       <c r="R49" t="n">
-        <v>6661796</v>
+        <v>6661858</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5458,32 +5458,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128792104</v>
+        <v>128792114</v>
       </c>
       <c r="B50" t="n">
-        <v>92800</v>
+        <v>100824</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>788</v>
+        <v>222498</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5493,10 +5493,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>631748</v>
+        <v>631859</v>
       </c>
       <c r="R50" t="n">
-        <v>6661858</v>
+        <v>6661778</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5555,10 +5555,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128792114</v>
+        <v>128792093</v>
       </c>
       <c r="B51" t="n">
-        <v>100824</v>
+        <v>5197</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5566,21 +5566,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5590,10 +5590,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>631859</v>
+        <v>631577</v>
       </c>
       <c r="R51" t="n">
-        <v>6661778</v>
+        <v>6661796</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>

--- a/artfynd/A 41611-2025 artfynd.xlsx
+++ b/artfynd/A 41611-2025 artfynd.xlsx
@@ -1170,7 +1170,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128493899</v>
+        <v>128493898</v>
       </c>
       <c r="B7" t="n">
         <v>98636</v>
@@ -1199,13 +1199,17 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>631997</v>
+        <v>631979</v>
       </c>
       <c r="R7" t="n">
         <v>6661713</v>
@@ -1243,12 +1247,18 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Mer än 30 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1267,7 +1277,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128493900</v>
+        <v>128493899</v>
       </c>
       <c r="B8" t="n">
         <v>98636</v>
@@ -1302,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>632030</v>
+        <v>631997</v>
       </c>
       <c r="R8" t="n">
-        <v>6661779</v>
+        <v>6661713</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1364,7 +1374,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128493898</v>
+        <v>128493900</v>
       </c>
       <c r="B9" t="n">
         <v>98636</v>
@@ -1393,20 +1403,16 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>631979</v>
+        <v>632030</v>
       </c>
       <c r="R9" t="n">
-        <v>6661713</v>
+        <v>6661779</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1441,18 +1447,12 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Mer än 30 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1471,49 +1471,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128493893</v>
+        <v>128493915</v>
       </c>
       <c r="B10" t="n">
-        <v>98636</v>
+        <v>96125</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>2170</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>632068</v>
+        <v>631915</v>
       </c>
       <c r="R10" t="n">
-        <v>6661949</v>
+        <v>6661808</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1548,18 +1544,12 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ca 20 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1578,45 +1568,49 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128493915</v>
+        <v>128493893</v>
       </c>
       <c r="B11" t="n">
-        <v>96125</v>
+        <v>98636</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2170</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>631915</v>
+        <v>632068</v>
       </c>
       <c r="R11" t="n">
-        <v>6661808</v>
+        <v>6661949</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1651,12 +1645,18 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ca 20 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1869,32 +1869,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128493913</v>
+        <v>128493919</v>
       </c>
       <c r="B14" t="n">
-        <v>96125</v>
+        <v>92816</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2170</v>
+        <v>4368</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1904,10 +1904,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>631960</v>
+        <v>631760</v>
       </c>
       <c r="R14" t="n">
-        <v>6661631</v>
+        <v>6661857</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1966,32 +1966,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128493919</v>
+        <v>128493913</v>
       </c>
       <c r="B15" t="n">
-        <v>92816</v>
+        <v>96125</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4368</v>
+        <v>2170</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2001,10 +2001,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>631760</v>
+        <v>631960</v>
       </c>
       <c r="R15" t="n">
-        <v>6661857</v>
+        <v>6661631</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2063,45 +2063,49 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128493914</v>
+        <v>128493902</v>
       </c>
       <c r="B16" t="n">
-        <v>96125</v>
+        <v>98636</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2170</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>632016</v>
+        <v>632008</v>
       </c>
       <c r="R16" t="n">
-        <v>6661935</v>
+        <v>6661933</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2136,12 +2140,18 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>mer än 40 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2160,7 +2170,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128493902</v>
+        <v>128493894</v>
       </c>
       <c r="B17" t="n">
         <v>98636</v>
@@ -2199,10 +2209,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>632008</v>
+        <v>631994</v>
       </c>
       <c r="R17" t="n">
-        <v>6661933</v>
+        <v>6661866</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2267,49 +2277,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128493894</v>
+        <v>128493914</v>
       </c>
       <c r="B18" t="n">
-        <v>98636</v>
+        <v>96125</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>2170</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>631994</v>
+        <v>632016</v>
       </c>
       <c r="R18" t="n">
-        <v>6661866</v>
+        <v>6661935</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2344,18 +2350,12 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>mer än 40 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2578,32 +2578,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128493884</v>
+        <v>128493879</v>
       </c>
       <c r="B21" t="n">
-        <v>80189</v>
+        <v>91508</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2613,10 +2613,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>631861</v>
+        <v>631703</v>
       </c>
       <c r="R21" t="n">
-        <v>6661676</v>
+        <v>6661853</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2675,32 +2675,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128493879</v>
+        <v>128493884</v>
       </c>
       <c r="B22" t="n">
-        <v>91508</v>
+        <v>80189</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2710,10 +2710,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>631703</v>
+        <v>631861</v>
       </c>
       <c r="R22" t="n">
-        <v>6661853</v>
+        <v>6661676</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3063,32 +3063,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128493872</v>
+        <v>128493906</v>
       </c>
       <c r="B26" t="n">
-        <v>96882</v>
+        <v>105699</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>53</v>
+        <v>221144</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3098,10 +3098,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>632001</v>
+        <v>631754</v>
       </c>
       <c r="R26" t="n">
-        <v>6661954</v>
+        <v>6661814</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3160,7 +3160,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128493876</v>
+        <v>128493872</v>
       </c>
       <c r="B27" t="n">
         <v>96882</v>
@@ -3195,10 +3195,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>631854</v>
+        <v>632001</v>
       </c>
       <c r="R27" t="n">
-        <v>6661710</v>
+        <v>6661954</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3257,32 +3257,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128493906</v>
+        <v>128493876</v>
       </c>
       <c r="B28" t="n">
-        <v>105699</v>
+        <v>96882</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221144</v>
+        <v>53</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3292,10 +3292,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>631754</v>
+        <v>631854</v>
       </c>
       <c r="R28" t="n">
-        <v>6661814</v>
+        <v>6661710</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3558,10 +3558,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128493918</v>
+        <v>128493874</v>
       </c>
       <c r="B31" t="n">
-        <v>92816</v>
+        <v>96882</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3569,21 +3569,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4368</v>
+        <v>53</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3593,10 +3593,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>631638</v>
+        <v>631878</v>
       </c>
       <c r="R31" t="n">
-        <v>6661884</v>
+        <v>6661711</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3655,10 +3655,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128493874</v>
+        <v>128493918</v>
       </c>
       <c r="B32" t="n">
-        <v>96882</v>
+        <v>92816</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3666,21 +3666,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>53</v>
+        <v>4368</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3690,10 +3690,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>631878</v>
+        <v>631638</v>
       </c>
       <c r="R32" t="n">
-        <v>6661711</v>
+        <v>6661884</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3849,32 +3849,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128493907</v>
+        <v>128493897</v>
       </c>
       <c r="B34" t="n">
-        <v>105699</v>
+        <v>98636</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3884,10 +3884,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>631741</v>
+        <v>631658</v>
       </c>
       <c r="R34" t="n">
-        <v>6661845</v>
+        <v>6661890</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -3924,7 +3924,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Mer än 20 bladrosetter</t>
+          <t>Ett fåtal bladrosetter</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3951,32 +3951,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128493897</v>
+        <v>128493907</v>
       </c>
       <c r="B35" t="n">
-        <v>98636</v>
+        <v>105699</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3986,10 +3986,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>631658</v>
+        <v>631741</v>
       </c>
       <c r="R35" t="n">
-        <v>6661890</v>
+        <v>6661845</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4026,7 +4026,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ett fåtal bladrosetter</t>
+          <t>Mer än 20 bladrosetter</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5361,32 +5361,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128792104</v>
+        <v>128792093</v>
       </c>
       <c r="B49" t="n">
-        <v>92800</v>
+        <v>5197</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>788</v>
+        <v>105930</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5396,10 +5396,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>631748</v>
+        <v>631577</v>
       </c>
       <c r="R49" t="n">
-        <v>6661858</v>
+        <v>6661796</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5555,32 +5555,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128792093</v>
+        <v>128792104</v>
       </c>
       <c r="B51" t="n">
-        <v>5197</v>
+        <v>92800</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>105930</v>
+        <v>788</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5590,10 +5590,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>631577</v>
+        <v>631748</v>
       </c>
       <c r="R51" t="n">
-        <v>6661796</v>
+        <v>6661858</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>

--- a/artfynd/A 41611-2025 artfynd.xlsx
+++ b/artfynd/A 41611-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128493877</v>
       </c>
       <c r="B2" t="n">
-        <v>96882</v>
+        <v>96889</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128493883</v>
       </c>
       <c r="B3" t="n">
-        <v>80264</v>
+        <v>80169</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128493904</v>
       </c>
       <c r="B4" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>128493901</v>
       </c>
       <c r="B5" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>128493909</v>
       </c>
       <c r="B6" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1170,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128493898</v>
+        <v>128493899</v>
       </c>
       <c r="B7" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1199,17 +1199,13 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>631979</v>
+        <v>631997</v>
       </c>
       <c r="R7" t="n">
         <v>6661713</v>
@@ -1247,18 +1243,12 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Mer än 30 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1277,10 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128493899</v>
+        <v>128493898</v>
       </c>
       <c r="B8" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1306,13 +1296,17 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>631997</v>
+        <v>631979</v>
       </c>
       <c r="R8" t="n">
         <v>6661713</v>
@@ -1350,12 +1344,18 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Mer än 30 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1377,7 +1377,7 @@
         <v>128493900</v>
       </c>
       <c r="B9" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1471,45 +1471,49 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128493915</v>
+        <v>128493893</v>
       </c>
       <c r="B10" t="n">
-        <v>96125</v>
+        <v>98643</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2170</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>631915</v>
+        <v>632068</v>
       </c>
       <c r="R10" t="n">
-        <v>6661808</v>
+        <v>6661949</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1544,12 +1548,18 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ca 20 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1568,49 +1578,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128493893</v>
+        <v>128493915</v>
       </c>
       <c r="B11" t="n">
-        <v>98636</v>
+        <v>96132</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>2170</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>632068</v>
+        <v>631915</v>
       </c>
       <c r="R11" t="n">
-        <v>6661949</v>
+        <v>6661808</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1645,18 +1651,12 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ca 20 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1678,7 +1678,7 @@
         <v>128493875</v>
       </c>
       <c r="B12" t="n">
-        <v>96882</v>
+        <v>96889</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>128493920</v>
       </c>
       <c r="B13" t="n">
-        <v>100824</v>
+        <v>100831</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1869,32 +1869,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128493919</v>
+        <v>128493913</v>
       </c>
       <c r="B14" t="n">
-        <v>92816</v>
+        <v>96132</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4368</v>
+        <v>2170</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1904,10 +1904,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>631760</v>
+        <v>631960</v>
       </c>
       <c r="R14" t="n">
-        <v>6661857</v>
+        <v>6661631</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1966,32 +1966,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128493913</v>
+        <v>128493919</v>
       </c>
       <c r="B15" t="n">
-        <v>96125</v>
+        <v>92821</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2170</v>
+        <v>4368</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2001,10 +2001,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>631960</v>
+        <v>631760</v>
       </c>
       <c r="R15" t="n">
-        <v>6661631</v>
+        <v>6661857</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2066,7 +2066,7 @@
         <v>128493902</v>
       </c>
       <c r="B16" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>128493894</v>
       </c>
       <c r="B17" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>128493914</v>
       </c>
       <c r="B18" t="n">
-        <v>96125</v>
+        <v>96132</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>128493882</v>
       </c>
       <c r="B19" t="n">
-        <v>91528</v>
+        <v>91533</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>128493892</v>
       </c>
       <c r="B20" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2578,32 +2578,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128493879</v>
+        <v>128493884</v>
       </c>
       <c r="B21" t="n">
-        <v>91508</v>
+        <v>80094</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2613,10 +2613,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>631703</v>
+        <v>631861</v>
       </c>
       <c r="R21" t="n">
-        <v>6661853</v>
+        <v>6661676</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2675,32 +2675,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128493884</v>
+        <v>128493879</v>
       </c>
       <c r="B22" t="n">
-        <v>80189</v>
+        <v>91513</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2710,10 +2710,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>631861</v>
+        <v>631703</v>
       </c>
       <c r="R22" t="n">
-        <v>6661676</v>
+        <v>6661853</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2772,32 +2772,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128493871</v>
+        <v>128493885</v>
       </c>
       <c r="B23" t="n">
-        <v>101729</v>
+        <v>57720</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221235</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2807,10 +2807,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>631816</v>
+        <v>631983</v>
       </c>
       <c r="R23" t="n">
-        <v>6661751</v>
+        <v>6661724</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2869,32 +2869,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128493885</v>
+        <v>128493871</v>
       </c>
       <c r="B24" t="n">
-        <v>57717</v>
+        <v>101736</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>221235</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2904,10 +2904,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>631983</v>
+        <v>631816</v>
       </c>
       <c r="R24" t="n">
-        <v>6661724</v>
+        <v>6661751</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2969,7 +2969,7 @@
         <v>128493905</v>
       </c>
       <c r="B25" t="n">
-        <v>92273</v>
+        <v>92278</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3063,32 +3063,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128493906</v>
+        <v>128493872</v>
       </c>
       <c r="B26" t="n">
-        <v>105699</v>
+        <v>96889</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221144</v>
+        <v>53</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3098,10 +3098,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>631754</v>
+        <v>632001</v>
       </c>
       <c r="R26" t="n">
-        <v>6661814</v>
+        <v>6661954</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3160,10 +3160,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128493872</v>
+        <v>128493876</v>
       </c>
       <c r="B27" t="n">
-        <v>96882</v>
+        <v>96889</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3195,10 +3195,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>632001</v>
+        <v>631854</v>
       </c>
       <c r="R27" t="n">
-        <v>6661954</v>
+        <v>6661710</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3257,32 +3257,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128493876</v>
+        <v>128493906</v>
       </c>
       <c r="B28" t="n">
-        <v>96882</v>
+        <v>105706</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>53</v>
+        <v>221144</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3292,10 +3292,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>631854</v>
+        <v>631754</v>
       </c>
       <c r="R28" t="n">
-        <v>6661710</v>
+        <v>6661814</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3357,7 +3357,7 @@
         <v>128493881</v>
       </c>
       <c r="B29" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
         <v>128493890</v>
       </c>
       <c r="B30" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3558,10 +3558,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128493874</v>
+        <v>128493918</v>
       </c>
       <c r="B31" t="n">
-        <v>96882</v>
+        <v>92821</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3569,21 +3569,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>53</v>
+        <v>4368</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3593,10 +3593,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>631878</v>
+        <v>631638</v>
       </c>
       <c r="R31" t="n">
-        <v>6661711</v>
+        <v>6661884</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3655,10 +3655,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128493918</v>
+        <v>128493874</v>
       </c>
       <c r="B32" t="n">
-        <v>92816</v>
+        <v>96889</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3666,21 +3666,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4368</v>
+        <v>53</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3690,10 +3690,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>631638</v>
+        <v>631878</v>
       </c>
       <c r="R32" t="n">
-        <v>6661884</v>
+        <v>6661711</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3755,7 +3755,7 @@
         <v>128493873</v>
       </c>
       <c r="B33" t="n">
-        <v>96882</v>
+        <v>96889</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>128493897</v>
       </c>
       <c r="B34" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>128493907</v>
       </c>
       <c r="B35" t="n">
-        <v>105699</v>
+        <v>105706</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         <v>128493896</v>
       </c>
       <c r="B36" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>128493903</v>
       </c>
       <c r="B37" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4262,45 +4262,49 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128493878</v>
+        <v>128493895</v>
       </c>
       <c r="B38" t="n">
-        <v>96882</v>
+        <v>98643</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>631686</v>
+        <v>631908</v>
       </c>
       <c r="R38" t="n">
-        <v>6661895</v>
+        <v>6661782</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4335,12 +4339,18 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Mer än 50  bladrosetter</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4362,7 +4372,7 @@
         <v>128493917</v>
       </c>
       <c r="B39" t="n">
-        <v>92816</v>
+        <v>92821</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4460,49 +4470,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128493895</v>
+        <v>128493878</v>
       </c>
       <c r="B40" t="n">
-        <v>98636</v>
+        <v>96889</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>631908</v>
+        <v>631686</v>
       </c>
       <c r="R40" t="n">
-        <v>6661782</v>
+        <v>6661895</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4537,18 +4543,12 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Mer än 50  bladrosetter</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4570,7 +4570,7 @@
         <v>128493916</v>
       </c>
       <c r="B41" t="n">
-        <v>92810</v>
+        <v>92815</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4671,7 +4671,7 @@
         <v>128792098</v>
       </c>
       <c r="B42" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4768,7 +4768,7 @@
         <v>128792102</v>
       </c>
       <c r="B43" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>128792106</v>
       </c>
       <c r="B44" t="n">
-        <v>96078</v>
+        <v>96085</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         <v>128792112</v>
       </c>
       <c r="B45" t="n">
-        <v>92816</v>
+        <v>92821</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5069,7 +5069,7 @@
         <v>128792097</v>
       </c>
       <c r="B46" t="n">
-        <v>96882</v>
+        <v>96889</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5166,7 +5166,7 @@
         <v>128792111</v>
       </c>
       <c r="B47" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         <v>128792108</v>
       </c>
       <c r="B48" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5361,32 +5361,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128792093</v>
+        <v>128792104</v>
       </c>
       <c r="B49" t="n">
-        <v>5197</v>
+        <v>92805</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>105930</v>
+        <v>788</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5396,10 +5396,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>631577</v>
+        <v>631748</v>
       </c>
       <c r="R49" t="n">
-        <v>6661796</v>
+        <v>6661858</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5458,10 +5458,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128792114</v>
+        <v>128792093</v>
       </c>
       <c r="B50" t="n">
-        <v>100824</v>
+        <v>5197</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5469,21 +5469,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5493,10 +5493,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>631859</v>
+        <v>631577</v>
       </c>
       <c r="R50" t="n">
-        <v>6661778</v>
+        <v>6661796</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5555,32 +5555,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128792104</v>
+        <v>128792114</v>
       </c>
       <c r="B51" t="n">
-        <v>92800</v>
+        <v>100831</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>788</v>
+        <v>222498</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5590,10 +5590,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>631748</v>
+        <v>631859</v>
       </c>
       <c r="R51" t="n">
-        <v>6661858</v>
+        <v>6661778</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5655,7 +5655,7 @@
         <v>128792110</v>
       </c>
       <c r="B52" t="n">
-        <v>96125</v>
+        <v>96132</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5752,7 +5752,7 @@
         <v>128792113</v>
       </c>
       <c r="B53" t="n">
-        <v>100824</v>
+        <v>100831</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 41611-2025 artfynd.xlsx
+++ b/artfynd/A 41611-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128493883</v>
+        <v>128493904</v>
       </c>
       <c r="B2" t="n">
-        <v>80169</v>
+        <v>98651</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>631861</v>
+        <v>631707</v>
       </c>
       <c r="R2" t="n">
-        <v>6661676</v>
+        <v>6661837</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>12 bladrosetter</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,32 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128493877</v>
+        <v>128493901</v>
       </c>
       <c r="B3" t="n">
-        <v>96892</v>
+        <v>98651</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>631706</v>
+        <v>632054</v>
       </c>
       <c r="R3" t="n">
-        <v>6661848</v>
+        <v>6661938</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -843,6 +848,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Mer än 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,32 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128493904</v>
+        <v>128493877</v>
       </c>
       <c r="B4" t="n">
-        <v>98646</v>
+        <v>96897</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>631707</v>
+        <v>631706</v>
       </c>
       <c r="R4" t="n">
-        <v>6661837</v>
+        <v>6661848</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -940,11 +950,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>12 bladrosetter</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,32 +976,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128493901</v>
+        <v>128493883</v>
       </c>
       <c r="B5" t="n">
-        <v>98646</v>
+        <v>80174</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>632054</v>
+        <v>631861</v>
       </c>
       <c r="R5" t="n">
-        <v>6661938</v>
+        <v>6661676</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1042,11 +1047,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Mer än 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1076,7 +1076,7 @@
         <v>128493909</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>128493898</v>
       </c>
       <c r="B7" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>128493899</v>
       </c>
       <c r="B8" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>128493900</v>
       </c>
       <c r="B9" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1471,45 +1471,49 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128493875</v>
+        <v>128493893</v>
       </c>
       <c r="B10" t="n">
-        <v>96892</v>
+        <v>98651</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>631869</v>
+        <v>632068</v>
       </c>
       <c r="R10" t="n">
-        <v>6661711</v>
+        <v>6661949</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1544,12 +1548,18 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ca 20 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1568,32 +1578,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128493915</v>
+        <v>128493875</v>
       </c>
       <c r="B11" t="n">
-        <v>96135</v>
+        <v>96897</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2170</v>
+        <v>53</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1603,10 +1613,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>631915</v>
+        <v>631869</v>
       </c>
       <c r="R11" t="n">
-        <v>6661808</v>
+        <v>6661711</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1665,49 +1675,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128493893</v>
+        <v>128493915</v>
       </c>
       <c r="B12" t="n">
-        <v>98646</v>
+        <v>96140</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>2170</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>632068</v>
+        <v>631915</v>
       </c>
       <c r="R12" t="n">
-        <v>6661949</v>
+        <v>6661808</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1742,18 +1748,12 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ca 20 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1775,7 +1775,7 @@
         <v>128493920</v>
       </c>
       <c r="B13" t="n">
-        <v>100834</v>
+        <v>100839</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>128493919</v>
       </c>
       <c r="B14" t="n">
-        <v>92824</v>
+        <v>92829</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>128493913</v>
       </c>
       <c r="B15" t="n">
-        <v>96135</v>
+        <v>96140</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2063,45 +2063,49 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128493914</v>
+        <v>128493902</v>
       </c>
       <c r="B16" t="n">
-        <v>96135</v>
+        <v>98651</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2170</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>632016</v>
+        <v>632008</v>
       </c>
       <c r="R16" t="n">
-        <v>6661935</v>
+        <v>6661933</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2136,12 +2140,18 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>mer än 40 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2160,45 +2170,49 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128493882</v>
+        <v>128493894</v>
       </c>
       <c r="B17" t="n">
-        <v>91535</v>
+        <v>98651</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>631713</v>
+        <v>631994</v>
       </c>
       <c r="R17" t="n">
-        <v>6661819</v>
+        <v>6661866</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2233,12 +2247,18 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>mer än 40 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2257,49 +2277,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128493902</v>
+        <v>128493914</v>
       </c>
       <c r="B18" t="n">
-        <v>98646</v>
+        <v>96140</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>2170</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>632008</v>
+        <v>632016</v>
       </c>
       <c r="R18" t="n">
-        <v>6661933</v>
+        <v>6661935</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2334,18 +2350,12 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>mer än 40 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2364,49 +2374,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128493894</v>
+        <v>128493882</v>
       </c>
       <c r="B19" t="n">
-        <v>98646</v>
+        <v>91540</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>631994</v>
+        <v>631713</v>
       </c>
       <c r="R19" t="n">
-        <v>6661866</v>
+        <v>6661819</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2441,18 +2447,12 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>mer än 40 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2474,7 +2474,7 @@
         <v>128493892</v>
       </c>
       <c r="B20" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2578,32 +2578,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128493879</v>
+        <v>128493884</v>
       </c>
       <c r="B21" t="n">
-        <v>91515</v>
+        <v>80099</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2613,10 +2613,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>631703</v>
+        <v>631861</v>
       </c>
       <c r="R21" t="n">
-        <v>6661853</v>
+        <v>6661676</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2675,32 +2675,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128493884</v>
+        <v>128493879</v>
       </c>
       <c r="B22" t="n">
-        <v>80094</v>
+        <v>91520</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2710,10 +2710,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>631861</v>
+        <v>631703</v>
       </c>
       <c r="R22" t="n">
-        <v>6661676</v>
+        <v>6661853</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2872,7 +2872,7 @@
         <v>128493871</v>
       </c>
       <c r="B24" t="n">
-        <v>101739</v>
+        <v>101744</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>128493905</v>
       </c>
       <c r="B25" t="n">
-        <v>92281</v>
+        <v>92286</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3063,32 +3063,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128493872</v>
+        <v>128493906</v>
       </c>
       <c r="B26" t="n">
-        <v>96892</v>
+        <v>105714</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>53</v>
+        <v>221144</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3098,10 +3098,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>632001</v>
+        <v>631754</v>
       </c>
       <c r="R26" t="n">
-        <v>6661954</v>
+        <v>6661814</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3160,10 +3160,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128493876</v>
+        <v>128493872</v>
       </c>
       <c r="B27" t="n">
-        <v>96892</v>
+        <v>96897</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3195,10 +3195,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>631854</v>
+        <v>632001</v>
       </c>
       <c r="R27" t="n">
-        <v>6661710</v>
+        <v>6661954</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3257,32 +3257,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128493906</v>
+        <v>128493876</v>
       </c>
       <c r="B28" t="n">
-        <v>105709</v>
+        <v>96897</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221144</v>
+        <v>53</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3292,10 +3292,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>631754</v>
+        <v>631854</v>
       </c>
       <c r="R28" t="n">
-        <v>6661814</v>
+        <v>6661710</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3354,48 +3354,52 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128493881</v>
+        <v>128493890</v>
       </c>
       <c r="B29" t="n">
-        <v>57883</v>
+        <v>98651</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>631713</v>
+        <v>631513</v>
       </c>
       <c r="R29" t="n">
-        <v>6661820</v>
+        <v>6661886</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3427,12 +3431,18 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ca 40 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3451,52 +3461,48 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128493890</v>
+        <v>128493881</v>
       </c>
       <c r="B30" t="n">
-        <v>98646</v>
+        <v>57883</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>631513</v>
+        <v>631713</v>
       </c>
       <c r="R30" t="n">
-        <v>6661886</v>
+        <v>6661820</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3528,18 +3534,12 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ca 40 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3561,7 +3561,7 @@
         <v>128493874</v>
       </c>
       <c r="B31" t="n">
-        <v>96892</v>
+        <v>96897</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>128493918</v>
       </c>
       <c r="B32" t="n">
-        <v>92824</v>
+        <v>92829</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
         <v>128493873</v>
       </c>
       <c r="B33" t="n">
-        <v>96892</v>
+        <v>96897</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>128493897</v>
       </c>
       <c r="B34" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>128493907</v>
       </c>
       <c r="B35" t="n">
-        <v>105709</v>
+        <v>105714</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         <v>128493896</v>
       </c>
       <c r="B36" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>128493903</v>
       </c>
       <c r="B37" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4262,45 +4262,49 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128493878</v>
+        <v>128493895</v>
       </c>
       <c r="B38" t="n">
-        <v>96892</v>
+        <v>98651</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>631686</v>
+        <v>631908</v>
       </c>
       <c r="R38" t="n">
-        <v>6661895</v>
+        <v>6661782</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4335,12 +4339,18 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Mer än 50  bladrosetter</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4359,49 +4369,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128493895</v>
+        <v>128493878</v>
       </c>
       <c r="B39" t="n">
-        <v>98646</v>
+        <v>96897</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>631908</v>
+        <v>631686</v>
       </c>
       <c r="R39" t="n">
-        <v>6661782</v>
+        <v>6661895</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4436,18 +4442,12 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Mer än 50  bladrosetter</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4469,7 +4469,7 @@
         <v>128493917</v>
       </c>
       <c r="B40" t="n">
-        <v>92824</v>
+        <v>92829</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5361,10 +5361,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128792114</v>
+        <v>128792093</v>
       </c>
       <c r="B49" t="n">
-        <v>100839</v>
+        <v>5197</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5372,21 +5372,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5396,10 +5396,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>631859</v>
+        <v>631577</v>
       </c>
       <c r="R49" t="n">
-        <v>6661778</v>
+        <v>6661796</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5555,10 +5555,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128792093</v>
+        <v>128792114</v>
       </c>
       <c r="B51" t="n">
-        <v>5197</v>
+        <v>100839</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5566,21 +5566,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5590,10 +5590,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>631577</v>
+        <v>631859</v>
       </c>
       <c r="R51" t="n">
-        <v>6661796</v>
+        <v>6661778</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>

--- a/artfynd/A 41611-2025 artfynd.xlsx
+++ b/artfynd/A 41611-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128493904</v>
+        <v>128493883</v>
       </c>
       <c r="B2" t="n">
-        <v>98651</v>
+        <v>80174</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>631707</v>
+        <v>631861</v>
       </c>
       <c r="R2" t="n">
-        <v>6661837</v>
+        <v>6661676</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>12 bladrosetter</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128493901</v>
+        <v>128493904</v>
       </c>
       <c r="B3" t="n">
         <v>98651</v>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>632054</v>
+        <v>631707</v>
       </c>
       <c r="R3" t="n">
-        <v>6661938</v>
+        <v>6661837</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -852,7 +847,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Mer än 10 bladrosetter</t>
+          <t>12 bladrosetter</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,32 +874,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128493877</v>
+        <v>128493901</v>
       </c>
       <c r="B4" t="n">
-        <v>96897</v>
+        <v>98651</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>631706</v>
+        <v>632054</v>
       </c>
       <c r="R4" t="n">
-        <v>6661848</v>
+        <v>6661938</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -950,6 +945,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Mer än 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,32 +976,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128493883</v>
+        <v>128493877</v>
       </c>
       <c r="B5" t="n">
-        <v>80174</v>
+        <v>96897</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6463</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>631861</v>
+        <v>631706</v>
       </c>
       <c r="R5" t="n">
-        <v>6661676</v>
+        <v>6661848</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1578,32 +1578,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128493875</v>
+        <v>128493915</v>
       </c>
       <c r="B11" t="n">
-        <v>96897</v>
+        <v>96140</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>53</v>
+        <v>2170</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1613,10 +1613,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>631869</v>
+        <v>631915</v>
       </c>
       <c r="R11" t="n">
-        <v>6661711</v>
+        <v>6661808</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1675,32 +1675,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128493915</v>
+        <v>128493875</v>
       </c>
       <c r="B12" t="n">
-        <v>96140</v>
+        <v>96897</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2170</v>
+        <v>53</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1710,10 +1710,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>631915</v>
+        <v>631869</v>
       </c>
       <c r="R12" t="n">
-        <v>6661808</v>
+        <v>6661711</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1869,32 +1869,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128493919</v>
+        <v>128493913</v>
       </c>
       <c r="B14" t="n">
-        <v>92829</v>
+        <v>96140</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4368</v>
+        <v>2170</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1904,10 +1904,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>631760</v>
+        <v>631960</v>
       </c>
       <c r="R14" t="n">
-        <v>6661857</v>
+        <v>6661631</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1966,32 +1966,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128493913</v>
+        <v>128493919</v>
       </c>
       <c r="B15" t="n">
-        <v>96140</v>
+        <v>92829</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2170</v>
+        <v>4368</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2001,10 +2001,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>631960</v>
+        <v>631760</v>
       </c>
       <c r="R15" t="n">
-        <v>6661631</v>
+        <v>6661857</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2063,49 +2063,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128493902</v>
+        <v>128493914</v>
       </c>
       <c r="B16" t="n">
-        <v>98651</v>
+        <v>96140</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>2170</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>632008</v>
+        <v>632016</v>
       </c>
       <c r="R16" t="n">
-        <v>6661933</v>
+        <v>6661935</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2140,18 +2136,12 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>mer än 40 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2170,49 +2160,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128493894</v>
+        <v>128493882</v>
       </c>
       <c r="B17" t="n">
-        <v>98651</v>
+        <v>91540</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>631994</v>
+        <v>631713</v>
       </c>
       <c r="R17" t="n">
-        <v>6661866</v>
+        <v>6661819</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2247,18 +2233,12 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>mer än 40 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2277,45 +2257,49 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128493914</v>
+        <v>128493902</v>
       </c>
       <c r="B18" t="n">
-        <v>96140</v>
+        <v>98651</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2170</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>632016</v>
+        <v>632008</v>
       </c>
       <c r="R18" t="n">
-        <v>6661935</v>
+        <v>6661933</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2350,12 +2334,18 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>mer än 40 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2374,45 +2364,49 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128493882</v>
+        <v>128493894</v>
       </c>
       <c r="B19" t="n">
-        <v>91540</v>
+        <v>98651</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>631713</v>
+        <v>631994</v>
       </c>
       <c r="R19" t="n">
-        <v>6661819</v>
+        <v>6661866</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2447,12 +2441,18 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>mer än 40 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -3063,32 +3063,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128493906</v>
+        <v>128493872</v>
       </c>
       <c r="B26" t="n">
-        <v>105714</v>
+        <v>96897</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221144</v>
+        <v>53</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3098,10 +3098,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>631754</v>
+        <v>632001</v>
       </c>
       <c r="R26" t="n">
-        <v>6661814</v>
+        <v>6661954</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3160,7 +3160,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128493872</v>
+        <v>128493876</v>
       </c>
       <c r="B27" t="n">
         <v>96897</v>
@@ -3195,10 +3195,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>632001</v>
+        <v>631854</v>
       </c>
       <c r="R27" t="n">
-        <v>6661954</v>
+        <v>6661710</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3257,32 +3257,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128493876</v>
+        <v>128493906</v>
       </c>
       <c r="B28" t="n">
-        <v>96897</v>
+        <v>105714</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>53</v>
+        <v>221144</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3292,10 +3292,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>631854</v>
+        <v>631754</v>
       </c>
       <c r="R28" t="n">
-        <v>6661710</v>
+        <v>6661814</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3354,52 +3354,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128493890</v>
+        <v>128493881</v>
       </c>
       <c r="B29" t="n">
-        <v>98651</v>
+        <v>57883</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>631513</v>
+        <v>631713</v>
       </c>
       <c r="R29" t="n">
-        <v>6661886</v>
+        <v>6661820</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3431,18 +3427,12 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ca 40 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3461,48 +3451,52 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128493881</v>
+        <v>128493890</v>
       </c>
       <c r="B30" t="n">
-        <v>57883</v>
+        <v>98651</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>631713</v>
+        <v>631513</v>
       </c>
       <c r="R30" t="n">
-        <v>6661820</v>
+        <v>6661886</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3534,12 +3528,18 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ca 40 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3849,32 +3849,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128493897</v>
+        <v>128493907</v>
       </c>
       <c r="B34" t="n">
-        <v>98651</v>
+        <v>105714</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3884,10 +3884,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>631658</v>
+        <v>631741</v>
       </c>
       <c r="R34" t="n">
-        <v>6661890</v>
+        <v>6661845</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -3924,7 +3924,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ett fåtal bladrosetter</t>
+          <t>Mer än 20 bladrosetter</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3951,32 +3951,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128493907</v>
+        <v>128493897</v>
       </c>
       <c r="B35" t="n">
-        <v>105714</v>
+        <v>98651</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3986,10 +3986,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>631741</v>
+        <v>631658</v>
       </c>
       <c r="R35" t="n">
-        <v>6661845</v>
+        <v>6661890</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4026,7 +4026,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Mer än 20 bladrosetter</t>
+          <t>Ett fåtal bladrosetter</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4262,49 +4262,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128493895</v>
+        <v>128493878</v>
       </c>
       <c r="B38" t="n">
-        <v>98651</v>
+        <v>96897</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>631908</v>
+        <v>631686</v>
       </c>
       <c r="R38" t="n">
-        <v>6661782</v>
+        <v>6661895</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4339,18 +4335,12 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Mer än 50  bladrosetter</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4369,10 +4359,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128493878</v>
+        <v>128493917</v>
       </c>
       <c r="B39" t="n">
-        <v>96897</v>
+        <v>92829</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4380,34 +4370,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>53</v>
+        <v>4368</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>631686</v>
+        <v>631806</v>
       </c>
       <c r="R39" t="n">
-        <v>6661895</v>
+        <v>6661784</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4448,6 +4441,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4466,37 +4460,38 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128493917</v>
+        <v>128493895</v>
       </c>
       <c r="B40" t="n">
-        <v>92829</v>
+        <v>98651</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4368</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4504,10 +4499,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>631806</v>
+        <v>631908</v>
       </c>
       <c r="R40" t="n">
-        <v>6661784</v>
+        <v>6661782</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4540,6 +4535,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Mer än 50  bladrosetter</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4570,7 +4570,7 @@
         <v>128493916</v>
       </c>
       <c r="B41" t="n">
-        <v>92823</v>
+        <v>92828</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4671,7 +4671,7 @@
         <v>128792098</v>
       </c>
       <c r="B42" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4768,7 +4768,7 @@
         <v>128792102</v>
       </c>
       <c r="B43" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4867,32 +4867,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128792106</v>
+        <v>128792112</v>
       </c>
       <c r="B44" t="n">
-        <v>96093</v>
+        <v>92834</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>210</v>
+        <v>4368</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4902,10 +4902,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>631759</v>
+        <v>631814</v>
       </c>
       <c r="R44" t="n">
-        <v>6661865</v>
+        <v>6661721</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4938,11 +4938,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>30 kapslar</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4969,32 +4964,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128792112</v>
+        <v>128792106</v>
       </c>
       <c r="B45" t="n">
-        <v>92829</v>
+        <v>96098</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4368</v>
+        <v>210</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5004,10 +4999,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>631814</v>
+        <v>631759</v>
       </c>
       <c r="R45" t="n">
-        <v>6661721</v>
+        <v>6661865</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5040,6 +5035,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>30 kapslar</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5069,7 +5069,7 @@
         <v>128792097</v>
       </c>
       <c r="B46" t="n">
-        <v>96897</v>
+        <v>96902</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5166,7 +5166,7 @@
         <v>128792111</v>
       </c>
       <c r="B47" t="n">
-        <v>92847</v>
+        <v>92852</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         <v>128792108</v>
       </c>
       <c r="B48" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>128792104</v>
       </c>
       <c r="B50" t="n">
-        <v>92813</v>
+        <v>92818</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5558,7 +5558,7 @@
         <v>128792114</v>
       </c>
       <c r="B51" t="n">
-        <v>100839</v>
+        <v>100844</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5655,7 +5655,7 @@
         <v>128792110</v>
       </c>
       <c r="B52" t="n">
-        <v>96140</v>
+        <v>96145</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5752,7 +5752,7 @@
         <v>128792113</v>
       </c>
       <c r="B53" t="n">
-        <v>100839</v>
+        <v>100844</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 41611-2025 artfynd.xlsx
+++ b/artfynd/A 41611-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128493883</v>
+        <v>128493877</v>
       </c>
       <c r="B2" t="n">
-        <v>80174</v>
+        <v>96905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6463</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>631861</v>
+        <v>631706</v>
       </c>
       <c r="R2" t="n">
-        <v>6661676</v>
+        <v>6661848</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128493904</v>
+        <v>128493883</v>
       </c>
       <c r="B3" t="n">
-        <v>98651</v>
+        <v>80175</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>631707</v>
+        <v>631861</v>
       </c>
       <c r="R3" t="n">
-        <v>6661837</v>
+        <v>6661676</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -843,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>12 bladrosetter</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128493901</v>
+        <v>128493904</v>
       </c>
       <c r="B4" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -909,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>632054</v>
+        <v>631707</v>
       </c>
       <c r="R4" t="n">
-        <v>6661938</v>
+        <v>6661837</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -949,7 +944,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Mer än 10 bladrosetter</t>
+          <t>12 bladrosetter</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,32 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128493877</v>
+        <v>128493901</v>
       </c>
       <c r="B5" t="n">
-        <v>96897</v>
+        <v>98659</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>631706</v>
+        <v>632054</v>
       </c>
       <c r="R5" t="n">
-        <v>6661848</v>
+        <v>6661938</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1047,6 +1042,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Mer än 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1076,7 +1076,7 @@
         <v>128493909</v>
       </c>
       <c r="B6" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>128493898</v>
       </c>
       <c r="B7" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>128493899</v>
       </c>
       <c r="B8" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>128493900</v>
       </c>
       <c r="B9" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1471,49 +1471,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128493893</v>
+        <v>128493875</v>
       </c>
       <c r="B10" t="n">
-        <v>98651</v>
+        <v>96905</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>632068</v>
+        <v>631869</v>
       </c>
       <c r="R10" t="n">
-        <v>6661949</v>
+        <v>6661711</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1548,18 +1544,12 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ca 20 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1581,7 +1571,7 @@
         <v>128493915</v>
       </c>
       <c r="B11" t="n">
-        <v>96140</v>
+        <v>96148</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1675,45 +1665,49 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128493875</v>
+        <v>128493893</v>
       </c>
       <c r="B12" t="n">
-        <v>96897</v>
+        <v>98659</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>631869</v>
+        <v>632068</v>
       </c>
       <c r="R12" t="n">
-        <v>6661711</v>
+        <v>6661949</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1748,12 +1742,18 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ca 20 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1775,7 +1775,7 @@
         <v>128493920</v>
       </c>
       <c r="B13" t="n">
-        <v>100839</v>
+        <v>100847</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>128493913</v>
       </c>
       <c r="B14" t="n">
-        <v>96140</v>
+        <v>96148</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>128493919</v>
       </c>
       <c r="B15" t="n">
-        <v>92829</v>
+        <v>92837</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>128493914</v>
       </c>
       <c r="B16" t="n">
-        <v>96140</v>
+        <v>96148</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2160,45 +2160,49 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128493882</v>
+        <v>128493902</v>
       </c>
       <c r="B17" t="n">
-        <v>91540</v>
+        <v>98659</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>631713</v>
+        <v>632008</v>
       </c>
       <c r="R17" t="n">
-        <v>6661819</v>
+        <v>6661933</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2233,12 +2237,18 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>mer än 40 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2257,10 +2267,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128493902</v>
+        <v>128493894</v>
       </c>
       <c r="B18" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2296,10 +2306,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>632008</v>
+        <v>631994</v>
       </c>
       <c r="R18" t="n">
-        <v>6661933</v>
+        <v>6661866</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2364,49 +2374,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128493894</v>
+        <v>128493882</v>
       </c>
       <c r="B19" t="n">
-        <v>98651</v>
+        <v>91546</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>631994</v>
+        <v>631713</v>
       </c>
       <c r="R19" t="n">
-        <v>6661866</v>
+        <v>6661819</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2441,18 +2447,12 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>mer än 40 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2474,7 +2474,7 @@
         <v>128493892</v>
       </c>
       <c r="B20" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2578,32 +2578,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128493884</v>
+        <v>128493879</v>
       </c>
       <c r="B21" t="n">
-        <v>80099</v>
+        <v>91526</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2613,10 +2613,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>631861</v>
+        <v>631703</v>
       </c>
       <c r="R21" t="n">
-        <v>6661676</v>
+        <v>6661853</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2675,32 +2675,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128493879</v>
+        <v>128493884</v>
       </c>
       <c r="B22" t="n">
-        <v>91520</v>
+        <v>80100</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2710,10 +2710,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>631703</v>
+        <v>631861</v>
       </c>
       <c r="R22" t="n">
-        <v>6661853</v>
+        <v>6661676</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2772,32 +2772,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128493885</v>
+        <v>128493871</v>
       </c>
       <c r="B23" t="n">
-        <v>57720</v>
+        <v>101752</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>221235</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2807,10 +2807,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>631983</v>
+        <v>631816</v>
       </c>
       <c r="R23" t="n">
-        <v>6661724</v>
+        <v>6661751</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2869,32 +2869,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128493871</v>
+        <v>128493885</v>
       </c>
       <c r="B24" t="n">
-        <v>101744</v>
+        <v>57720</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221235</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2904,10 +2904,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>631816</v>
+        <v>631983</v>
       </c>
       <c r="R24" t="n">
-        <v>6661751</v>
+        <v>6661724</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2969,7 +2969,7 @@
         <v>128493905</v>
       </c>
       <c r="B25" t="n">
-        <v>92286</v>
+        <v>92294</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
         <v>128493872</v>
       </c>
       <c r="B26" t="n">
-        <v>96897</v>
+        <v>96905</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>128493876</v>
       </c>
       <c r="B27" t="n">
-        <v>96897</v>
+        <v>96905</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
         <v>128493906</v>
       </c>
       <c r="B28" t="n">
-        <v>105714</v>
+        <v>105722</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
         <v>128493890</v>
       </c>
       <c r="B30" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>128493874</v>
       </c>
       <c r="B31" t="n">
-        <v>96897</v>
+        <v>96905</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>128493918</v>
       </c>
       <c r="B32" t="n">
-        <v>92829</v>
+        <v>92837</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
         <v>128493873</v>
       </c>
       <c r="B33" t="n">
-        <v>96897</v>
+        <v>96905</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>128493907</v>
       </c>
       <c r="B34" t="n">
-        <v>105714</v>
+        <v>105722</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>128493897</v>
       </c>
       <c r="B35" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         <v>128493896</v>
       </c>
       <c r="B36" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>128493903</v>
       </c>
       <c r="B37" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         <v>128493878</v>
       </c>
       <c r="B38" t="n">
-        <v>96897</v>
+        <v>96905</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4359,37 +4359,38 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128493917</v>
+        <v>128493895</v>
       </c>
       <c r="B39" t="n">
-        <v>92829</v>
+        <v>98659</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4368</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4397,10 +4398,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>631806</v>
+        <v>631908</v>
       </c>
       <c r="R39" t="n">
-        <v>6661784</v>
+        <v>6661782</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4433,6 +4434,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Mer än 50  bladrosetter</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4460,38 +4466,37 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128493895</v>
+        <v>128493917</v>
       </c>
       <c r="B40" t="n">
-        <v>98651</v>
+        <v>92837</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>4368</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4499,10 +4504,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>631908</v>
+        <v>631806</v>
       </c>
       <c r="R40" t="n">
-        <v>6661782</v>
+        <v>6661784</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4535,11 +4540,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Mer än 50  bladrosetter</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4570,7 +4570,7 @@
         <v>128493916</v>
       </c>
       <c r="B41" t="n">
-        <v>92828</v>
+        <v>92831</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4671,7 +4671,7 @@
         <v>128792098</v>
       </c>
       <c r="B42" t="n">
-        <v>91488</v>
+        <v>91491</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4768,7 +4768,7 @@
         <v>128792102</v>
       </c>
       <c r="B43" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>128792112</v>
       </c>
       <c r="B44" t="n">
-        <v>92834</v>
+        <v>92837</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4967,7 +4967,7 @@
         <v>128792106</v>
       </c>
       <c r="B45" t="n">
-        <v>96098</v>
+        <v>96101</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5069,7 +5069,7 @@
         <v>128792097</v>
       </c>
       <c r="B46" t="n">
-        <v>96902</v>
+        <v>96905</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5166,7 +5166,7 @@
         <v>128792111</v>
       </c>
       <c r="B47" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         <v>128792108</v>
       </c>
       <c r="B48" t="n">
-        <v>91541</v>
+        <v>91544</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5361,32 +5361,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128792093</v>
+        <v>128792104</v>
       </c>
       <c r="B49" t="n">
-        <v>5197</v>
+        <v>92821</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>105930</v>
+        <v>788</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5396,10 +5396,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>631577</v>
+        <v>631748</v>
       </c>
       <c r="R49" t="n">
-        <v>6661796</v>
+        <v>6661858</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5458,32 +5458,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128792104</v>
+        <v>128792093</v>
       </c>
       <c r="B50" t="n">
-        <v>92818</v>
+        <v>5197</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>788</v>
+        <v>105930</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5493,10 +5493,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>631748</v>
+        <v>631577</v>
       </c>
       <c r="R50" t="n">
-        <v>6661858</v>
+        <v>6661796</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5558,7 +5558,7 @@
         <v>128792114</v>
       </c>
       <c r="B51" t="n">
-        <v>100844</v>
+        <v>100847</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5655,7 +5655,7 @@
         <v>128792110</v>
       </c>
       <c r="B52" t="n">
-        <v>96145</v>
+        <v>96148</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5752,7 +5752,7 @@
         <v>128792113</v>
       </c>
       <c r="B53" t="n">
-        <v>100844</v>
+        <v>100847</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 41611-2025 artfynd.xlsx
+++ b/artfynd/A 41611-2025 artfynd.xlsx
@@ -3383,6 +3383,14 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
@@ -4867,32 +4875,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128792112</v>
+        <v>128792106</v>
       </c>
       <c r="B44" t="n">
-        <v>92837</v>
+        <v>96101</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4368</v>
+        <v>210</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4902,10 +4910,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>631814</v>
+        <v>631759</v>
       </c>
       <c r="R44" t="n">
-        <v>6661721</v>
+        <v>6661865</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4938,6 +4946,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>30 kapslar</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4964,32 +4977,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128792106</v>
+        <v>128792112</v>
       </c>
       <c r="B45" t="n">
-        <v>96101</v>
+        <v>92837</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>210</v>
+        <v>4368</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4999,10 +5012,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>631759</v>
+        <v>631814</v>
       </c>
       <c r="R45" t="n">
-        <v>6661865</v>
+        <v>6661721</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5035,11 +5048,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>30 kapslar</t>
         </is>
       </c>
       <c r="AD45" t="b">

--- a/artfynd/A 41611-2025 artfynd.xlsx
+++ b/artfynd/A 41611-2025 artfynd.xlsx
@@ -5369,32 +5369,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128792104</v>
+        <v>128792093</v>
       </c>
       <c r="B49" t="n">
-        <v>92821</v>
+        <v>5197</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>788</v>
+        <v>105930</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5404,10 +5404,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>631748</v>
+        <v>631577</v>
       </c>
       <c r="R49" t="n">
-        <v>6661858</v>
+        <v>6661796</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5466,32 +5466,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128792093</v>
+        <v>128792104</v>
       </c>
       <c r="B50" t="n">
-        <v>5197</v>
+        <v>92821</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>105930</v>
+        <v>788</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5501,10 +5501,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>631577</v>
+        <v>631748</v>
       </c>
       <c r="R50" t="n">
-        <v>6661796</v>
+        <v>6661858</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>

--- a/artfynd/A 41611-2025 artfynd.xlsx
+++ b/artfynd/A 41611-2025 artfynd.xlsx
@@ -4875,32 +4875,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128792106</v>
+        <v>128792112</v>
       </c>
       <c r="B44" t="n">
-        <v>96101</v>
+        <v>92837</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>210</v>
+        <v>4368</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4910,10 +4910,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>631759</v>
+        <v>631814</v>
       </c>
       <c r="R44" t="n">
-        <v>6661865</v>
+        <v>6661721</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4946,11 +4946,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>30 kapslar</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4977,32 +4972,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128792112</v>
+        <v>128792106</v>
       </c>
       <c r="B45" t="n">
-        <v>92837</v>
+        <v>96101</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4368</v>
+        <v>210</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5012,10 +5007,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>631814</v>
+        <v>631759</v>
       </c>
       <c r="R45" t="n">
-        <v>6661721</v>
+        <v>6661865</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5048,6 +5043,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>30 kapslar</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5369,32 +5369,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128792093</v>
+        <v>128792104</v>
       </c>
       <c r="B49" t="n">
-        <v>5197</v>
+        <v>92821</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>105930</v>
+        <v>788</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5404,10 +5404,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>631577</v>
+        <v>631748</v>
       </c>
       <c r="R49" t="n">
-        <v>6661796</v>
+        <v>6661858</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5466,32 +5466,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128792104</v>
+        <v>128792093</v>
       </c>
       <c r="B50" t="n">
-        <v>92821</v>
+        <v>5197</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>788</v>
+        <v>105930</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5501,10 +5501,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>631748</v>
+        <v>631577</v>
       </c>
       <c r="R50" t="n">
-        <v>6661858</v>
+        <v>6661796</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>

--- a/artfynd/A 41611-2025 artfynd.xlsx
+++ b/artfynd/A 41611-2025 artfynd.xlsx
@@ -3357,7 +3357,7 @@
         <v>128493881</v>
       </c>
       <c r="B29" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         <v>128493916</v>
       </c>
       <c r="B41" t="n">
-        <v>92831</v>
+        <v>92838</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4679,7 +4679,7 @@
         <v>128792098</v>
       </c>
       <c r="B42" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4776,7 +4776,7 @@
         <v>128792102</v>
       </c>
       <c r="B43" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         <v>128792112</v>
       </c>
       <c r="B44" t="n">
-        <v>92837</v>
+        <v>92844</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         <v>128792106</v>
       </c>
       <c r="B45" t="n">
-        <v>96101</v>
+        <v>96111</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5077,7 +5077,7 @@
         <v>128792097</v>
       </c>
       <c r="B46" t="n">
-        <v>96905</v>
+        <v>96915</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>128792111</v>
       </c>
       <c r="B47" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5275,7 +5275,7 @@
         <v>128792108</v>
       </c>
       <c r="B48" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5369,32 +5369,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128792104</v>
+        <v>128792093</v>
       </c>
       <c r="B49" t="n">
-        <v>92821</v>
+        <v>5197</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>788</v>
+        <v>105930</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5404,10 +5404,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>631748</v>
+        <v>631577</v>
       </c>
       <c r="R49" t="n">
-        <v>6661858</v>
+        <v>6661796</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5466,10 +5466,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128792093</v>
+        <v>128792114</v>
       </c>
       <c r="B50" t="n">
-        <v>5197</v>
+        <v>100857</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5477,21 +5477,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5501,10 +5501,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>631577</v>
+        <v>631859</v>
       </c>
       <c r="R50" t="n">
-        <v>6661796</v>
+        <v>6661778</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5563,32 +5563,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128792114</v>
+        <v>128792104</v>
       </c>
       <c r="B51" t="n">
-        <v>100847</v>
+        <v>92828</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>222498</v>
+        <v>788</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5598,10 +5598,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>631859</v>
+        <v>631748</v>
       </c>
       <c r="R51" t="n">
-        <v>6661778</v>
+        <v>6661858</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5663,7 +5663,7 @@
         <v>128792110</v>
       </c>
       <c r="B52" t="n">
-        <v>96148</v>
+        <v>96158</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5760,7 +5760,7 @@
         <v>128792113</v>
       </c>
       <c r="B53" t="n">
-        <v>100847</v>
+        <v>100857</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 41611-2025 artfynd.xlsx
+++ b/artfynd/A 41611-2025 artfynd.xlsx
@@ -4578,7 +4578,7 @@
         <v>128493916</v>
       </c>
       <c r="B41" t="n">
-        <v>92838</v>
+        <v>92845</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4679,7 +4679,7 @@
         <v>128792098</v>
       </c>
       <c r="B42" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4776,7 +4776,7 @@
         <v>128792102</v>
       </c>
       <c r="B43" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4875,32 +4875,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128792112</v>
+        <v>128792106</v>
       </c>
       <c r="B44" t="n">
-        <v>92844</v>
+        <v>96118</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4368</v>
+        <v>210</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4910,10 +4910,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>631814</v>
+        <v>631759</v>
       </c>
       <c r="R44" t="n">
-        <v>6661721</v>
+        <v>6661865</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4946,6 +4946,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>30 kapslar</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4972,32 +4977,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128792106</v>
+        <v>128792112</v>
       </c>
       <c r="B45" t="n">
-        <v>96111</v>
+        <v>92851</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>210</v>
+        <v>4368</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5007,10 +5012,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>631759</v>
+        <v>631814</v>
       </c>
       <c r="R45" t="n">
-        <v>6661865</v>
+        <v>6661721</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5043,11 +5048,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>30 kapslar</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5077,7 +5077,7 @@
         <v>128792097</v>
       </c>
       <c r="B46" t="n">
-        <v>96915</v>
+        <v>96922</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>128792111</v>
       </c>
       <c r="B47" t="n">
-        <v>92862</v>
+        <v>92869</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5275,7 +5275,7 @@
         <v>128792108</v>
       </c>
       <c r="B48" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5369,32 +5369,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128792093</v>
+        <v>128792104</v>
       </c>
       <c r="B49" t="n">
-        <v>5197</v>
+        <v>92835</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>105930</v>
+        <v>788</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5404,10 +5404,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>631577</v>
+        <v>631748</v>
       </c>
       <c r="R49" t="n">
-        <v>6661796</v>
+        <v>6661858</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5469,7 +5469,7 @@
         <v>128792114</v>
       </c>
       <c r="B50" t="n">
-        <v>100857</v>
+        <v>100864</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5563,32 +5563,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128792104</v>
+        <v>128792093</v>
       </c>
       <c r="B51" t="n">
-        <v>92828</v>
+        <v>5197</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>788</v>
+        <v>105930</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5598,10 +5598,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>631748</v>
+        <v>631577</v>
       </c>
       <c r="R51" t="n">
-        <v>6661858</v>
+        <v>6661796</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5663,7 +5663,7 @@
         <v>128792110</v>
       </c>
       <c r="B52" t="n">
-        <v>96158</v>
+        <v>96165</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5760,7 +5760,7 @@
         <v>128792113</v>
       </c>
       <c r="B53" t="n">
-        <v>100857</v>
+        <v>100864</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 41611-2025 artfynd.xlsx
+++ b/artfynd/A 41611-2025 artfynd.xlsx
@@ -3357,7 +3357,7 @@
         <v>128493881</v>
       </c>
       <c r="B29" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         <v>128493916</v>
       </c>
       <c r="B41" t="n">
-        <v>92845</v>
+        <v>92847</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4679,7 +4679,7 @@
         <v>128792098</v>
       </c>
       <c r="B42" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4776,7 +4776,7 @@
         <v>128792102</v>
       </c>
       <c r="B43" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         <v>128792106</v>
       </c>
       <c r="B44" t="n">
-        <v>96118</v>
+        <v>96120</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
         <v>128792112</v>
       </c>
       <c r="B45" t="n">
-        <v>92851</v>
+        <v>92853</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5077,7 +5077,7 @@
         <v>128792097</v>
       </c>
       <c r="B46" t="n">
-        <v>96922</v>
+        <v>96924</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>128792111</v>
       </c>
       <c r="B47" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5275,7 +5275,7 @@
         <v>128792108</v>
       </c>
       <c r="B48" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5369,32 +5369,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128792104</v>
+        <v>128792114</v>
       </c>
       <c r="B49" t="n">
-        <v>92835</v>
+        <v>100866</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>788</v>
+        <v>222498</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5404,10 +5404,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>631748</v>
+        <v>631859</v>
       </c>
       <c r="R49" t="n">
-        <v>6661858</v>
+        <v>6661778</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5466,32 +5466,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128792114</v>
+        <v>128792104</v>
       </c>
       <c r="B50" t="n">
-        <v>100864</v>
+        <v>92837</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222498</v>
+        <v>788</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5501,10 +5501,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>631859</v>
+        <v>631748</v>
       </c>
       <c r="R50" t="n">
-        <v>6661778</v>
+        <v>6661858</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5663,7 +5663,7 @@
         <v>128792110</v>
       </c>
       <c r="B52" t="n">
-        <v>96165</v>
+        <v>96167</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5760,7 +5760,7 @@
         <v>128792113</v>
       </c>
       <c r="B53" t="n">
-        <v>100864</v>
+        <v>100866</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 41611-2025 artfynd.xlsx
+++ b/artfynd/A 41611-2025 artfynd.xlsx
@@ -4875,32 +4875,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128792106</v>
+        <v>128792112</v>
       </c>
       <c r="B44" t="n">
-        <v>96120</v>
+        <v>92853</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>210</v>
+        <v>4368</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4910,10 +4910,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>631759</v>
+        <v>631814</v>
       </c>
       <c r="R44" t="n">
-        <v>6661865</v>
+        <v>6661721</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4946,11 +4946,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>30 kapslar</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4977,32 +4972,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128792112</v>
+        <v>128792106</v>
       </c>
       <c r="B45" t="n">
-        <v>92853</v>
+        <v>96120</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4368</v>
+        <v>210</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5012,10 +5007,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>631814</v>
+        <v>631759</v>
       </c>
       <c r="R45" t="n">
-        <v>6661721</v>
+        <v>6661865</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5048,6 +5043,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>30 kapslar</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5369,32 +5369,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128792114</v>
+        <v>128792104</v>
       </c>
       <c r="B49" t="n">
-        <v>100866</v>
+        <v>92837</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>222498</v>
+        <v>788</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5404,10 +5404,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>631859</v>
+        <v>631748</v>
       </c>
       <c r="R49" t="n">
-        <v>6661778</v>
+        <v>6661858</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5466,32 +5466,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128792104</v>
+        <v>128792093</v>
       </c>
       <c r="B50" t="n">
-        <v>92837</v>
+        <v>5197</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>788</v>
+        <v>105930</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5501,10 +5501,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>631748</v>
+        <v>631577</v>
       </c>
       <c r="R50" t="n">
-        <v>6661858</v>
+        <v>6661796</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5563,10 +5563,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128792093</v>
+        <v>128792114</v>
       </c>
       <c r="B51" t="n">
-        <v>5197</v>
+        <v>100866</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5574,21 +5574,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5598,10 +5598,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>631577</v>
+        <v>631859</v>
       </c>
       <c r="R51" t="n">
-        <v>6661796</v>
+        <v>6661778</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>

--- a/artfynd/A 41611-2025 artfynd.xlsx
+++ b/artfynd/A 41611-2025 artfynd.xlsx
@@ -5369,32 +5369,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128792104</v>
+        <v>128792093</v>
       </c>
       <c r="B49" t="n">
-        <v>92837</v>
+        <v>5197</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>788</v>
+        <v>105930</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5404,10 +5404,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>631748</v>
+        <v>631577</v>
       </c>
       <c r="R49" t="n">
-        <v>6661858</v>
+        <v>6661796</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5466,10 +5466,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128792093</v>
+        <v>128792114</v>
       </c>
       <c r="B50" t="n">
-        <v>5197</v>
+        <v>100866</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5477,21 +5477,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5501,10 +5501,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>631577</v>
+        <v>631859</v>
       </c>
       <c r="R50" t="n">
-        <v>6661796</v>
+        <v>6661778</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5563,32 +5563,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128792114</v>
+        <v>128792104</v>
       </c>
       <c r="B51" t="n">
-        <v>100866</v>
+        <v>92837</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>222498</v>
+        <v>788</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5598,10 +5598,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>631859</v>
+        <v>631748</v>
       </c>
       <c r="R51" t="n">
-        <v>6661778</v>
+        <v>6661858</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>

--- a/artfynd/A 41611-2025 artfynd.xlsx
+++ b/artfynd/A 41611-2025 artfynd.xlsx
@@ -4578,7 +4578,7 @@
         <v>128493916</v>
       </c>
       <c r="B41" t="n">
-        <v>92847</v>
+        <v>92833</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4679,7 +4679,7 @@
         <v>128792098</v>
       </c>
       <c r="B42" t="n">
-        <v>91506</v>
+        <v>91504</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4776,7 +4776,7 @@
         <v>128792102</v>
       </c>
       <c r="B43" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4875,32 +4875,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128792112</v>
+        <v>128792106</v>
       </c>
       <c r="B44" t="n">
-        <v>92853</v>
+        <v>96146</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4368</v>
+        <v>210</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4910,10 +4910,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>631814</v>
+        <v>631759</v>
       </c>
       <c r="R44" t="n">
-        <v>6661721</v>
+        <v>6661865</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4946,6 +4946,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>30 kapslar</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4972,32 +4977,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128792106</v>
+        <v>128792112</v>
       </c>
       <c r="B45" t="n">
-        <v>96120</v>
+        <v>92839</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>210</v>
+        <v>4368</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5007,10 +5012,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>631759</v>
+        <v>631814</v>
       </c>
       <c r="R45" t="n">
-        <v>6661865</v>
+        <v>6661721</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5043,11 +5048,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>30 kapslar</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5077,7 +5077,7 @@
         <v>128792097</v>
       </c>
       <c r="B46" t="n">
-        <v>96924</v>
+        <v>96950</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>128792111</v>
       </c>
       <c r="B47" t="n">
-        <v>92871</v>
+        <v>92857</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5275,7 +5275,7 @@
         <v>128792108</v>
       </c>
       <c r="B48" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5369,32 +5369,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128792093</v>
+        <v>128792104</v>
       </c>
       <c r="B49" t="n">
-        <v>5197</v>
+        <v>92823</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>105930</v>
+        <v>788</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5404,10 +5404,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>631577</v>
+        <v>631748</v>
       </c>
       <c r="R49" t="n">
-        <v>6661796</v>
+        <v>6661858</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5466,10 +5466,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128792114</v>
+        <v>128792093</v>
       </c>
       <c r="B50" t="n">
-        <v>100866</v>
+        <v>5197</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5477,21 +5477,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5501,10 +5501,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>631859</v>
+        <v>631577</v>
       </c>
       <c r="R50" t="n">
-        <v>6661778</v>
+        <v>6661796</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5563,32 +5563,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128792104</v>
+        <v>128792114</v>
       </c>
       <c r="B51" t="n">
-        <v>92837</v>
+        <v>100892</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>788</v>
+        <v>222498</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5598,10 +5598,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>631748</v>
+        <v>631859</v>
       </c>
       <c r="R51" t="n">
-        <v>6661858</v>
+        <v>6661778</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5663,7 +5663,7 @@
         <v>128792110</v>
       </c>
       <c r="B52" t="n">
-        <v>96167</v>
+        <v>96193</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5760,7 +5760,7 @@
         <v>128792113</v>
       </c>
       <c r="B53" t="n">
-        <v>100866</v>
+        <v>100892</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 41611-2025 artfynd.xlsx
+++ b/artfynd/A 41611-2025 artfynd.xlsx
@@ -4776,7 +4776,7 @@
         <v>128792102</v>
       </c>
       <c r="B43" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         <v>128792106</v>
       </c>
       <c r="B44" t="n">
-        <v>96146</v>
+        <v>96147</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
         <v>128792112</v>
       </c>
       <c r="B45" t="n">
-        <v>92839</v>
+        <v>92840</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5077,7 +5077,7 @@
         <v>128792097</v>
       </c>
       <c r="B46" t="n">
-        <v>96950</v>
+        <v>96951</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>128792111</v>
       </c>
       <c r="B47" t="n">
-        <v>92857</v>
+        <v>92858</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5275,7 +5275,7 @@
         <v>128792108</v>
       </c>
       <c r="B48" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5292,14 +5292,10 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5372,7 +5368,7 @@
         <v>128792104</v>
       </c>
       <c r="B49" t="n">
-        <v>92823</v>
+        <v>92824</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5466,10 +5462,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128792093</v>
+        <v>128792114</v>
       </c>
       <c r="B50" t="n">
-        <v>5197</v>
+        <v>100894</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5477,21 +5473,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5501,10 +5497,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>631577</v>
+        <v>631859</v>
       </c>
       <c r="R50" t="n">
-        <v>6661796</v>
+        <v>6661778</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5563,10 +5559,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128792114</v>
+        <v>128792093</v>
       </c>
       <c r="B51" t="n">
-        <v>100892</v>
+        <v>5197</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5574,21 +5570,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5598,10 +5594,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>631859</v>
+        <v>631577</v>
       </c>
       <c r="R51" t="n">
-        <v>6661778</v>
+        <v>6661796</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5663,7 +5659,7 @@
         <v>128792110</v>
       </c>
       <c r="B52" t="n">
-        <v>96193</v>
+        <v>96194</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5760,7 +5756,7 @@
         <v>128792113</v>
       </c>
       <c r="B53" t="n">
-        <v>100892</v>
+        <v>100894</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 41611-2025 artfynd.xlsx
+++ b/artfynd/A 41611-2025 artfynd.xlsx
@@ -4776,7 +4776,7 @@
         <v>128792102</v>
       </c>
       <c r="B43" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4875,32 +4875,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128792106</v>
+        <v>128792112</v>
       </c>
       <c r="B44" t="n">
-        <v>96147</v>
+        <v>92840</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>210</v>
+        <v>4368</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4910,10 +4910,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>631759</v>
+        <v>631814</v>
       </c>
       <c r="R44" t="n">
-        <v>6661865</v>
+        <v>6661721</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4946,11 +4946,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>30 kapslar</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4977,32 +4972,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128792112</v>
+        <v>128792106</v>
       </c>
       <c r="B45" t="n">
-        <v>92840</v>
+        <v>96148</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4368</v>
+        <v>210</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5012,10 +5007,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>631814</v>
+        <v>631759</v>
       </c>
       <c r="R45" t="n">
-        <v>6661721</v>
+        <v>6661865</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5048,6 +5043,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>30 kapslar</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5077,7 +5077,7 @@
         <v>128792097</v>
       </c>
       <c r="B46" t="n">
-        <v>96951</v>
+        <v>96952</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5365,32 +5365,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128792104</v>
+        <v>128792114</v>
       </c>
       <c r="B49" t="n">
-        <v>92824</v>
+        <v>100895</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>788</v>
+        <v>222498</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5400,10 +5400,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>631748</v>
+        <v>631859</v>
       </c>
       <c r="R49" t="n">
-        <v>6661858</v>
+        <v>6661778</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5462,32 +5462,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128792114</v>
+        <v>128792104</v>
       </c>
       <c r="B50" t="n">
-        <v>100894</v>
+        <v>92824</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222498</v>
+        <v>788</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5497,10 +5497,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>631859</v>
+        <v>631748</v>
       </c>
       <c r="R50" t="n">
-        <v>6661778</v>
+        <v>6661858</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5659,7 +5659,7 @@
         <v>128792110</v>
       </c>
       <c r="B52" t="n">
-        <v>96194</v>
+        <v>96195</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5756,7 +5756,7 @@
         <v>128792113</v>
       </c>
       <c r="B53" t="n">
-        <v>100894</v>
+        <v>100895</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 41611-2025 artfynd.xlsx
+++ b/artfynd/A 41611-2025 artfynd.xlsx
@@ -3357,7 +3357,7 @@
         <v>128493881</v>
       </c>
       <c r="B29" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 41611-2025 artfynd.xlsx
+++ b/artfynd/A 41611-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY53"/>
+  <dimension ref="A1:AY64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5848,6 +5848,1180 @@
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>129727473</v>
+      </c>
+      <c r="B54" t="n">
+        <v>57732</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Risboskogen nr, sydväst, Upl</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>631757</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6661818</v>
+      </c>
+      <c r="S54" t="n">
+        <v>1</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Hack</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Johanna Dalmalm</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Johanna Dalmalm</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>129725210</v>
+      </c>
+      <c r="B55" t="n">
+        <v>75187</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Kungsängsbergen, Upl</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>631551</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6661824</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>129727475</v>
+      </c>
+      <c r="B56" t="n">
+        <v>97639</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Risboskogen nr, sydväst, Upl</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>631546</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6661864</v>
+      </c>
+      <c r="S56" t="n">
+        <v>1</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Johanna Dalmalm</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Johanna Dalmalm</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>129720291</v>
+      </c>
+      <c r="B57" t="n">
+        <v>75059</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6428</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Rostfläck</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Arthonia vinosa</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Risboskogens NR Sydväst om, Upl</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>631822</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6661808</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Rikligt, basen klibbal. Glupstråk. Foton.</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>129727478</v>
+      </c>
+      <c r="B58" t="n">
+        <v>98768</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Risboskogen nr, sydväst, Upl</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>631609</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6661841</v>
+      </c>
+      <c r="S58" t="n">
+        <v>1</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Johanna Dalmalm</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Johanna Dalmalm</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>129727479</v>
+      </c>
+      <c r="B59" t="n">
+        <v>98768</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Risboskogen nr, sydväst, Upl</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>631607</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6661842</v>
+      </c>
+      <c r="S59" t="n">
+        <v>1</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Johanna Dalmalm</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Johanna Dalmalm</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>129740781</v>
+      </c>
+      <c r="B60" t="n">
+        <v>98768</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Söder om Risboskogens NR, Upl</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>631757</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6661750</v>
+      </c>
+      <c r="S60" t="n">
+        <v>15</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>129719077</v>
+      </c>
+      <c r="B61" t="n">
+        <v>91885</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>658</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Risboskogens NR Sydväst om, Upl</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>631795</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6661899</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Största fruktkrp 85 mm bred! Inom avverkningsanmälan, lågan ligger utanför naturvårdssnitslat klibbalkärr. Foton</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>129740788</v>
+      </c>
+      <c r="B62" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Söder om Risboskogens NR, Upl</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>631768</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6661758</v>
+      </c>
+      <c r="S62" t="n">
+        <v>15</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>129729709</v>
+      </c>
+      <c r="B63" t="n">
+        <v>75059</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>6428</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Rostfläck</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Arthonia vinosa</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Risboskogen NR SV om, Upl</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>631816</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6661829</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Klibbal i kanten av våtmark med nga decimeter djupt vatten. Glupliknande miljö. Naturvårdssnitslat dikt an eller med enstaka meters hänsynszon.  Riktigt fin miljö hela fuktstråket nedströms med kringliggande skog som UAF har avverkningsanmält.</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>129740776</v>
+      </c>
+      <c r="B64" t="n">
+        <v>91551</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Söder om Risboskogens NR, Upl</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>631764</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6661826</v>
+      </c>
+      <c r="S64" t="n">
+        <v>15</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41611-2025 artfynd.xlsx
+++ b/artfynd/A 41611-2025 artfynd.xlsx
@@ -5853,7 +5853,7 @@
         <v>129727473</v>
       </c>
       <c r="B54" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>129725210</v>
       </c>
       <c r="B55" t="n">
-        <v>75187</v>
+        <v>75188</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6070,7 +6070,7 @@
         <v>129727475</v>
       </c>
       <c r="B56" t="n">
-        <v>97639</v>
+        <v>97640</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6167,7 +6167,7 @@
         <v>129720291</v>
       </c>
       <c r="B57" t="n">
-        <v>75059</v>
+        <v>75060</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6279,7 +6279,7 @@
         <v>129727478</v>
       </c>
       <c r="B58" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         <v>129727479</v>
       </c>
       <c r="B59" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6499,7 +6499,7 @@
         <v>129740781</v>
       </c>
       <c r="B60" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6596,7 +6596,7 @@
         <v>129719077</v>
       </c>
       <c r="B61" t="n">
-        <v>91885</v>
+        <v>91886</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6814,7 +6814,7 @@
         <v>129729709</v>
       </c>
       <c r="B63" t="n">
-        <v>75059</v>
+        <v>75060</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6930,7 +6930,7 @@
         <v>129740776</v>
       </c>
       <c r="B64" t="n">
-        <v>91551</v>
+        <v>91552</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 41611-2025 artfynd.xlsx
+++ b/artfynd/A 41611-2025 artfynd.xlsx
@@ -5963,7 +5963,7 @@
         <v>129725210</v>
       </c>
       <c r="B55" t="n">
-        <v>75188</v>
+        <v>75193</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6070,7 +6070,7 @@
         <v>129727475</v>
       </c>
       <c r="B56" t="n">
-        <v>97640</v>
+        <v>97645</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6167,7 +6167,7 @@
         <v>129720291</v>
       </c>
       <c r="B57" t="n">
-        <v>75060</v>
+        <v>75065</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6279,7 +6279,7 @@
         <v>129727478</v>
       </c>
       <c r="B58" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         <v>129727479</v>
       </c>
       <c r="B59" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6499,7 +6499,7 @@
         <v>129740781</v>
       </c>
       <c r="B60" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6596,7 +6596,7 @@
         <v>129719077</v>
       </c>
       <c r="B61" t="n">
-        <v>91886</v>
+        <v>91891</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6814,7 +6814,7 @@
         <v>129729709</v>
       </c>
       <c r="B63" t="n">
-        <v>75060</v>
+        <v>75065</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6930,7 +6930,7 @@
         <v>129740776</v>
       </c>
       <c r="B64" t="n">
-        <v>91552</v>
+        <v>91557</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 41611-2025 artfynd.xlsx
+++ b/artfynd/A 41611-2025 artfynd.xlsx
@@ -6070,7 +6070,7 @@
         <v>129727475</v>
       </c>
       <c r="B56" t="n">
-        <v>97645</v>
+        <v>97649</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6279,7 +6279,7 @@
         <v>129727478</v>
       </c>
       <c r="B58" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         <v>129727479</v>
       </c>
       <c r="B59" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6499,7 +6499,7 @@
         <v>129740781</v>
       </c>
       <c r="B60" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6596,7 +6596,7 @@
         <v>129719077</v>
       </c>
       <c r="B61" t="n">
-        <v>91891</v>
+        <v>91895</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6930,7 +6930,7 @@
         <v>129740776</v>
       </c>
       <c r="B64" t="n">
-        <v>91557</v>
+        <v>91561</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 41611-2025 artfynd.xlsx
+++ b/artfynd/A 41611-2025 artfynd.xlsx
@@ -6070,7 +6070,7 @@
         <v>129727475</v>
       </c>
       <c r="B56" t="n">
-        <v>97649</v>
+        <v>97651</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6279,7 +6279,7 @@
         <v>129727478</v>
       </c>
       <c r="B58" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         <v>129727479</v>
       </c>
       <c r="B59" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6499,7 +6499,7 @@
         <v>129740781</v>
       </c>
       <c r="B60" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6596,7 +6596,7 @@
         <v>129719077</v>
       </c>
       <c r="B61" t="n">
-        <v>91895</v>
+        <v>91897</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6930,7 +6930,7 @@
         <v>129740776</v>
       </c>
       <c r="B64" t="n">
-        <v>91561</v>
+        <v>91563</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 41611-2025 artfynd.xlsx
+++ b/artfynd/A 41611-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY64"/>
+  <dimension ref="A1:AY69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7022,6 +7022,591 @@
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>129906687</v>
+      </c>
+      <c r="B65" t="n">
+        <v>91372</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Risboskogen NR SV om, Upl</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>631690</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6661900</v>
+      </c>
+      <c r="S65" t="n">
+        <v>15</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>129906451</v>
+      </c>
+      <c r="B66" t="n">
+        <v>97031</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>53</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Risboskogen NR SV om, Upl</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>631739</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6661912</v>
+      </c>
+      <c r="S66" t="n">
+        <v>9</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Foton</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>129906047</v>
+      </c>
+      <c r="B67" t="n">
+        <v>75065</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>6428</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Rostfläck</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Arthonia vinosa</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Risboskogen NR SV om, Upl</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>631774</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6661912</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>På klibbal i utkanten av kärr.</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>klibbal</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>129906140</v>
+      </c>
+      <c r="B68" t="n">
+        <v>75193</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Risboskogen NR SV om, Upl</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>631774</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6661912</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Mkt rikligt på 15 cm (bho) klen gran i alsockelkärrkant. Uppåt 3 kvadratdecimeter bålyta!</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>129900942</v>
+      </c>
+      <c r="B69" t="n">
+        <v>105851</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Risboskogen NR SV om, Upl</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>631560</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6661805</v>
+      </c>
+      <c r="S69" t="n">
+        <v>5</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41611-2025 artfynd.xlsx
+++ b/artfynd/A 41611-2025 artfynd.xlsx
@@ -6070,7 +6070,7 @@
         <v>129727475</v>
       </c>
       <c r="B56" t="n">
-        <v>97651</v>
+        <v>97661</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6279,7 +6279,7 @@
         <v>129727478</v>
       </c>
       <c r="B58" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         <v>129727479</v>
       </c>
       <c r="B59" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6499,7 +6499,7 @@
         <v>129740781</v>
       </c>
       <c r="B60" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7134,7 +7134,7 @@
         <v>129906451</v>
       </c>
       <c r="B66" t="n">
-        <v>97031</v>
+        <v>97036</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7505,7 +7505,7 @@
         <v>129900942</v>
       </c>
       <c r="B69" t="n">
-        <v>105851</v>
+        <v>105856</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 41611-2025 artfynd.xlsx
+++ b/artfynd/A 41611-2025 artfynd.xlsx
@@ -6499,7 +6499,7 @@
         <v>129740781</v>
       </c>
       <c r="B60" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6596,7 +6596,7 @@
         <v>129719077</v>
       </c>
       <c r="B61" t="n">
-        <v>91897</v>
+        <v>91900</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6814,7 +6814,7 @@
         <v>129729709</v>
       </c>
       <c r="B63" t="n">
-        <v>75065</v>
+        <v>75068</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6930,7 +6930,7 @@
         <v>129740776</v>
       </c>
       <c r="B64" t="n">
-        <v>91563</v>
+        <v>91566</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7027,7 +7027,7 @@
         <v>129906687</v>
       </c>
       <c r="B65" t="n">
-        <v>91372</v>
+        <v>91375</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7134,7 +7134,7 @@
         <v>129906451</v>
       </c>
       <c r="B66" t="n">
-        <v>97036</v>
+        <v>97040</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7246,7 +7246,7 @@
         <v>129906047</v>
       </c>
       <c r="B67" t="n">
-        <v>75065</v>
+        <v>75068</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7377,7 +7377,7 @@
         <v>129906140</v>
       </c>
       <c r="B68" t="n">
-        <v>75193</v>
+        <v>75196</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7505,7 +7505,7 @@
         <v>129900942</v>
       </c>
       <c r="B69" t="n">
-        <v>105856</v>
+        <v>105860</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 41611-2025 artfynd.xlsx
+++ b/artfynd/A 41611-2025 artfynd.xlsx
@@ -5853,7 +5853,7 @@
         <v>129727473</v>
       </c>
       <c r="B54" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>129725210</v>
       </c>
       <c r="B55" t="n">
-        <v>75193</v>
+        <v>75196</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6070,7 +6070,7 @@
         <v>129727475</v>
       </c>
       <c r="B56" t="n">
-        <v>97661</v>
+        <v>97665</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6167,7 +6167,7 @@
         <v>129720291</v>
       </c>
       <c r="B57" t="n">
-        <v>75065</v>
+        <v>75068</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6279,7 +6279,7 @@
         <v>129727478</v>
       </c>
       <c r="B58" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         <v>129727479</v>
       </c>
       <c r="B59" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 41611-2025 artfynd.xlsx
+++ b/artfynd/A 41611-2025 artfynd.xlsx
@@ -5853,7 +5853,7 @@
         <v>129727473</v>
       </c>
       <c r="B54" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>129725210</v>
       </c>
       <c r="B55" t="n">
-        <v>75196</v>
+        <v>75199</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6070,7 +6070,7 @@
         <v>129727475</v>
       </c>
       <c r="B56" t="n">
-        <v>97665</v>
+        <v>97668</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6167,7 +6167,7 @@
         <v>129720291</v>
       </c>
       <c r="B57" t="n">
-        <v>75068</v>
+        <v>75071</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6279,7 +6279,7 @@
         <v>129727478</v>
       </c>
       <c r="B58" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         <v>129727479</v>
       </c>
       <c r="B59" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6499,7 +6499,7 @@
         <v>129740781</v>
       </c>
       <c r="B60" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6596,7 +6596,7 @@
         <v>129719077</v>
       </c>
       <c r="B61" t="n">
-        <v>91900</v>
+        <v>91903</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6814,7 +6814,7 @@
         <v>129729709</v>
       </c>
       <c r="B63" t="n">
-        <v>75068</v>
+        <v>75071</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6930,7 +6930,7 @@
         <v>129740776</v>
       </c>
       <c r="B64" t="n">
-        <v>91566</v>
+        <v>91569</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7027,7 +7027,7 @@
         <v>129906687</v>
       </c>
       <c r="B65" t="n">
-        <v>91375</v>
+        <v>91378</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7134,7 +7134,7 @@
         <v>129906451</v>
       </c>
       <c r="B66" t="n">
-        <v>97040</v>
+        <v>97043</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7246,7 +7246,7 @@
         <v>129906047</v>
       </c>
       <c r="B67" t="n">
-        <v>75068</v>
+        <v>75071</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7377,7 +7377,7 @@
         <v>129906140</v>
       </c>
       <c r="B68" t="n">
-        <v>75196</v>
+        <v>75199</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7505,7 +7505,7 @@
         <v>129900942</v>
       </c>
       <c r="B69" t="n">
-        <v>105860</v>
+        <v>105863</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 41611-2025 artfynd.xlsx
+++ b/artfynd/A 41611-2025 artfynd.xlsx
@@ -6070,7 +6070,7 @@
         <v>129727475</v>
       </c>
       <c r="B56" t="n">
-        <v>97668</v>
+        <v>97669</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6279,7 +6279,7 @@
         <v>129727478</v>
       </c>
       <c r="B58" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         <v>129727479</v>
       </c>
       <c r="B59" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6499,7 +6499,7 @@
         <v>129740781</v>
       </c>
       <c r="B60" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6596,7 +6596,7 @@
         <v>129719077</v>
       </c>
       <c r="B61" t="n">
-        <v>91903</v>
+        <v>91904</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6930,7 +6930,7 @@
         <v>129740776</v>
       </c>
       <c r="B64" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7027,7 +7027,7 @@
         <v>129906687</v>
       </c>
       <c r="B65" t="n">
-        <v>91378</v>
+        <v>91379</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7134,7 +7134,7 @@
         <v>129906451</v>
       </c>
       <c r="B66" t="n">
-        <v>97043</v>
+        <v>97044</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7505,7 +7505,7 @@
         <v>129900942</v>
       </c>
       <c r="B69" t="n">
-        <v>105863</v>
+        <v>105864</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 41611-2025 artfynd.xlsx
+++ b/artfynd/A 41611-2025 artfynd.xlsx
@@ -5963,7 +5963,7 @@
         <v>129725210</v>
       </c>
       <c r="B55" t="n">
-        <v>75199</v>
+        <v>75200</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6070,7 +6070,7 @@
         <v>129727475</v>
       </c>
       <c r="B56" t="n">
-        <v>97669</v>
+        <v>97686</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6167,7 +6167,7 @@
         <v>129720291</v>
       </c>
       <c r="B57" t="n">
-        <v>75071</v>
+        <v>75072</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6279,7 +6279,7 @@
         <v>129727478</v>
       </c>
       <c r="B58" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         <v>129727479</v>
       </c>
       <c r="B59" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6499,7 +6499,7 @@
         <v>129740781</v>
       </c>
       <c r="B60" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6596,7 +6596,7 @@
         <v>129719077</v>
       </c>
       <c r="B61" t="n">
-        <v>91904</v>
+        <v>91921</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6814,7 +6814,7 @@
         <v>129729709</v>
       </c>
       <c r="B63" t="n">
-        <v>75071</v>
+        <v>75072</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6930,7 +6930,7 @@
         <v>129740776</v>
       </c>
       <c r="B64" t="n">
-        <v>91570</v>
+        <v>91587</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7027,7 +7027,7 @@
         <v>129906687</v>
       </c>
       <c r="B65" t="n">
-        <v>91379</v>
+        <v>91396</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7134,7 +7134,7 @@
         <v>129906451</v>
       </c>
       <c r="B66" t="n">
-        <v>97044</v>
+        <v>97061</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7246,7 +7246,7 @@
         <v>129906047</v>
       </c>
       <c r="B67" t="n">
-        <v>75071</v>
+        <v>75072</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7377,7 +7377,7 @@
         <v>129906140</v>
       </c>
       <c r="B68" t="n">
-        <v>75199</v>
+        <v>75200</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7505,7 +7505,7 @@
         <v>129900942</v>
       </c>
       <c r="B69" t="n">
-        <v>105864</v>
+        <v>105881</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 41611-2025 artfynd.xlsx
+++ b/artfynd/A 41611-2025 artfynd.xlsx
@@ -7027,7 +7027,7 @@
         <v>129906687</v>
       </c>
       <c r="B65" t="n">
-        <v>91412</v>
+        <v>91414</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7134,7 +7134,7 @@
         <v>129906451</v>
       </c>
       <c r="B66" t="n">
-        <v>97077</v>
+        <v>97079</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7505,7 +7505,7 @@
         <v>129900942</v>
       </c>
       <c r="B69" t="n">
-        <v>105897</v>
+        <v>105900</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 41611-2025 artfynd.xlsx
+++ b/artfynd/A 41611-2025 artfynd.xlsx
@@ -7027,7 +7027,7 @@
         <v>129906687</v>
       </c>
       <c r="B65" t="n">
-        <v>91414</v>
+        <v>91501</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7134,7 +7134,7 @@
         <v>129906451</v>
       </c>
       <c r="B66" t="n">
-        <v>97079</v>
+        <v>97166</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7246,7 +7246,7 @@
         <v>129906047</v>
       </c>
       <c r="B67" t="n">
-        <v>75073</v>
+        <v>75158</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7377,7 +7377,7 @@
         <v>129906140</v>
       </c>
       <c r="B68" t="n">
-        <v>75201</v>
+        <v>75286</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7505,7 +7505,7 @@
         <v>129900942</v>
       </c>
       <c r="B69" t="n">
-        <v>105900</v>
+        <v>105987</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 41611-2025 artfynd.xlsx
+++ b/artfynd/A 41611-2025 artfynd.xlsx
@@ -7612,7 +7612,7 @@
         <v>131268322</v>
       </c>
       <c r="B70" t="n">
-        <v>83209</v>
+        <v>83211</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>131268316</v>
       </c>
       <c r="B71" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         <v>131268315</v>
       </c>
       <c r="B72" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7919,7 +7919,7 @@
         <v>131268317</v>
       </c>
       <c r="B73" t="n">
-        <v>92273</v>
+        <v>92275</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8016,7 +8016,7 @@
         <v>131268314</v>
       </c>
       <c r="B74" t="n">
-        <v>97259</v>
+        <v>97261</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
         <v>131268321</v>
       </c>
       <c r="B75" t="n">
-        <v>57064</v>
+        <v>57066</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 41611-2025 artfynd.xlsx
+++ b/artfynd/A 41611-2025 artfynd.xlsx
@@ -7612,7 +7612,7 @@
         <v>131268322</v>
       </c>
       <c r="B70" t="n">
-        <v>83211</v>
+        <v>83212</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>131268316</v>
       </c>
       <c r="B71" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         <v>131268315</v>
       </c>
       <c r="B72" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7919,7 +7919,7 @@
         <v>131268317</v>
       </c>
       <c r="B73" t="n">
-        <v>92275</v>
+        <v>92276</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8016,7 +8016,7 @@
         <v>131268314</v>
       </c>
       <c r="B74" t="n">
-        <v>97261</v>
+        <v>97262</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
         <v>131268321</v>
       </c>
       <c r="B75" t="n">
-        <v>57066</v>
+        <v>57067</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 41611-2025 artfynd.xlsx
+++ b/artfynd/A 41611-2025 artfynd.xlsx
@@ -8233,7 +8233,7 @@
         <v>131894430</v>
       </c>
       <c r="B76" t="n">
-        <v>101301</v>
+        <v>101304</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8444,7 +8444,7 @@
         <v>131890776</v>
       </c>
       <c r="B78" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8551,7 +8551,7 @@
         <v>131890774</v>
       </c>
       <c r="B79" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8655,10 +8655,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131890762</v>
+        <v>131890767</v>
       </c>
       <c r="B80" t="n">
-        <v>91889</v>
+        <v>57945</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8666,34 +8666,42 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Risboskogens nr, söder om, Upl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>631785</v>
+        <v>631834</v>
       </c>
       <c r="R80" t="n">
-        <v>6661901</v>
+        <v>6661821</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -8752,10 +8760,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131890777</v>
+        <v>131890753</v>
       </c>
       <c r="B81" t="n">
-        <v>57127</v>
+        <v>97338</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8763,42 +8771,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>102612</v>
+        <v>53</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Risboskogens nr, söder om, Upl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>631980</v>
+        <v>631602</v>
       </c>
       <c r="R81" t="n">
-        <v>6661999</v>
+        <v>6661856</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -8831,11 +8831,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Spillningshög med blindtarmstömning</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8862,10 +8857,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>131890753</v>
+        <v>131890762</v>
       </c>
       <c r="B82" t="n">
-        <v>97335</v>
+        <v>91892</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8873,21 +8868,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8897,10 +8892,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>631602</v>
+        <v>631785</v>
       </c>
       <c r="R82" t="n">
-        <v>6661856</v>
+        <v>6661901</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -8959,10 +8954,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>131890767</v>
+        <v>131890777</v>
       </c>
       <c r="B83" t="n">
-        <v>57945</v>
+        <v>57127</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8970,16 +8965,16 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -8992,7 +8987,7 @@
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N83" t="inlineStr"/>
@@ -9002,10 +8997,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>631834</v>
+        <v>631980</v>
       </c>
       <c r="R83" t="n">
-        <v>6661821</v>
+        <v>6661999</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -9038,6 +9033,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Spillningshög med blindtarmstömning</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9067,7 +9067,7 @@
         <v>131890788</v>
       </c>
       <c r="B84" t="n">
-        <v>96578</v>
+        <v>96581</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9164,7 +9164,7 @@
         <v>131890760</v>
       </c>
       <c r="B85" t="n">
-        <v>91852</v>
+        <v>91855</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9261,7 +9261,7 @@
         <v>131890757</v>
       </c>
       <c r="B86" t="n">
-        <v>91852</v>
+        <v>91855</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9583,7 +9583,7 @@
         <v>131894431</v>
       </c>
       <c r="B89" t="n">
-        <v>101301</v>
+        <v>101304</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9677,45 +9677,45 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>131890761</v>
+        <v>131894428</v>
       </c>
       <c r="B90" t="n">
-        <v>79934</v>
+        <v>80457</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6453</v>
+        <v>6463</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Risboskogens nr, söder om, Upl</t>
+          <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>631501</v>
+        <v>631897</v>
       </c>
       <c r="R90" t="n">
-        <v>6661799</v>
+        <v>6661723</v>
       </c>
       <c r="S90" t="n">
         <v>15</v>
@@ -9742,12 +9742,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9774,45 +9774,45 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>131894428</v>
+        <v>131890761</v>
       </c>
       <c r="B91" t="n">
-        <v>80455</v>
+        <v>79936</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6463</v>
+        <v>6453</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Risboskogen, Upl</t>
+          <t>Risboskogens nr, söder om, Upl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>631897</v>
+        <v>631501</v>
       </c>
       <c r="R91" t="n">
-        <v>6661723</v>
+        <v>6661799</v>
       </c>
       <c r="S91" t="n">
         <v>15</v>
@@ -9839,12 +9839,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9874,7 +9874,7 @@
         <v>131894427</v>
       </c>
       <c r="B92" t="n">
-        <v>96403</v>
+        <v>96406</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9971,7 +9971,7 @@
         <v>131894429</v>
       </c>
       <c r="B93" t="n">
-        <v>83287</v>
+        <v>83289</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>131890780</v>
       </c>
       <c r="B94" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10165,7 +10165,7 @@
         <v>131890758</v>
       </c>
       <c r="B95" t="n">
-        <v>91852</v>
+        <v>91855</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10262,7 +10262,7 @@
         <v>131890786</v>
       </c>
       <c r="B96" t="n">
-        <v>96403</v>
+        <v>96406</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10356,10 +10356,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>131890772</v>
+        <v>131890778</v>
       </c>
       <c r="B97" t="n">
-        <v>80380</v>
+        <v>96534</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10367,34 +10367,46 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>229497</v>
+        <v>210</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Risboskogens nr, söder om, Upl</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>632024</v>
+        <v>631545</v>
       </c>
       <c r="R97" t="n">
-        <v>6661958</v>
+        <v>6661872</v>
       </c>
       <c r="S97" t="n">
         <v>15</v>
@@ -10435,6 +10447,7 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -10453,49 +10466,45 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>131890775</v>
+        <v>131890789</v>
       </c>
       <c r="B98" t="n">
-        <v>99095</v>
+        <v>83289</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Risboskogens nr, söder om, Upl</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>631932</v>
+        <v>631544</v>
       </c>
       <c r="R98" t="n">
-        <v>6661790</v>
+        <v>6661863</v>
       </c>
       <c r="S98" t="n">
         <v>15</v>
@@ -10530,18 +10539,12 @@
           <t>2026-03-23</t>
         </is>
       </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Mer än 20 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -10563,7 +10566,7 @@
         <v>131890779</v>
       </c>
       <c r="B99" t="n">
-        <v>91903</v>
+        <v>91906</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10657,32 +10660,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>131890789</v>
+        <v>131890772</v>
       </c>
       <c r="B100" t="n">
-        <v>83287</v>
+        <v>80382</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>308</v>
+        <v>229497</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10692,10 +10695,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>631544</v>
+        <v>632024</v>
       </c>
       <c r="R100" t="n">
-        <v>6661863</v>
+        <v>6661958</v>
       </c>
       <c r="S100" t="n">
         <v>15</v>
@@ -10754,44 +10757,36 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>131890778</v>
+        <v>131890775</v>
       </c>
       <c r="B101" t="n">
-        <v>96531</v>
+        <v>99098</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>210</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr"/>
       <c r="L101" t="inlineStr"/>
       <c r="N101" t="inlineStr"/>
@@ -10801,10 +10796,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>631545</v>
+        <v>631932</v>
       </c>
       <c r="R101" t="n">
-        <v>6661872</v>
+        <v>6661790</v>
       </c>
       <c r="S101" t="n">
         <v>15</v>
@@ -10837,6 +10832,11 @@
       <c r="AA101" t="inlineStr">
         <is>
           <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Mer än 20 bladrosetter</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10974,32 +10974,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>131890759</v>
+        <v>131890754</v>
       </c>
       <c r="B103" t="n">
-        <v>91852</v>
+        <v>97338</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11009,10 +11009,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>631607</v>
+        <v>631584</v>
       </c>
       <c r="R103" t="n">
-        <v>6661856</v>
+        <v>6661788</v>
       </c>
       <c r="S103" t="n">
         <v>15</v>
@@ -11071,32 +11071,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>131890754</v>
+        <v>131890759</v>
       </c>
       <c r="B104" t="n">
-        <v>97335</v>
+        <v>91855</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11106,10 +11106,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>631584</v>
+        <v>631607</v>
       </c>
       <c r="R104" t="n">
-        <v>6661788</v>
+        <v>6661856</v>
       </c>
       <c r="S104" t="n">
         <v>15</v>
@@ -11168,45 +11168,49 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>131890755</v>
+        <v>131890773</v>
       </c>
       <c r="B105" t="n">
-        <v>97335</v>
+        <v>99098</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Risboskogens nr, söder om, Upl</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>631573</v>
+        <v>632005</v>
       </c>
       <c r="R105" t="n">
-        <v>6661854</v>
+        <v>6661952</v>
       </c>
       <c r="S105" t="n">
         <v>15</v>
@@ -11241,12 +11245,18 @@
           <t>2026-03-23</t>
         </is>
       </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Ett fåtal bladrosetter</t>
+        </is>
+      </c>
       <c r="AD105" t="b">
         <v>0</v>
       </c>
       <c r="AE105" t="b">
         <v>0</v>
       </c>
+      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
@@ -11265,56 +11275,48 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>131890768</v>
+        <v>131890787</v>
       </c>
       <c r="B106" t="n">
-        <v>57945</v>
+        <v>96581</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100049</v>
+        <v>2170</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Risboskogens nr, söder om, Upl</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>631613</v>
+        <v>631600</v>
       </c>
       <c r="R106" t="n">
-        <v>6661765</v>
+        <v>6661750</v>
       </c>
       <c r="S106" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11370,32 +11372,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>131890787</v>
+        <v>131890755</v>
       </c>
       <c r="B107" t="n">
-        <v>96578</v>
+        <v>97338</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>2170</v>
+        <v>53</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11405,10 +11407,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>631600</v>
+        <v>631573</v>
       </c>
       <c r="R107" t="n">
-        <v>6661750</v>
+        <v>6661854</v>
       </c>
       <c r="S107" t="n">
         <v>15</v>
@@ -11467,38 +11469,42 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>131890773</v>
+        <v>131890768</v>
       </c>
       <c r="B108" t="n">
-        <v>99095</v>
+        <v>57945</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
@@ -11506,13 +11512,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>632005</v>
+        <v>631613</v>
       </c>
       <c r="R108" t="n">
-        <v>6661952</v>
+        <v>6661765</v>
       </c>
       <c r="S108" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11544,18 +11550,12 @@
           <t>2026-03-23</t>
         </is>
       </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>Ett fåtal bladrosetter</t>
-        </is>
-      </c>
       <c r="AD108" t="b">
         <v>0</v>
       </c>
       <c r="AE108" t="b">
         <v>0</v>
       </c>
-      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -11577,7 +11577,7 @@
         <v>131890771</v>
       </c>
       <c r="B109" t="n">
-        <v>81300</v>
+        <v>81302</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11678,7 +11678,7 @@
         <v>131890766</v>
       </c>
       <c r="B110" t="n">
-        <v>96437</v>
+        <v>96440</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11780,7 +11780,7 @@
         <v>132247080</v>
       </c>
       <c r="B111" t="n">
-        <v>97335</v>
+        <v>97338</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11877,7 +11877,7 @@
         <v>132247084</v>
       </c>
       <c r="B112" t="n">
-        <v>81300</v>
+        <v>81302</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11974,7 +11974,7 @@
         <v>132247081</v>
       </c>
       <c r="B113" t="n">
-        <v>97335</v>
+        <v>97338</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12068,49 +12068,45 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>132247086</v>
+        <v>132247087</v>
       </c>
       <c r="B114" t="n">
-        <v>99095</v>
+        <v>96581</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>220787</v>
+        <v>2170</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
-      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>632060</v>
+        <v>632046</v>
       </c>
       <c r="R114" t="n">
-        <v>6661605</v>
+        <v>6661591</v>
       </c>
       <c r="S114" t="n">
         <v>15</v>
@@ -12145,18 +12141,12 @@
           <t>2026-04-06</t>
         </is>
       </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>3 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD114" t="b">
         <v>0</v>
       </c>
       <c r="AE114" t="b">
         <v>0</v>
       </c>
-      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
@@ -12175,10 +12165,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>132247085</v>
+        <v>132247086</v>
       </c>
       <c r="B115" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12204,16 +12194,20 @@
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>632051</v>
+        <v>632060</v>
       </c>
       <c r="R115" t="n">
-        <v>6661556</v>
+        <v>6661605</v>
       </c>
       <c r="S115" t="n">
         <v>15</v>
@@ -12250,7 +12244,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>20 tal bladrosetter</t>
+          <t>3 bladrosetter</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12259,6 +12253,7 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
+      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
@@ -12277,32 +12272,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>132247087</v>
+        <v>132247085</v>
       </c>
       <c r="B116" t="n">
-        <v>96578</v>
+        <v>99098</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>2170</v>
+        <v>220787</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12312,10 +12307,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>632046</v>
+        <v>632051</v>
       </c>
       <c r="R116" t="n">
-        <v>6661591</v>
+        <v>6661556</v>
       </c>
       <c r="S116" t="n">
         <v>15</v>
@@ -12348,6 +12343,11 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>20 tal bladrosetter</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12587,7 +12587,7 @@
         <v>132286086</v>
       </c>
       <c r="B119" t="n">
-        <v>101301</v>
+        <v>101304</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12789,7 +12789,7 @@
         <v>132286080</v>
       </c>
       <c r="B121" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12899,7 +12899,7 @@
         <v>132286078</v>
       </c>
       <c r="B122" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13009,7 +13009,7 @@
         <v>132286088</v>
       </c>
       <c r="B123" t="n">
-        <v>101301</v>
+        <v>101304</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13106,7 +13106,7 @@
         <v>132410204</v>
       </c>
       <c r="B124" t="n">
-        <v>58107</v>
+        <v>58109</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>

--- a/artfynd/A 41611-2025 artfynd.xlsx
+++ b/artfynd/A 41611-2025 artfynd.xlsx
@@ -9161,45 +9161,53 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131890760</v>
+        <v>131894426</v>
       </c>
       <c r="B85" t="n">
-        <v>91855</v>
+        <v>57127</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5447</v>
+        <v>102612</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Risboskogens nr, söder om, Upl</t>
+          <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>631513</v>
+        <v>631854</v>
       </c>
       <c r="R85" t="n">
-        <v>6661837</v>
+        <v>6661782</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -9226,12 +9234,17 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>spillning</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9258,10 +9271,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131890757</v>
+        <v>131890769</v>
       </c>
       <c r="B86" t="n">
-        <v>91855</v>
+        <v>57789</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9269,37 +9282,45 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5447</v>
+        <v>102621</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Risboskogens nr, söder om, Upl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>631992</v>
+        <v>631746</v>
       </c>
       <c r="R86" t="n">
-        <v>6661795</v>
+        <v>6661893</v>
       </c>
       <c r="S86" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9326,9 +9347,19 @@
           <t>2026-03-23</t>
         </is>
       </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9355,50 +9386,42 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131894426</v>
+        <v>131894431</v>
       </c>
       <c r="B87" t="n">
-        <v>57127</v>
+        <v>101304</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>102612</v>
+        <v>222498</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>631854</v>
+        <v>631874</v>
       </c>
       <c r="R87" t="n">
         <v>6661782</v>
@@ -9434,11 +9457,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>spillning</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9465,10 +9483,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131890769</v>
+        <v>131890760</v>
       </c>
       <c r="B88" t="n">
-        <v>57789</v>
+        <v>91855</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9476,45 +9494,37 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>102621</v>
+        <v>5447</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Risboskogens nr, söder om, Upl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>631746</v>
+        <v>631513</v>
       </c>
       <c r="R88" t="n">
-        <v>6661893</v>
+        <v>6661837</v>
       </c>
       <c r="S88" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9541,19 +9551,9 @@
           <t>2026-03-23</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>18:30</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9580,10 +9580,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131894431</v>
+        <v>131890757</v>
       </c>
       <c r="B89" t="n">
-        <v>101304</v>
+        <v>91855</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9591,34 +9591,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Risboskogen, Upl</t>
+          <t>Risboskogens nr, söder om, Upl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>631874</v>
+        <v>631992</v>
       </c>
       <c r="R89" t="n">
-        <v>6661782</v>
+        <v>6661795</v>
       </c>
       <c r="S89" t="n">
         <v>15</v>
@@ -9645,12 +9645,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10356,10 +10356,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>131890778</v>
+        <v>131890772</v>
       </c>
       <c r="B97" t="n">
-        <v>96534</v>
+        <v>80382</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10367,46 +10367,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>210</v>
+        <v>229497</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Risboskogens nr, söder om, Upl</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>631545</v>
+        <v>632024</v>
       </c>
       <c r="R97" t="n">
-        <v>6661872</v>
+        <v>6661958</v>
       </c>
       <c r="S97" t="n">
         <v>15</v>
@@ -10447,7 +10435,6 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -10466,45 +10453,57 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>131890789</v>
+        <v>131890778</v>
       </c>
       <c r="B98" t="n">
-        <v>83289</v>
+        <v>96534</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>308</v>
+        <v>210</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Risboskogens nr, söder om, Upl</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>631544</v>
+        <v>631545</v>
       </c>
       <c r="R98" t="n">
-        <v>6661863</v>
+        <v>6661872</v>
       </c>
       <c r="S98" t="n">
         <v>15</v>
@@ -10545,6 +10544,7 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -10563,10 +10563,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>131890779</v>
+        <v>131890789</v>
       </c>
       <c r="B99" t="n">
-        <v>91906</v>
+        <v>83289</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10574,21 +10574,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1204</v>
+        <v>308</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10598,10 +10598,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>631992</v>
+        <v>631544</v>
       </c>
       <c r="R99" t="n">
-        <v>6661795</v>
+        <v>6661863</v>
       </c>
       <c r="S99" t="n">
         <v>15</v>
@@ -10660,32 +10660,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>131890772</v>
+        <v>131890779</v>
       </c>
       <c r="B100" t="n">
-        <v>80382</v>
+        <v>91906</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>229497</v>
+        <v>1204</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10695,10 +10695,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>632024</v>
+        <v>631992</v>
       </c>
       <c r="R100" t="n">
-        <v>6661958</v>
+        <v>6661795</v>
       </c>
       <c r="S100" t="n">
         <v>15</v>
@@ -12068,45 +12068,49 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>132247087</v>
+        <v>132247086</v>
       </c>
       <c r="B114" t="n">
-        <v>96581</v>
+        <v>99098</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>2170</v>
+        <v>220787</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>632046</v>
+        <v>632060</v>
       </c>
       <c r="R114" t="n">
-        <v>6661591</v>
+        <v>6661605</v>
       </c>
       <c r="S114" t="n">
         <v>15</v>
@@ -12141,12 +12145,18 @@
           <t>2026-04-06</t>
         </is>
       </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>3 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD114" t="b">
         <v>0</v>
       </c>
       <c r="AE114" t="b">
         <v>0</v>
       </c>
+      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
@@ -12165,7 +12175,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>132247086</v>
+        <v>132247085</v>
       </c>
       <c r="B115" t="n">
         <v>99098</v>
@@ -12194,20 +12204,16 @@
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
-      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>632060</v>
+        <v>632051</v>
       </c>
       <c r="R115" t="n">
-        <v>6661605</v>
+        <v>6661556</v>
       </c>
       <c r="S115" t="n">
         <v>15</v>
@@ -12244,7 +12250,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>3 bladrosetter</t>
+          <t>20 tal bladrosetter</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12253,7 +12259,6 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
-      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
@@ -12272,32 +12277,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>132247085</v>
+        <v>132247087</v>
       </c>
       <c r="B116" t="n">
-        <v>99098</v>
+        <v>96581</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>220787</v>
+        <v>2170</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12307,10 +12312,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>632051</v>
+        <v>632046</v>
       </c>
       <c r="R116" t="n">
-        <v>6661556</v>
+        <v>6661591</v>
       </c>
       <c r="S116" t="n">
         <v>15</v>
@@ -12343,11 +12348,6 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>20 tal bladrosetter</t>
         </is>
       </c>
       <c r="AD116" t="b">

--- a/artfynd/A 41611-2025 artfynd.xlsx
+++ b/artfynd/A 41611-2025 artfynd.xlsx
@@ -9161,53 +9161,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131894426</v>
+        <v>131890760</v>
       </c>
       <c r="B85" t="n">
-        <v>57127</v>
+        <v>91855</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>102612</v>
+        <v>5447</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Risboskogen, Upl</t>
+          <t>Risboskogens nr, söder om, Upl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>631854</v>
+        <v>631513</v>
       </c>
       <c r="R85" t="n">
-        <v>6661782</v>
+        <v>6661837</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -9234,17 +9226,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>spillning</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9271,10 +9258,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131890769</v>
+        <v>131890757</v>
       </c>
       <c r="B86" t="n">
-        <v>57789</v>
+        <v>91855</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9282,45 +9269,37 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>102621</v>
+        <v>5447</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Risboskogens nr, söder om, Upl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>631746</v>
+        <v>631992</v>
       </c>
       <c r="R86" t="n">
-        <v>6661893</v>
+        <v>6661795</v>
       </c>
       <c r="S86" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9347,19 +9326,9 @@
           <t>2026-03-23</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>18:30</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9386,42 +9355,50 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131894431</v>
+        <v>131894426</v>
       </c>
       <c r="B87" t="n">
-        <v>101304</v>
+        <v>57127</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>222498</v>
+        <v>102612</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>631874</v>
+        <v>631854</v>
       </c>
       <c r="R87" t="n">
         <v>6661782</v>
@@ -9457,6 +9434,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>spillning</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9483,10 +9465,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131890760</v>
+        <v>131890769</v>
       </c>
       <c r="B88" t="n">
-        <v>91855</v>
+        <v>57789</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9494,37 +9476,45 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>5447</v>
+        <v>102621</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Risboskogens nr, söder om, Upl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>631513</v>
+        <v>631746</v>
       </c>
       <c r="R88" t="n">
-        <v>6661837</v>
+        <v>6661893</v>
       </c>
       <c r="S88" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9551,9 +9541,19 @@
           <t>2026-03-23</t>
         </is>
       </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9580,10 +9580,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131890757</v>
+        <v>131894431</v>
       </c>
       <c r="B89" t="n">
-        <v>91855</v>
+        <v>101304</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9591,34 +9591,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Risboskogens nr, söder om, Upl</t>
+          <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>631992</v>
+        <v>631874</v>
       </c>
       <c r="R89" t="n">
-        <v>6661795</v>
+        <v>6661782</v>
       </c>
       <c r="S89" t="n">
         <v>15</v>
@@ -9645,12 +9645,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="AD89" t="b">

--- a/artfynd/A 41611-2025 artfynd.xlsx
+++ b/artfynd/A 41611-2025 artfynd.xlsx
@@ -8655,10 +8655,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131890767</v>
+        <v>131890762</v>
       </c>
       <c r="B80" t="n">
-        <v>57945</v>
+        <v>91892</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8666,42 +8666,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Risboskogens nr, söder om, Upl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>631834</v>
+        <v>631785</v>
       </c>
       <c r="R80" t="n">
-        <v>6661821</v>
+        <v>6661901</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -8760,10 +8752,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131890753</v>
+        <v>131890777</v>
       </c>
       <c r="B81" t="n">
-        <v>97338</v>
+        <v>57127</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8771,34 +8763,42 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>53</v>
+        <v>102612</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Risboskogens nr, söder om, Upl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>631602</v>
+        <v>631980</v>
       </c>
       <c r="R81" t="n">
-        <v>6661856</v>
+        <v>6661999</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -8831,6 +8831,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Spillningshög med blindtarmstömning</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8857,10 +8862,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>131890762</v>
+        <v>131890767</v>
       </c>
       <c r="B82" t="n">
-        <v>91892</v>
+        <v>57945</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8868,34 +8873,42 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Risboskogens nr, söder om, Upl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>631785</v>
+        <v>631834</v>
       </c>
       <c r="R82" t="n">
-        <v>6661901</v>
+        <v>6661821</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -8954,10 +8967,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>131890777</v>
+        <v>131890753</v>
       </c>
       <c r="B83" t="n">
-        <v>57127</v>
+        <v>97338</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8965,42 +8978,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>102612</v>
+        <v>53</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Risboskogens nr, söder om, Upl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>631980</v>
+        <v>631602</v>
       </c>
       <c r="R83" t="n">
-        <v>6661999</v>
+        <v>6661856</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -9033,11 +9038,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Spillningshög med blindtarmstömning</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9355,50 +9355,42 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131894426</v>
+        <v>131894431</v>
       </c>
       <c r="B87" t="n">
-        <v>57127</v>
+        <v>101304</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>102612</v>
+        <v>222498</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>631854</v>
+        <v>631874</v>
       </c>
       <c r="R87" t="n">
         <v>6661782</v>
@@ -9434,11 +9426,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>spillning</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9465,27 +9452,27 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131890769</v>
+        <v>131894426</v>
       </c>
       <c r="B88" t="n">
-        <v>57789</v>
+        <v>57127</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>102621</v>
+        <v>102612</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -9498,23 +9485,23 @@
       <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Risboskogens nr, söder om, Upl</t>
+          <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>631746</v>
+        <v>631854</v>
       </c>
       <c r="R88" t="n">
-        <v>6661893</v>
+        <v>6661782</v>
       </c>
       <c r="S88" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9538,22 +9525,17 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>17:30</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>18:30</t>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>spillning</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9580,10 +9562,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131894431</v>
+        <v>131890769</v>
       </c>
       <c r="B89" t="n">
-        <v>101304</v>
+        <v>57789</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9591,37 +9573,45 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>222498</v>
+        <v>102621</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Risboskogen, Upl</t>
+          <t>Risboskogens nr, söder om, Upl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>631874</v>
+        <v>631746</v>
       </c>
       <c r="R89" t="n">
-        <v>6661782</v>
+        <v>6661893</v>
       </c>
       <c r="S89" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9645,12 +9635,22 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10356,45 +10356,49 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>131890772</v>
+        <v>131890775</v>
       </c>
       <c r="B97" t="n">
-        <v>80382</v>
+        <v>99098</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Risboskogens nr, söder om, Upl</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>632024</v>
+        <v>631932</v>
       </c>
       <c r="R97" t="n">
-        <v>6661958</v>
+        <v>6661790</v>
       </c>
       <c r="S97" t="n">
         <v>15</v>
@@ -10429,12 +10433,18 @@
           <t>2026-03-23</t>
         </is>
       </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Mer än 20 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -10757,49 +10767,45 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>131890775</v>
+        <v>131890772</v>
       </c>
       <c r="B101" t="n">
-        <v>99098</v>
+        <v>80382</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Risboskogens nr, söder om, Upl</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>631932</v>
+        <v>632024</v>
       </c>
       <c r="R101" t="n">
-        <v>6661790</v>
+        <v>6661958</v>
       </c>
       <c r="S101" t="n">
         <v>15</v>
@@ -10834,18 +10840,12 @@
           <t>2026-03-23</t>
         </is>
       </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Mer än 20 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD101" t="b">
         <v>0</v>
       </c>
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -10974,32 +10974,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>131890754</v>
+        <v>131890759</v>
       </c>
       <c r="B103" t="n">
-        <v>97338</v>
+        <v>91855</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11009,10 +11009,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>631584</v>
+        <v>631607</v>
       </c>
       <c r="R103" t="n">
-        <v>6661788</v>
+        <v>6661856</v>
       </c>
       <c r="S103" t="n">
         <v>15</v>
@@ -11071,32 +11071,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>131890759</v>
+        <v>131890754</v>
       </c>
       <c r="B104" t="n">
-        <v>91855</v>
+        <v>97338</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11106,10 +11106,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>631607</v>
+        <v>631584</v>
       </c>
       <c r="R104" t="n">
-        <v>6661856</v>
+        <v>6661788</v>
       </c>
       <c r="S104" t="n">
         <v>15</v>
@@ -11168,38 +11168,42 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>131890773</v>
+        <v>131890768</v>
       </c>
       <c r="B105" t="n">
-        <v>99098</v>
+        <v>57945</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr"/>
       <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
@@ -11207,13 +11211,13 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>632005</v>
+        <v>631613</v>
       </c>
       <c r="R105" t="n">
-        <v>6661952</v>
+        <v>6661765</v>
       </c>
       <c r="S105" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11245,18 +11249,12 @@
           <t>2026-03-23</t>
         </is>
       </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Ett fåtal bladrosetter</t>
-        </is>
-      </c>
       <c r="AD105" t="b">
         <v>0</v>
       </c>
       <c r="AE105" t="b">
         <v>0</v>
       </c>
-      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
@@ -11372,45 +11370,49 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>131890755</v>
+        <v>131890773</v>
       </c>
       <c r="B107" t="n">
-        <v>97338</v>
+        <v>99098</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Risboskogens nr, söder om, Upl</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>631573</v>
+        <v>632005</v>
       </c>
       <c r="R107" t="n">
-        <v>6661854</v>
+        <v>6661952</v>
       </c>
       <c r="S107" t="n">
         <v>15</v>
@@ -11445,12 +11447,18 @@
           <t>2026-03-23</t>
         </is>
       </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Ett fåtal bladrosetter</t>
+        </is>
+      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
       <c r="AE107" t="b">
         <v>0</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
@@ -11469,10 +11477,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>131890768</v>
+        <v>131890755</v>
       </c>
       <c r="B108" t="n">
-        <v>57945</v>
+        <v>97338</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11480,45 +11488,37 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Risboskogens nr, söder om, Upl</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>631613</v>
+        <v>631573</v>
       </c>
       <c r="R108" t="n">
-        <v>6661765</v>
+        <v>6661854</v>
       </c>
       <c r="S108" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12068,7 +12068,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>132247086</v>
+        <v>132247085</v>
       </c>
       <c r="B114" t="n">
         <v>99098</v>
@@ -12097,20 +12097,16 @@
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
-      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>632060</v>
+        <v>632051</v>
       </c>
       <c r="R114" t="n">
-        <v>6661605</v>
+        <v>6661556</v>
       </c>
       <c r="S114" t="n">
         <v>15</v>
@@ -12147,7 +12143,7 @@
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>3 bladrosetter</t>
+          <t>20 tal bladrosetter</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12156,7 +12152,6 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
-      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
@@ -12175,7 +12170,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>132247085</v>
+        <v>132247086</v>
       </c>
       <c r="B115" t="n">
         <v>99098</v>
@@ -12204,16 +12199,20 @@
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>632051</v>
+        <v>632060</v>
       </c>
       <c r="R115" t="n">
-        <v>6661556</v>
+        <v>6661605</v>
       </c>
       <c r="S115" t="n">
         <v>15</v>
@@ -12250,7 +12249,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>20 tal bladrosetter</t>
+          <t>3 bladrosetter</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12259,6 +12258,7 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
+      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 41611-2025 artfynd.xlsx
+++ b/artfynd/A 41611-2025 artfynd.xlsx
@@ -8655,10 +8655,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131890762</v>
+        <v>131890767</v>
       </c>
       <c r="B80" t="n">
-        <v>91892</v>
+        <v>57945</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8666,34 +8666,42 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Risboskogens nr, söder om, Upl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>631785</v>
+        <v>631834</v>
       </c>
       <c r="R80" t="n">
-        <v>6661901</v>
+        <v>6661821</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -8862,10 +8870,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>131890767</v>
+        <v>131890753</v>
       </c>
       <c r="B82" t="n">
-        <v>57945</v>
+        <v>97338</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8873,42 +8881,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Risboskogens nr, söder om, Upl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>631834</v>
+        <v>631602</v>
       </c>
       <c r="R82" t="n">
-        <v>6661821</v>
+        <v>6661856</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -8967,10 +8967,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>131890753</v>
+        <v>131890762</v>
       </c>
       <c r="B83" t="n">
-        <v>97338</v>
+        <v>91892</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8978,21 +8978,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9002,10 +9002,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>631602</v>
+        <v>631785</v>
       </c>
       <c r="R83" t="n">
-        <v>6661856</v>
+        <v>6661901</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>

--- a/artfynd/A 41611-2025 artfynd.xlsx
+++ b/artfynd/A 41611-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY124"/>
+  <dimension ref="A1:AY133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12068,32 +12068,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>132247085</v>
+        <v>132247087</v>
       </c>
       <c r="B114" t="n">
-        <v>99098</v>
+        <v>96581</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>220787</v>
+        <v>2170</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12103,10 +12103,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>632051</v>
+        <v>632046</v>
       </c>
       <c r="R114" t="n">
-        <v>6661556</v>
+        <v>6661591</v>
       </c>
       <c r="S114" t="n">
         <v>15</v>
@@ -12139,11 +12139,6 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>20 tal bladrosetter</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12170,7 +12165,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>132247086</v>
+        <v>132247085</v>
       </c>
       <c r="B115" t="n">
         <v>99098</v>
@@ -12199,20 +12194,16 @@
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
-      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>632060</v>
+        <v>632051</v>
       </c>
       <c r="R115" t="n">
-        <v>6661605</v>
+        <v>6661556</v>
       </c>
       <c r="S115" t="n">
         <v>15</v>
@@ -12249,7 +12240,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>3 bladrosetter</t>
+          <t>20 tal bladrosetter</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12258,7 +12249,6 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
-      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
@@ -12277,45 +12267,49 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>132247087</v>
+        <v>132247086</v>
       </c>
       <c r="B116" t="n">
-        <v>96581</v>
+        <v>99098</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>2170</v>
+        <v>220787</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>632046</v>
+        <v>632060</v>
       </c>
       <c r="R116" t="n">
-        <v>6661591</v>
+        <v>6661605</v>
       </c>
       <c r="S116" t="n">
         <v>15</v>
@@ -12350,12 +12344,18 @@
           <t>2026-04-06</t>
         </is>
       </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>3 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD116" t="b">
         <v>0</v>
       </c>
       <c r="AE116" t="b">
         <v>0</v>
       </c>
+      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -13220,6 +13220,903 @@
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>132617077</v>
+      </c>
+      <c r="B125" t="n">
+        <v>80382</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Mångelbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q125" t="n">
+        <v>631855</v>
+      </c>
+      <c r="R125" t="n">
+        <v>6661694</v>
+      </c>
+      <c r="S125" t="n">
+        <v>5</v>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AD125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT125" t="inlineStr"/>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>132603522</v>
+      </c>
+      <c r="B126" t="n">
+        <v>80382</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>Kungsängsbergen, Kungsängsbergen, Upl</t>
+        </is>
+      </c>
+      <c r="Q126" t="n">
+        <v>631865</v>
+      </c>
+      <c r="R126" t="n">
+        <v>6661672</v>
+      </c>
+      <c r="S126" t="n">
+        <v>10</v>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AD126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT126" t="inlineStr"/>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>Filippa Paperin</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>Filippa Paperin</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>132617083</v>
+      </c>
+      <c r="B127" t="n">
+        <v>96534</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>210</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>Mångelbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q127" t="n">
+        <v>631854</v>
+      </c>
+      <c r="R127" t="n">
+        <v>6661785</v>
+      </c>
+      <c r="S127" t="n">
+        <v>5</v>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AD127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT127" t="inlineStr"/>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>132617073</v>
+      </c>
+      <c r="B128" t="n">
+        <v>92191</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>658</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Mångelbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q128" t="n">
+        <v>631790</v>
+      </c>
+      <c r="R128" t="n">
+        <v>6661899</v>
+      </c>
+      <c r="S128" t="n">
+        <v>5</v>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AD128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT128" t="inlineStr"/>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>132617066</v>
+      </c>
+      <c r="B129" t="n">
+        <v>97338</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>53</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>Mångelbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q129" t="n">
+        <v>632039</v>
+      </c>
+      <c r="R129" t="n">
+        <v>6661551</v>
+      </c>
+      <c r="S129" t="n">
+        <v>5</v>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AD129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT129" t="inlineStr"/>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>132617068</v>
+      </c>
+      <c r="B130" t="n">
+        <v>91892</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>Mångelbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q130" t="n">
+        <v>631593</v>
+      </c>
+      <c r="R130" t="n">
+        <v>6661917</v>
+      </c>
+      <c r="S130" t="n">
+        <v>5</v>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AD130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT130" t="inlineStr"/>
+      <c r="AW130" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX130" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>132617085</v>
+      </c>
+      <c r="B131" t="n">
+        <v>91906</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>Mångelbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q131" t="n">
+        <v>631731</v>
+      </c>
+      <c r="R131" t="n">
+        <v>6661917</v>
+      </c>
+      <c r="S131" t="n">
+        <v>5</v>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AD131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT131" t="inlineStr"/>
+      <c r="AW131" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX131" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>132606960</v>
+      </c>
+      <c r="B132" t="n">
+        <v>97338</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>53</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>Kungsängsbergen, Upl</t>
+        </is>
+      </c>
+      <c r="Q132" t="n">
+        <v>631979</v>
+      </c>
+      <c r="R132" t="n">
+        <v>6661634</v>
+      </c>
+      <c r="S132" t="n">
+        <v>3</v>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AD132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT132" t="inlineStr"/>
+      <c r="AW132" t="inlineStr">
+        <is>
+          <t>Elvira Klang</t>
+        </is>
+      </c>
+      <c r="AX132" t="inlineStr">
+        <is>
+          <t>Elvira Klang, Tore Dahlberg, Elias Blad, Filippa Paperin</t>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>132617069</v>
+      </c>
+      <c r="B133" t="n">
+        <v>91892</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>Mångelbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q133" t="n">
+        <v>631788</v>
+      </c>
+      <c r="R133" t="n">
+        <v>6661900</v>
+      </c>
+      <c r="S133" t="n">
+        <v>5</v>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AD133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT133" t="inlineStr"/>
+      <c r="AW133" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX133" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41611-2025 artfynd.xlsx
+++ b/artfynd/A 41611-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY133"/>
+  <dimension ref="A1:AY142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10356,49 +10356,45 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>131890775</v>
+        <v>131890772</v>
       </c>
       <c r="B97" t="n">
-        <v>99098</v>
+        <v>80382</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Risboskogens nr, söder om, Upl</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>631932</v>
+        <v>632024</v>
       </c>
       <c r="R97" t="n">
-        <v>6661790</v>
+        <v>6661958</v>
       </c>
       <c r="S97" t="n">
         <v>15</v>
@@ -10433,18 +10429,12 @@
           <t>2026-03-23</t>
         </is>
       </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Mer än 20 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -10767,45 +10757,49 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>131890772</v>
+        <v>131890775</v>
       </c>
       <c r="B101" t="n">
-        <v>80382</v>
+        <v>99098</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Risboskogens nr, söder om, Upl</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>632024</v>
+        <v>631932</v>
       </c>
       <c r="R101" t="n">
-        <v>6661958</v>
+        <v>6661790</v>
       </c>
       <c r="S101" t="n">
         <v>15</v>
@@ -10840,12 +10834,18 @@
           <t>2026-03-23</t>
         </is>
       </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Mer än 20 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD101" t="b">
         <v>0</v>
       </c>
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -14117,6 +14117,978 @@
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>132622046</v>
+      </c>
+      <c r="B134" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>Risbyskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q134" t="n">
+        <v>631888</v>
+      </c>
+      <c r="R134" t="n">
+        <v>6661655</v>
+      </c>
+      <c r="S134" t="n">
+        <v>5</v>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AD134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT134" t="inlineStr"/>
+      <c r="AW134" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX134" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>132622045</v>
+      </c>
+      <c r="B135" t="n">
+        <v>79936</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>Risbyskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q135" t="n">
+        <v>631882</v>
+      </c>
+      <c r="R135" t="n">
+        <v>6661651</v>
+      </c>
+      <c r="S135" t="n">
+        <v>5</v>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AD135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT135" t="inlineStr"/>
+      <c r="AW135" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX135" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>132622049</v>
+      </c>
+      <c r="B136" t="n">
+        <v>101304</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>Risbyskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q136" t="n">
+        <v>631834</v>
+      </c>
+      <c r="R136" t="n">
+        <v>6661764</v>
+      </c>
+      <c r="S136" t="n">
+        <v>5</v>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W136" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AD136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT136" t="inlineStr"/>
+      <c r="AW136" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX136" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>132622043</v>
+      </c>
+      <c r="B137" t="n">
+        <v>97338</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>53</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>Risbyskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q137" t="n">
+        <v>631918</v>
+      </c>
+      <c r="R137" t="n">
+        <v>6661646</v>
+      </c>
+      <c r="S137" t="n">
+        <v>5</v>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AB137" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AD137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT137" t="inlineStr"/>
+      <c r="AW137" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX137" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>132622044</v>
+      </c>
+      <c r="B138" t="n">
+        <v>44172</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>101735</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Jättesvampmal</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Scardia boletella</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>Risbyskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q138" t="n">
+        <v>631870</v>
+      </c>
+      <c r="R138" t="n">
+        <v>6661643</v>
+      </c>
+      <c r="S138" t="n">
+        <v>5</v>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="Z138" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AB138" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AD138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT138" t="inlineStr"/>
+      <c r="AW138" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX138" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>132622047</v>
+      </c>
+      <c r="B139" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>Risbyskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q139" t="n">
+        <v>631865</v>
+      </c>
+      <c r="R139" t="n">
+        <v>6661681</v>
+      </c>
+      <c r="S139" t="n">
+        <v>5</v>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AD139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT139" t="inlineStr"/>
+      <c r="AW139" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX139" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>132622051</v>
+      </c>
+      <c r="B140" t="n">
+        <v>91892</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>Risbyskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q140" t="n">
+        <v>631691</v>
+      </c>
+      <c r="R140" t="n">
+        <v>6661904</v>
+      </c>
+      <c r="S140" t="n">
+        <v>5</v>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AD140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT140" t="inlineStr"/>
+      <c r="AW140" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX140" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>132622040</v>
+      </c>
+      <c r="B141" t="n">
+        <v>99098</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>Risbyskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q141" t="n">
+        <v>632005</v>
+      </c>
+      <c r="R141" t="n">
+        <v>6661501</v>
+      </c>
+      <c r="S141" t="n">
+        <v>5</v>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AB141" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AD141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT141" t="inlineStr"/>
+      <c r="AW141" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX141" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>132622048</v>
+      </c>
+      <c r="B142" t="n">
+        <v>101304</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr"/>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>Risbyskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q142" t="n">
+        <v>631856</v>
+      </c>
+      <c r="R142" t="n">
+        <v>6661762</v>
+      </c>
+      <c r="S142" t="n">
+        <v>5</v>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AB142" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AD142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT142" t="inlineStr"/>
+      <c r="AW142" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX142" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY142" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41611-2025 artfynd.xlsx
+++ b/artfynd/A 41611-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY142"/>
+  <dimension ref="A1:AY146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8233,7 +8233,7 @@
         <v>131894430</v>
       </c>
       <c r="B76" t="n">
-        <v>101304</v>
+        <v>101312</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8327,46 +8327,38 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131890765</v>
+        <v>131890776</v>
       </c>
       <c r="B77" t="n">
-        <v>57136</v>
+        <v>99106</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="L77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -8374,10 +8366,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>631624</v>
+        <v>631853</v>
       </c>
       <c r="R77" t="n">
-        <v>6661852</v>
+        <v>6661839</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8414,7 +8406,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Stärtpenna från tupp</t>
+          <t>Mer än 10 rosetter</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8423,6 +8415,7 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8441,38 +8434,46 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131890776</v>
+        <v>131890765</v>
       </c>
       <c r="B78" t="n">
-        <v>99098</v>
+        <v>57137</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
@@ -8480,10 +8481,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>631853</v>
+        <v>631624</v>
       </c>
       <c r="R78" t="n">
-        <v>6661839</v>
+        <v>6661852</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -8520,7 +8521,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Mer än 10 rosetter</t>
+          <t>Stärtpenna från tupp</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8529,7 +8530,6 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8551,7 +8551,7 @@
         <v>131890774</v>
       </c>
       <c r="B79" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8655,10 +8655,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131890767</v>
+        <v>131890753</v>
       </c>
       <c r="B80" t="n">
-        <v>57945</v>
+        <v>97346</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8666,42 +8666,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Risboskogens nr, söder om, Upl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>631834</v>
+        <v>631602</v>
       </c>
       <c r="R80" t="n">
-        <v>6661821</v>
+        <v>6661856</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -8760,10 +8752,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131890777</v>
+        <v>131890762</v>
       </c>
       <c r="B81" t="n">
-        <v>57127</v>
+        <v>91898</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8771,42 +8763,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Risboskogens nr, söder om, Upl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>631980</v>
+        <v>631785</v>
       </c>
       <c r="R81" t="n">
-        <v>6661999</v>
+        <v>6661901</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -8839,11 +8823,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Spillningshög med blindtarmstömning</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8870,10 +8849,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>131890753</v>
+        <v>131890767</v>
       </c>
       <c r="B82" t="n">
-        <v>97338</v>
+        <v>57946</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8881,34 +8860,42 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Risboskogens nr, söder om, Upl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>631602</v>
+        <v>631834</v>
       </c>
       <c r="R82" t="n">
-        <v>6661856</v>
+        <v>6661821</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -8967,10 +8954,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>131890762</v>
+        <v>131890777</v>
       </c>
       <c r="B83" t="n">
-        <v>91892</v>
+        <v>57128</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8978,34 +8965,42 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Risboskogens nr, söder om, Upl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>631785</v>
+        <v>631980</v>
       </c>
       <c r="R83" t="n">
-        <v>6661901</v>
+        <v>6661999</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -9038,6 +9033,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Spillningshög med blindtarmstömning</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9067,7 +9067,7 @@
         <v>131890788</v>
       </c>
       <c r="B84" t="n">
-        <v>96581</v>
+        <v>96589</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9161,45 +9161,53 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131890760</v>
+        <v>131894426</v>
       </c>
       <c r="B85" t="n">
-        <v>91855</v>
+        <v>57128</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5447</v>
+        <v>102612</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Risboskogens nr, söder om, Upl</t>
+          <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>631513</v>
+        <v>631854</v>
       </c>
       <c r="R85" t="n">
-        <v>6661837</v>
+        <v>6661782</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -9226,12 +9234,17 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>spillning</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9258,10 +9271,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131890757</v>
+        <v>131890769</v>
       </c>
       <c r="B86" t="n">
-        <v>91855</v>
+        <v>57790</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9269,37 +9282,45 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5447</v>
+        <v>102621</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Risboskogens nr, söder om, Upl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>631992</v>
+        <v>631746</v>
       </c>
       <c r="R86" t="n">
-        <v>6661795</v>
+        <v>6661893</v>
       </c>
       <c r="S86" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9326,9 +9347,19 @@
           <t>2026-03-23</t>
         </is>
       </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9358,7 +9389,7 @@
         <v>131894431</v>
       </c>
       <c r="B87" t="n">
-        <v>101304</v>
+        <v>101312</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9452,53 +9483,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131894426</v>
+        <v>131890760</v>
       </c>
       <c r="B88" t="n">
-        <v>57127</v>
+        <v>91861</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>102612</v>
+        <v>5447</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Risboskogen, Upl</t>
+          <t>Risboskogens nr, söder om, Upl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>631854</v>
+        <v>631513</v>
       </c>
       <c r="R88" t="n">
-        <v>6661782</v>
+        <v>6661837</v>
       </c>
       <c r="S88" t="n">
         <v>15</v>
@@ -9525,17 +9548,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>spillning</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9562,10 +9580,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131890769</v>
+        <v>131890757</v>
       </c>
       <c r="B89" t="n">
-        <v>57789</v>
+        <v>91861</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9573,45 +9591,37 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>102621</v>
+        <v>5447</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Risboskogens nr, söder om, Upl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>631746</v>
+        <v>631992</v>
       </c>
       <c r="R89" t="n">
-        <v>6661893</v>
+        <v>6661795</v>
       </c>
       <c r="S89" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9638,19 +9648,9 @@
           <t>2026-03-23</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>18:30</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9680,7 +9680,7 @@
         <v>131894428</v>
       </c>
       <c r="B90" t="n">
-        <v>80457</v>
+        <v>80459</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9777,7 +9777,7 @@
         <v>131890761</v>
       </c>
       <c r="B91" t="n">
-        <v>79936</v>
+        <v>79938</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9874,7 +9874,7 @@
         <v>131894427</v>
       </c>
       <c r="B92" t="n">
-        <v>96406</v>
+        <v>96414</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9971,7 +9971,7 @@
         <v>131894429</v>
       </c>
       <c r="B93" t="n">
-        <v>83289</v>
+        <v>83291</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>131890780</v>
       </c>
       <c r="B94" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10165,7 +10165,7 @@
         <v>131890758</v>
       </c>
       <c r="B95" t="n">
-        <v>91855</v>
+        <v>91861</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10262,7 +10262,7 @@
         <v>131890786</v>
       </c>
       <c r="B96" t="n">
-        <v>96406</v>
+        <v>96414</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10356,10 +10356,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>131890772</v>
+        <v>131890778</v>
       </c>
       <c r="B97" t="n">
-        <v>80382</v>
+        <v>96542</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10367,34 +10367,46 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>229497</v>
+        <v>210</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Risboskogens nr, söder om, Upl</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>632024</v>
+        <v>631545</v>
       </c>
       <c r="R97" t="n">
-        <v>6661958</v>
+        <v>6661872</v>
       </c>
       <c r="S97" t="n">
         <v>15</v>
@@ -10435,6 +10447,7 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -10453,57 +10466,45 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>131890778</v>
+        <v>131890789</v>
       </c>
       <c r="B98" t="n">
-        <v>96534</v>
+        <v>83291</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>210</v>
+        <v>308</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Risboskogens nr, söder om, Upl</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>631545</v>
+        <v>631544</v>
       </c>
       <c r="R98" t="n">
-        <v>6661872</v>
+        <v>6661863</v>
       </c>
       <c r="S98" t="n">
         <v>15</v>
@@ -10544,7 +10545,6 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -10563,10 +10563,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>131890789</v>
+        <v>131890779</v>
       </c>
       <c r="B99" t="n">
-        <v>83289</v>
+        <v>91912</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10574,21 +10574,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>308</v>
+        <v>1204</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10598,10 +10598,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>631544</v>
+        <v>631992</v>
       </c>
       <c r="R99" t="n">
-        <v>6661863</v>
+        <v>6661795</v>
       </c>
       <c r="S99" t="n">
         <v>15</v>
@@ -10660,45 +10660,49 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>131890779</v>
+        <v>131890775</v>
       </c>
       <c r="B100" t="n">
-        <v>91906</v>
+        <v>99106</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Risboskogens nr, söder om, Upl</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>631992</v>
+        <v>631932</v>
       </c>
       <c r="R100" t="n">
-        <v>6661795</v>
+        <v>6661790</v>
       </c>
       <c r="S100" t="n">
         <v>15</v>
@@ -10733,12 +10737,18 @@
           <t>2026-03-23</t>
         </is>
       </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Mer än 20 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -10757,49 +10767,45 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>131890775</v>
+        <v>131890772</v>
       </c>
       <c r="B101" t="n">
-        <v>99098</v>
+        <v>80384</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Risboskogens nr, söder om, Upl</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>631932</v>
+        <v>632024</v>
       </c>
       <c r="R101" t="n">
-        <v>6661790</v>
+        <v>6661958</v>
       </c>
       <c r="S101" t="n">
         <v>15</v>
@@ -10834,18 +10840,12 @@
           <t>2026-03-23</t>
         </is>
       </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Mer än 20 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD101" t="b">
         <v>0</v>
       </c>
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -10867,7 +10867,7 @@
         <v>131890764</v>
       </c>
       <c r="B102" t="n">
-        <v>57136</v>
+        <v>57137</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10977,7 +10977,7 @@
         <v>131890759</v>
       </c>
       <c r="B103" t="n">
-        <v>91855</v>
+        <v>91861</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11074,7 +11074,7 @@
         <v>131890754</v>
       </c>
       <c r="B104" t="n">
-        <v>97338</v>
+        <v>97346</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11168,56 +11168,48 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>131890768</v>
+        <v>131890787</v>
       </c>
       <c r="B105" t="n">
-        <v>57945</v>
+        <v>96589</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100049</v>
+        <v>2170</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Risboskogens nr, söder om, Upl</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>631613</v>
+        <v>631600</v>
       </c>
       <c r="R105" t="n">
-        <v>6661765</v>
+        <v>6661750</v>
       </c>
       <c r="S105" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11273,32 +11265,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>131890787</v>
+        <v>131890755</v>
       </c>
       <c r="B106" t="n">
-        <v>96581</v>
+        <v>97346</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>2170</v>
+        <v>53</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11308,10 +11300,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>631600</v>
+        <v>631573</v>
       </c>
       <c r="R106" t="n">
-        <v>6661750</v>
+        <v>6661854</v>
       </c>
       <c r="S106" t="n">
         <v>15</v>
@@ -11370,38 +11362,42 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>131890773</v>
+        <v>131890768</v>
       </c>
       <c r="B107" t="n">
-        <v>99098</v>
+        <v>57946</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
@@ -11409,13 +11405,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>632005</v>
+        <v>631613</v>
       </c>
       <c r="R107" t="n">
-        <v>6661952</v>
+        <v>6661765</v>
       </c>
       <c r="S107" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11447,18 +11443,12 @@
           <t>2026-03-23</t>
         </is>
       </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Ett fåtal bladrosetter</t>
-        </is>
-      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
       <c r="AE107" t="b">
         <v>0</v>
       </c>
-      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
@@ -11477,45 +11467,49 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>131890755</v>
+        <v>131890773</v>
       </c>
       <c r="B108" t="n">
-        <v>97338</v>
+        <v>99106</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Risboskogens nr, söder om, Upl</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>631573</v>
+        <v>632005</v>
       </c>
       <c r="R108" t="n">
-        <v>6661854</v>
+        <v>6661952</v>
       </c>
       <c r="S108" t="n">
         <v>15</v>
@@ -11550,12 +11544,18 @@
           <t>2026-03-23</t>
         </is>
       </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Ett fåtal bladrosetter</t>
+        </is>
+      </c>
       <c r="AD108" t="b">
         <v>0</v>
       </c>
       <c r="AE108" t="b">
         <v>0</v>
       </c>
+      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -11577,7 +11577,7 @@
         <v>131890771</v>
       </c>
       <c r="B109" t="n">
-        <v>81302</v>
+        <v>81304</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11678,7 +11678,7 @@
         <v>131890766</v>
       </c>
       <c r="B110" t="n">
-        <v>96440</v>
+        <v>96448</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11780,7 +11780,7 @@
         <v>132247080</v>
       </c>
       <c r="B111" t="n">
-        <v>97338</v>
+        <v>97346</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11877,7 +11877,7 @@
         <v>132247084</v>
       </c>
       <c r="B112" t="n">
-        <v>81302</v>
+        <v>81304</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11974,7 +11974,7 @@
         <v>132247081</v>
       </c>
       <c r="B113" t="n">
-        <v>97338</v>
+        <v>97346</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12071,7 +12071,7 @@
         <v>132247087</v>
       </c>
       <c r="B114" t="n">
-        <v>96581</v>
+        <v>96589</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12165,10 +12165,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>132247085</v>
+        <v>132247086</v>
       </c>
       <c r="B115" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12194,16 +12194,20 @@
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>632051</v>
+        <v>632060</v>
       </c>
       <c r="R115" t="n">
-        <v>6661556</v>
+        <v>6661605</v>
       </c>
       <c r="S115" t="n">
         <v>15</v>
@@ -12240,7 +12244,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>20 tal bladrosetter</t>
+          <t>3 bladrosetter</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12249,6 +12253,7 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
+      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
@@ -12267,10 +12272,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>132247086</v>
+        <v>132247085</v>
       </c>
       <c r="B116" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12296,20 +12301,16 @@
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>632060</v>
+        <v>632051</v>
       </c>
       <c r="R116" t="n">
-        <v>6661605</v>
+        <v>6661556</v>
       </c>
       <c r="S116" t="n">
         <v>15</v>
@@ -12346,7 +12347,7 @@
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>3 bladrosetter</t>
+          <t>20 tal bladrosetter</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12355,7 +12356,6 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
-      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -12377,7 +12377,7 @@
         <v>132247082</v>
       </c>
       <c r="B117" t="n">
-        <v>57136</v>
+        <v>57137</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12482,7 +12482,7 @@
         <v>132286073</v>
       </c>
       <c r="B118" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12587,7 +12587,7 @@
         <v>132286086</v>
       </c>
       <c r="B119" t="n">
-        <v>101304</v>
+        <v>101312</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12684,7 +12684,7 @@
         <v>132286072</v>
       </c>
       <c r="B120" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12789,7 +12789,7 @@
         <v>132286080</v>
       </c>
       <c r="B121" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12899,7 +12899,7 @@
         <v>132286078</v>
       </c>
       <c r="B122" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13009,7 +13009,7 @@
         <v>132286088</v>
       </c>
       <c r="B123" t="n">
-        <v>101304</v>
+        <v>101312</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13106,7 +13106,7 @@
         <v>132410204</v>
       </c>
       <c r="B124" t="n">
-        <v>58109</v>
+        <v>58110</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13225,7 +13225,7 @@
         <v>132617077</v>
       </c>
       <c r="B125" t="n">
-        <v>80382</v>
+        <v>80384</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13322,7 +13322,7 @@
         <v>132603522</v>
       </c>
       <c r="B126" t="n">
-        <v>80382</v>
+        <v>80384</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13429,7 +13429,7 @@
         <v>132617083</v>
       </c>
       <c r="B127" t="n">
-        <v>96534</v>
+        <v>96542</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13526,7 +13526,7 @@
         <v>132617073</v>
       </c>
       <c r="B128" t="n">
-        <v>92191</v>
+        <v>92197</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13623,7 +13623,7 @@
         <v>132617066</v>
       </c>
       <c r="B129" t="n">
-        <v>97338</v>
+        <v>97346</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13720,7 +13720,7 @@
         <v>132617068</v>
       </c>
       <c r="B130" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13817,7 +13817,7 @@
         <v>132617085</v>
       </c>
       <c r="B131" t="n">
-        <v>91906</v>
+        <v>91912</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13914,7 +13914,7 @@
         <v>132606960</v>
       </c>
       <c r="B132" t="n">
-        <v>97338</v>
+        <v>97346</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14025,7 +14025,7 @@
         <v>132617069</v>
       </c>
       <c r="B133" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14229,7 +14229,7 @@
         <v>132622045</v>
       </c>
       <c r="B135" t="n">
-        <v>79936</v>
+        <v>79938</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14336,7 +14336,7 @@
         <v>132622049</v>
       </c>
       <c r="B136" t="n">
-        <v>101304</v>
+        <v>101312</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14443,7 +14443,7 @@
         <v>132622043</v>
       </c>
       <c r="B137" t="n">
-        <v>97338</v>
+        <v>97346</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14550,7 +14550,7 @@
         <v>132622044</v>
       </c>
       <c r="B138" t="n">
-        <v>44172</v>
+        <v>44173</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14764,7 +14764,7 @@
         <v>132622051</v>
       </c>
       <c r="B140" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14871,7 +14871,7 @@
         <v>132622040</v>
       </c>
       <c r="B141" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14987,7 +14987,7 @@
         <v>132622048</v>
       </c>
       <c r="B142" t="n">
-        <v>101304</v>
+        <v>101312</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15088,6 +15088,461 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>132663326</v>
+      </c>
+      <c r="B143" t="n">
+        <v>57946</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr"/>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>Spillkråka, Upl</t>
+        </is>
+      </c>
+      <c r="Q143" t="n">
+        <v>631887</v>
+      </c>
+      <c r="R143" t="n">
+        <v>6661745</v>
+      </c>
+      <c r="S143" t="n">
+        <v>5</v>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="Z143" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AB143" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AD143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT143" t="inlineStr"/>
+      <c r="AW143" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX143" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>132651716</v>
+      </c>
+      <c r="B144" t="n">
+        <v>57946</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr"/>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>Sydväst Risbosjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q144" t="n">
+        <v>632027</v>
+      </c>
+      <c r="R144" t="n">
+        <v>6661732</v>
+      </c>
+      <c r="S144" t="n">
+        <v>5</v>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AD144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT144" t="inlineStr"/>
+      <c r="AW144" t="inlineStr">
+        <is>
+          <t>Eric Grund</t>
+        </is>
+      </c>
+      <c r="AX144" t="inlineStr">
+        <is>
+          <t>Eric Grund</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>132663350</v>
+      </c>
+      <c r="B145" t="n">
+        <v>83291</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>308</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr"/>
+      <c r="K145" t="inlineStr"/>
+      <c r="N145" t="inlineStr"/>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav, Åkerlänna-Marstalla, Upl</t>
+        </is>
+      </c>
+      <c r="Q145" t="n">
+        <v>631879</v>
+      </c>
+      <c r="R145" t="n">
+        <v>6661764</v>
+      </c>
+      <c r="S145" t="n">
+        <v>5</v>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W145" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="Z145" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AB145" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AD145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF145" t="inlineStr"/>
+      <c r="AG145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT145" t="inlineStr"/>
+      <c r="AW145" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX145" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>132651173</v>
+      </c>
+      <c r="B146" t="n">
+        <v>57137</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr"/>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>Sydväst Risbosjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q146" t="n">
+        <v>631679</v>
+      </c>
+      <c r="R146" t="n">
+        <v>6661868</v>
+      </c>
+      <c r="S146" t="n">
+        <v>5</v>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W146" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="Z146" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AB146" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>Vid en rotvälte.</t>
+        </is>
+      </c>
+      <c r="AD146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT146" t="inlineStr"/>
+      <c r="AW146" t="inlineStr">
+        <is>
+          <t>Eric Grund</t>
+        </is>
+      </c>
+      <c r="AX146" t="inlineStr">
+        <is>
+          <t>Eric Grund</t>
+        </is>
+      </c>
+      <c r="AY146" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 41611-2025 artfynd.xlsx
+++ b/artfynd/A 41611-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY146"/>
+  <dimension ref="A1:AY147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8327,38 +8327,46 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131890776</v>
+        <v>131890765</v>
       </c>
       <c r="B77" t="n">
-        <v>99106</v>
+        <v>57137</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -8366,10 +8374,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>631853</v>
+        <v>631624</v>
       </c>
       <c r="R77" t="n">
-        <v>6661839</v>
+        <v>6661852</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8406,7 +8414,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Mer än 10 rosetter</t>
+          <t>Stärtpenna från tupp</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8415,7 +8423,6 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8434,46 +8441,38 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131890765</v>
+        <v>131890776</v>
       </c>
       <c r="B78" t="n">
-        <v>57137</v>
+        <v>99106</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="L78" t="inlineStr"/>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
@@ -8481,10 +8480,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>631624</v>
+        <v>631853</v>
       </c>
       <c r="R78" t="n">
-        <v>6661852</v>
+        <v>6661839</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -8521,7 +8520,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Stärtpenna från tupp</t>
+          <t>Mer än 10 rosetter</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8530,6 +8529,7 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -15544,6 +15544,103 @@
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>132688846</v>
+      </c>
+      <c r="B147" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>Risboskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q147" t="n">
+        <v>631955</v>
+      </c>
+      <c r="R147" t="n">
+        <v>6661572</v>
+      </c>
+      <c r="S147" t="n">
+        <v>15</v>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W147" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y147" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AD147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT147" t="inlineStr"/>
+      <c r="AW147" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX147" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY147" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41611-2025 artfynd.xlsx
+++ b/artfynd/A 41611-2025 artfynd.xlsx
@@ -11577,7 +11577,7 @@
         <v>131890771</v>
       </c>
       <c r="B109" t="n">
-        <v>81304</v>
+        <v>81312</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11678,7 +11678,7 @@
         <v>131890766</v>
       </c>
       <c r="B110" t="n">
-        <v>96448</v>
+        <v>96458</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11780,7 +11780,7 @@
         <v>132247080</v>
       </c>
       <c r="B111" t="n">
-        <v>97346</v>
+        <v>97356</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11877,7 +11877,7 @@
         <v>132247084</v>
       </c>
       <c r="B112" t="n">
-        <v>81304</v>
+        <v>81312</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11974,7 +11974,7 @@
         <v>132247081</v>
       </c>
       <c r="B113" t="n">
-        <v>97346</v>
+        <v>97356</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12068,45 +12068,49 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>132247087</v>
+        <v>132247086</v>
       </c>
       <c r="B114" t="n">
-        <v>96589</v>
+        <v>99116</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>2170</v>
+        <v>220787</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>632046</v>
+        <v>632060</v>
       </c>
       <c r="R114" t="n">
-        <v>6661591</v>
+        <v>6661605</v>
       </c>
       <c r="S114" t="n">
         <v>15</v>
@@ -12141,12 +12145,18 @@
           <t>2026-04-06</t>
         </is>
       </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>3 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD114" t="b">
         <v>0</v>
       </c>
       <c r="AE114" t="b">
         <v>0</v>
       </c>
+      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
@@ -12165,10 +12175,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>132247086</v>
+        <v>132247085</v>
       </c>
       <c r="B115" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12194,20 +12204,16 @@
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
-      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>632060</v>
+        <v>632051</v>
       </c>
       <c r="R115" t="n">
-        <v>6661605</v>
+        <v>6661556</v>
       </c>
       <c r="S115" t="n">
         <v>15</v>
@@ -12244,7 +12250,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>3 bladrosetter</t>
+          <t>20 tal bladrosetter</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12253,7 +12259,6 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
-      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
@@ -12272,32 +12277,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>132247085</v>
+        <v>132247087</v>
       </c>
       <c r="B116" t="n">
-        <v>99106</v>
+        <v>96599</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>220787</v>
+        <v>2170</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12307,10 +12312,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>632051</v>
+        <v>632046</v>
       </c>
       <c r="R116" t="n">
-        <v>6661556</v>
+        <v>6661591</v>
       </c>
       <c r="S116" t="n">
         <v>15</v>
@@ -12343,11 +12348,6 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>20 tal bladrosetter</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12377,7 +12377,7 @@
         <v>132247082</v>
       </c>
       <c r="B117" t="n">
-        <v>57137</v>
+        <v>57141</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12482,7 +12482,7 @@
         <v>132286073</v>
       </c>
       <c r="B118" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12587,7 +12587,7 @@
         <v>132286086</v>
       </c>
       <c r="B119" t="n">
-        <v>101312</v>
+        <v>101323</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12684,7 +12684,7 @@
         <v>132286072</v>
       </c>
       <c r="B120" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12789,7 +12789,7 @@
         <v>132286080</v>
       </c>
       <c r="B121" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12899,7 +12899,7 @@
         <v>132286078</v>
       </c>
       <c r="B122" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13009,7 +13009,7 @@
         <v>132286088</v>
       </c>
       <c r="B123" t="n">
-        <v>101312</v>
+        <v>101323</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13106,7 +13106,7 @@
         <v>132410204</v>
       </c>
       <c r="B124" t="n">
-        <v>58110</v>
+        <v>58114</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13225,7 +13225,7 @@
         <v>132617077</v>
       </c>
       <c r="B125" t="n">
-        <v>80384</v>
+        <v>80392</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13322,7 +13322,7 @@
         <v>132603522</v>
       </c>
       <c r="B126" t="n">
-        <v>80384</v>
+        <v>80392</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13429,7 +13429,7 @@
         <v>132617083</v>
       </c>
       <c r="B127" t="n">
-        <v>96542</v>
+        <v>96552</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13526,7 +13526,7 @@
         <v>132617073</v>
       </c>
       <c r="B128" t="n">
-        <v>92197</v>
+        <v>92207</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13623,7 +13623,7 @@
         <v>132617066</v>
       </c>
       <c r="B129" t="n">
-        <v>97346</v>
+        <v>97356</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13720,7 +13720,7 @@
         <v>132617068</v>
       </c>
       <c r="B130" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13817,7 +13817,7 @@
         <v>132617085</v>
       </c>
       <c r="B131" t="n">
-        <v>91912</v>
+        <v>91922</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13914,7 +13914,7 @@
         <v>132606960</v>
       </c>
       <c r="B132" t="n">
-        <v>97346</v>
+        <v>97356</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14025,7 +14025,7 @@
         <v>132617069</v>
       </c>
       <c r="B133" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14229,7 +14229,7 @@
         <v>132622045</v>
       </c>
       <c r="B135" t="n">
-        <v>79938</v>
+        <v>79946</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14336,7 +14336,7 @@
         <v>132622049</v>
       </c>
       <c r="B136" t="n">
-        <v>101312</v>
+        <v>101323</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14443,7 +14443,7 @@
         <v>132622043</v>
       </c>
       <c r="B137" t="n">
-        <v>97346</v>
+        <v>97356</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14550,7 +14550,7 @@
         <v>132622044</v>
       </c>
       <c r="B138" t="n">
-        <v>44173</v>
+        <v>44177</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14764,7 +14764,7 @@
         <v>132622051</v>
       </c>
       <c r="B140" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14871,7 +14871,7 @@
         <v>132622040</v>
       </c>
       <c r="B141" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14987,7 +14987,7 @@
         <v>132622048</v>
       </c>
       <c r="B142" t="n">
-        <v>101312</v>
+        <v>101323</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15094,7 +15094,7 @@
         <v>132663326</v>
       </c>
       <c r="B143" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15213,7 +15213,7 @@
         <v>132651716</v>
       </c>
       <c r="B144" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15318,7 +15318,7 @@
         <v>132663350</v>
       </c>
       <c r="B145" t="n">
-        <v>83291</v>
+        <v>83299</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15429,7 +15429,7 @@
         <v>132651173</v>
       </c>
       <c r="B146" t="n">
-        <v>57137</v>
+        <v>57141</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15549,7 +15549,7 @@
         <v>132688846</v>
       </c>
       <c r="B147" t="n">
-        <v>99112</v>
+        <v>99116</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>

--- a/artfynd/A 41611-2025 artfynd.xlsx
+++ b/artfynd/A 41611-2025 artfynd.xlsx
@@ -11780,7 +11780,7 @@
         <v>132247080</v>
       </c>
       <c r="B111" t="n">
-        <v>97356</v>
+        <v>97357</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11974,7 +11974,7 @@
         <v>132247081</v>
       </c>
       <c r="B113" t="n">
-        <v>97356</v>
+        <v>97357</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12068,49 +12068,45 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>132247086</v>
+        <v>132247087</v>
       </c>
       <c r="B114" t="n">
-        <v>99116</v>
+        <v>96600</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>220787</v>
+        <v>2170</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
-      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>632060</v>
+        <v>632046</v>
       </c>
       <c r="R114" t="n">
-        <v>6661605</v>
+        <v>6661591</v>
       </c>
       <c r="S114" t="n">
         <v>15</v>
@@ -12145,18 +12141,12 @@
           <t>2026-04-06</t>
         </is>
       </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>3 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD114" t="b">
         <v>0</v>
       </c>
       <c r="AE114" t="b">
         <v>0</v>
       </c>
-      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
@@ -12175,10 +12165,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>132247085</v>
+        <v>132247086</v>
       </c>
       <c r="B115" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12204,16 +12194,20 @@
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>632051</v>
+        <v>632060</v>
       </c>
       <c r="R115" t="n">
-        <v>6661556</v>
+        <v>6661605</v>
       </c>
       <c r="S115" t="n">
         <v>15</v>
@@ -12250,7 +12244,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>20 tal bladrosetter</t>
+          <t>3 bladrosetter</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12259,6 +12253,7 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
+      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
@@ -12277,32 +12272,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>132247087</v>
+        <v>132247085</v>
       </c>
       <c r="B116" t="n">
-        <v>96599</v>
+        <v>99117</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>2170</v>
+        <v>220787</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12312,10 +12307,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>632046</v>
+        <v>632051</v>
       </c>
       <c r="R116" t="n">
-        <v>6661591</v>
+        <v>6661556</v>
       </c>
       <c r="S116" t="n">
         <v>15</v>
@@ -12348,6 +12343,11 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>20 tal bladrosetter</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12587,7 +12587,7 @@
         <v>132286086</v>
       </c>
       <c r="B119" t="n">
-        <v>101323</v>
+        <v>101324</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12789,7 +12789,7 @@
         <v>132286080</v>
       </c>
       <c r="B121" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12899,7 +12899,7 @@
         <v>132286078</v>
       </c>
       <c r="B122" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13009,7 +13009,7 @@
         <v>132286088</v>
       </c>
       <c r="B123" t="n">
-        <v>101323</v>
+        <v>101324</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13429,7 +13429,7 @@
         <v>132617083</v>
       </c>
       <c r="B127" t="n">
-        <v>96552</v>
+        <v>96553</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13526,7 +13526,7 @@
         <v>132617073</v>
       </c>
       <c r="B128" t="n">
-        <v>92207</v>
+        <v>92208</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13623,7 +13623,7 @@
         <v>132617066</v>
       </c>
       <c r="B129" t="n">
-        <v>97356</v>
+        <v>97357</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13720,7 +13720,7 @@
         <v>132617068</v>
       </c>
       <c r="B130" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13817,7 +13817,7 @@
         <v>132617085</v>
       </c>
       <c r="B131" t="n">
-        <v>91922</v>
+        <v>91923</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13914,7 +13914,7 @@
         <v>132606960</v>
       </c>
       <c r="B132" t="n">
-        <v>97356</v>
+        <v>97357</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14015,7 +14015,7 @@
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Elvira Klang, Tore Dahlberg, Elias Blad, Filippa Paperin</t>
+          <t>Filippa Paperin, Elias Blad, Tore Dahlberg, Elvira Klang</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
@@ -14025,7 +14025,7 @@
         <v>132617069</v>
       </c>
       <c r="B133" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14336,7 +14336,7 @@
         <v>132622049</v>
       </c>
       <c r="B136" t="n">
-        <v>101323</v>
+        <v>101324</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14443,7 +14443,7 @@
         <v>132622043</v>
       </c>
       <c r="B137" t="n">
-        <v>97356</v>
+        <v>97357</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14764,7 +14764,7 @@
         <v>132622051</v>
       </c>
       <c r="B140" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14871,7 +14871,7 @@
         <v>132622040</v>
       </c>
       <c r="B141" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14987,7 +14987,7 @@
         <v>132622048</v>
       </c>
       <c r="B142" t="n">
-        <v>101323</v>
+        <v>101324</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15549,7 +15549,7 @@
         <v>132688846</v>
       </c>
       <c r="B147" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>

--- a/artfynd/A 41611-2025 artfynd.xlsx
+++ b/artfynd/A 41611-2025 artfynd.xlsx
@@ -11780,7 +11780,7 @@
         <v>132247080</v>
       </c>
       <c r="B111" t="n">
-        <v>97357</v>
+        <v>97358</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11974,7 +11974,7 @@
         <v>132247081</v>
       </c>
       <c r="B113" t="n">
-        <v>97357</v>
+        <v>97358</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12071,7 +12071,7 @@
         <v>132247087</v>
       </c>
       <c r="B114" t="n">
-        <v>96600</v>
+        <v>96601</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12168,7 +12168,7 @@
         <v>132247086</v>
       </c>
       <c r="B115" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12275,7 +12275,7 @@
         <v>132247085</v>
       </c>
       <c r="B116" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12587,7 +12587,7 @@
         <v>132286086</v>
       </c>
       <c r="B119" t="n">
-        <v>101324</v>
+        <v>101325</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12789,7 +12789,7 @@
         <v>132286080</v>
       </c>
       <c r="B121" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12899,7 +12899,7 @@
         <v>132286078</v>
       </c>
       <c r="B122" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13009,7 +13009,7 @@
         <v>132286088</v>
       </c>
       <c r="B123" t="n">
-        <v>101324</v>
+        <v>101325</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13429,7 +13429,7 @@
         <v>132617083</v>
       </c>
       <c r="B127" t="n">
-        <v>96553</v>
+        <v>96554</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13623,7 +13623,7 @@
         <v>132617066</v>
       </c>
       <c r="B129" t="n">
-        <v>97357</v>
+        <v>97358</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13914,7 +13914,7 @@
         <v>132606960</v>
       </c>
       <c r="B132" t="n">
-        <v>97357</v>
+        <v>97358</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14015,7 +14015,7 @@
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elias Blad, Tore Dahlberg, Elvira Klang</t>
+          <t>Elvira Klang, Filippa Paperin, Elias Blad, Tore Dahlberg</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
@@ -14226,32 +14226,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>132622045</v>
+        <v>132622049</v>
       </c>
       <c r="B135" t="n">
-        <v>79946</v>
+        <v>101325</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6453</v>
+        <v>222498</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14261,10 +14261,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>631882</v>
+        <v>631834</v>
       </c>
       <c r="R135" t="n">
-        <v>6661651</v>
+        <v>6661764</v>
       </c>
       <c r="S135" t="n">
         <v>5</v>
@@ -14296,7 +14296,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -14306,7 +14306,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14333,32 +14333,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>132622049</v>
+        <v>132622045</v>
       </c>
       <c r="B136" t="n">
-        <v>101324</v>
+        <v>79946</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>222498</v>
+        <v>6453</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14368,10 +14368,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>631834</v>
+        <v>631882</v>
       </c>
       <c r="R136" t="n">
-        <v>6661764</v>
+        <v>6661651</v>
       </c>
       <c r="S136" t="n">
         <v>5</v>
@@ -14403,7 +14403,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -14413,7 +14413,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14443,7 +14443,7 @@
         <v>132622043</v>
       </c>
       <c r="B137" t="n">
-        <v>97357</v>
+        <v>97358</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14871,7 +14871,7 @@
         <v>132622040</v>
       </c>
       <c r="B141" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14987,7 +14987,7 @@
         <v>132622048</v>
       </c>
       <c r="B142" t="n">
-        <v>101324</v>
+        <v>101325</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15549,7 +15549,7 @@
         <v>132688846</v>
       </c>
       <c r="B147" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>

--- a/artfynd/A 41611-2025 artfynd.xlsx
+++ b/artfynd/A 41611-2025 artfynd.xlsx
@@ -14226,32 +14226,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>132622049</v>
+        <v>132622045</v>
       </c>
       <c r="B135" t="n">
-        <v>101325</v>
+        <v>79946</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>222498</v>
+        <v>6453</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14261,10 +14261,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>631834</v>
+        <v>631882</v>
       </c>
       <c r="R135" t="n">
-        <v>6661764</v>
+        <v>6661651</v>
       </c>
       <c r="S135" t="n">
         <v>5</v>
@@ -14296,7 +14296,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -14306,7 +14306,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14333,32 +14333,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>132622045</v>
+        <v>132622049</v>
       </c>
       <c r="B136" t="n">
-        <v>79946</v>
+        <v>101325</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6453</v>
+        <v>222498</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14368,10 +14368,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>631882</v>
+        <v>631834</v>
       </c>
       <c r="R136" t="n">
-        <v>6661651</v>
+        <v>6661764</v>
       </c>
       <c r="S136" t="n">
         <v>5</v>
@@ -14403,7 +14403,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -14413,7 +14413,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD136" t="b">

--- a/artfynd/A 41611-2025 artfynd.xlsx
+++ b/artfynd/A 41611-2025 artfynd.xlsx
@@ -12587,7 +12587,7 @@
         <v>132286086</v>
       </c>
       <c r="B119" t="n">
-        <v>101325</v>
+        <v>101326</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13009,7 +13009,7 @@
         <v>132286088</v>
       </c>
       <c r="B123" t="n">
-        <v>101325</v>
+        <v>101326</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14015,7 +14015,7 @@
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Elvira Klang, Filippa Paperin, Elias Blad, Tore Dahlberg</t>
+          <t>Elvira Klang, Tore Dahlberg, Elias Blad, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
@@ -14226,32 +14226,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>132622045</v>
+        <v>132622049</v>
       </c>
       <c r="B135" t="n">
-        <v>79946</v>
+        <v>101326</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6453</v>
+        <v>222498</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14261,10 +14261,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>631882</v>
+        <v>631834</v>
       </c>
       <c r="R135" t="n">
-        <v>6661651</v>
+        <v>6661764</v>
       </c>
       <c r="S135" t="n">
         <v>5</v>
@@ -14296,7 +14296,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -14306,7 +14306,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14333,32 +14333,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>132622049</v>
+        <v>132622045</v>
       </c>
       <c r="B136" t="n">
-        <v>101325</v>
+        <v>79946</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>222498</v>
+        <v>6453</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14368,10 +14368,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>631834</v>
+        <v>631882</v>
       </c>
       <c r="R136" t="n">
-        <v>6661764</v>
+        <v>6661651</v>
       </c>
       <c r="S136" t="n">
         <v>5</v>
@@ -14403,7 +14403,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -14413,7 +14413,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14987,7 +14987,7 @@
         <v>132622048</v>
       </c>
       <c r="B142" t="n">
-        <v>101325</v>
+        <v>101326</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>

--- a/artfynd/A 41611-2025 artfynd.xlsx
+++ b/artfynd/A 41611-2025 artfynd.xlsx
@@ -11780,7 +11780,7 @@
         <v>132247080</v>
       </c>
       <c r="B111" t="n">
-        <v>97358</v>
+        <v>97359</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11877,7 +11877,7 @@
         <v>132247084</v>
       </c>
       <c r="B112" t="n">
-        <v>81312</v>
+        <v>81313</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11974,7 +11974,7 @@
         <v>132247081</v>
       </c>
       <c r="B113" t="n">
-        <v>97358</v>
+        <v>97359</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12071,7 +12071,7 @@
         <v>132247087</v>
       </c>
       <c r="B114" t="n">
-        <v>96601</v>
+        <v>96602</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12165,10 +12165,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>132247086</v>
+        <v>132247085</v>
       </c>
       <c r="B115" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12194,20 +12194,16 @@
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
-      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>632060</v>
+        <v>632051</v>
       </c>
       <c r="R115" t="n">
-        <v>6661605</v>
+        <v>6661556</v>
       </c>
       <c r="S115" t="n">
         <v>15</v>
@@ -12244,7 +12240,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>3 bladrosetter</t>
+          <t>20 tal bladrosetter</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12253,7 +12249,6 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
-      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
@@ -12272,10 +12267,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>132247085</v>
+        <v>132247086</v>
       </c>
       <c r="B116" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12301,16 +12296,20 @@
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>632051</v>
+        <v>632060</v>
       </c>
       <c r="R116" t="n">
-        <v>6661556</v>
+        <v>6661605</v>
       </c>
       <c r="S116" t="n">
         <v>15</v>
@@ -12347,7 +12346,7 @@
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>20 tal bladrosetter</t>
+          <t>3 bladrosetter</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12356,6 +12355,7 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
+      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -12377,7 +12377,7 @@
         <v>132247082</v>
       </c>
       <c r="B117" t="n">
-        <v>57141</v>
+        <v>57142</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12482,7 +12482,7 @@
         <v>132286073</v>
       </c>
       <c r="B118" t="n">
-        <v>57950</v>
+        <v>57951</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12587,7 +12587,7 @@
         <v>132286086</v>
       </c>
       <c r="B119" t="n">
-        <v>101326</v>
+        <v>101327</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12684,7 +12684,7 @@
         <v>132286072</v>
       </c>
       <c r="B120" t="n">
-        <v>57950</v>
+        <v>57951</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12789,7 +12789,7 @@
         <v>132286080</v>
       </c>
       <c r="B121" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12899,7 +12899,7 @@
         <v>132286078</v>
       </c>
       <c r="B122" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13009,7 +13009,7 @@
         <v>132286088</v>
       </c>
       <c r="B123" t="n">
-        <v>101326</v>
+        <v>101327</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13106,7 +13106,7 @@
         <v>132410204</v>
       </c>
       <c r="B124" t="n">
-        <v>58114</v>
+        <v>58115</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13225,7 +13225,7 @@
         <v>132617077</v>
       </c>
       <c r="B125" t="n">
-        <v>80392</v>
+        <v>80393</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13322,7 +13322,7 @@
         <v>132603522</v>
       </c>
       <c r="B126" t="n">
-        <v>80392</v>
+        <v>80393</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13429,7 +13429,7 @@
         <v>132617083</v>
       </c>
       <c r="B127" t="n">
-        <v>96554</v>
+        <v>96555</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13526,7 +13526,7 @@
         <v>132617073</v>
       </c>
       <c r="B128" t="n">
-        <v>92208</v>
+        <v>92209</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13623,7 +13623,7 @@
         <v>132617066</v>
       </c>
       <c r="B129" t="n">
-        <v>97358</v>
+        <v>97359</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13720,7 +13720,7 @@
         <v>132617068</v>
       </c>
       <c r="B130" t="n">
-        <v>91909</v>
+        <v>91910</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13817,7 +13817,7 @@
         <v>132617085</v>
       </c>
       <c r="B131" t="n">
-        <v>91923</v>
+        <v>91924</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13914,7 +13914,7 @@
         <v>132606960</v>
       </c>
       <c r="B132" t="n">
-        <v>97358</v>
+        <v>97359</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14015,7 +14015,7 @@
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Elvira Klang, Tore Dahlberg, Elias Blad, Filippa Paperin</t>
+          <t>Filippa Paperin, Elias Blad, Tore Dahlberg, Elvira Klang</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
@@ -14025,7 +14025,7 @@
         <v>132617069</v>
       </c>
       <c r="B133" t="n">
-        <v>91909</v>
+        <v>91910</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14226,32 +14226,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>132622049</v>
+        <v>132622045</v>
       </c>
       <c r="B135" t="n">
-        <v>101326</v>
+        <v>79947</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>222498</v>
+        <v>6453</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14261,10 +14261,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>631834</v>
+        <v>631882</v>
       </c>
       <c r="R135" t="n">
-        <v>6661764</v>
+        <v>6661651</v>
       </c>
       <c r="S135" t="n">
         <v>5</v>
@@ -14296,7 +14296,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -14306,7 +14306,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14333,32 +14333,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>132622045</v>
+        <v>132622049</v>
       </c>
       <c r="B136" t="n">
-        <v>79946</v>
+        <v>101327</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6453</v>
+        <v>222498</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14368,10 +14368,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>631882</v>
+        <v>631834</v>
       </c>
       <c r="R136" t="n">
-        <v>6661651</v>
+        <v>6661764</v>
       </c>
       <c r="S136" t="n">
         <v>5</v>
@@ -14403,7 +14403,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -14413,7 +14413,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14443,7 +14443,7 @@
         <v>132622043</v>
       </c>
       <c r="B137" t="n">
-        <v>97358</v>
+        <v>97359</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14764,7 +14764,7 @@
         <v>132622051</v>
       </c>
       <c r="B140" t="n">
-        <v>91909</v>
+        <v>91910</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14871,7 +14871,7 @@
         <v>132622040</v>
       </c>
       <c r="B141" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14987,7 +14987,7 @@
         <v>132622048</v>
       </c>
       <c r="B142" t="n">
-        <v>101326</v>
+        <v>101327</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15094,7 +15094,7 @@
         <v>132663326</v>
       </c>
       <c r="B143" t="n">
-        <v>57950</v>
+        <v>57951</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15213,7 +15213,7 @@
         <v>132651716</v>
       </c>
       <c r="B144" t="n">
-        <v>57950</v>
+        <v>57951</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15318,7 +15318,7 @@
         <v>132663350</v>
       </c>
       <c r="B145" t="n">
-        <v>83299</v>
+        <v>83300</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15429,7 +15429,7 @@
         <v>132651173</v>
       </c>
       <c r="B146" t="n">
-        <v>57141</v>
+        <v>57142</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15549,7 +15549,7 @@
         <v>132688846</v>
       </c>
       <c r="B147" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>

--- a/artfynd/A 41611-2025 artfynd.xlsx
+++ b/artfynd/A 41611-2025 artfynd.xlsx
@@ -11780,7 +11780,7 @@
         <v>132247080</v>
       </c>
       <c r="B111" t="n">
-        <v>97359</v>
+        <v>97361</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11974,7 +11974,7 @@
         <v>132247081</v>
       </c>
       <c r="B113" t="n">
-        <v>97359</v>
+        <v>97361</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12071,7 +12071,7 @@
         <v>132247087</v>
       </c>
       <c r="B114" t="n">
-        <v>96602</v>
+        <v>96604</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12168,7 +12168,7 @@
         <v>132247085</v>
       </c>
       <c r="B115" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12270,7 +12270,7 @@
         <v>132247086</v>
       </c>
       <c r="B116" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12587,7 +12587,7 @@
         <v>132286086</v>
       </c>
       <c r="B119" t="n">
-        <v>101327</v>
+        <v>101329</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12789,7 +12789,7 @@
         <v>132286080</v>
       </c>
       <c r="B121" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12899,7 +12899,7 @@
         <v>132286078</v>
       </c>
       <c r="B122" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13009,7 +13009,7 @@
         <v>132286088</v>
       </c>
       <c r="B123" t="n">
-        <v>101327</v>
+        <v>101329</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13429,7 +13429,7 @@
         <v>132617083</v>
       </c>
       <c r="B127" t="n">
-        <v>96555</v>
+        <v>96557</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13526,7 +13526,7 @@
         <v>132617073</v>
       </c>
       <c r="B128" t="n">
-        <v>92209</v>
+        <v>92211</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13623,7 +13623,7 @@
         <v>132617066</v>
       </c>
       <c r="B129" t="n">
-        <v>97359</v>
+        <v>97361</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13720,7 +13720,7 @@
         <v>132617068</v>
       </c>
       <c r="B130" t="n">
-        <v>91910</v>
+        <v>91912</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13817,7 +13817,7 @@
         <v>132617085</v>
       </c>
       <c r="B131" t="n">
-        <v>91924</v>
+        <v>91926</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13914,7 +13914,7 @@
         <v>132606960</v>
       </c>
       <c r="B132" t="n">
-        <v>97359</v>
+        <v>97361</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14015,7 +14015,7 @@
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elias Blad, Tore Dahlberg, Elvira Klang</t>
+          <t>Elvira Klang, Tore Dahlberg, Elias Blad, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
@@ -14025,7 +14025,7 @@
         <v>132617069</v>
       </c>
       <c r="B133" t="n">
-        <v>91910</v>
+        <v>91912</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14336,7 +14336,7 @@
         <v>132622049</v>
       </c>
       <c r="B136" t="n">
-        <v>101327</v>
+        <v>101329</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14443,7 +14443,7 @@
         <v>132622043</v>
       </c>
       <c r="B137" t="n">
-        <v>97359</v>
+        <v>97361</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14764,7 +14764,7 @@
         <v>132622051</v>
       </c>
       <c r="B140" t="n">
-        <v>91910</v>
+        <v>91912</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14871,7 +14871,7 @@
         <v>132622040</v>
       </c>
       <c r="B141" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14987,7 +14987,7 @@
         <v>132622048</v>
       </c>
       <c r="B142" t="n">
-        <v>101327</v>
+        <v>101329</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15318,7 +15318,7 @@
         <v>132663350</v>
       </c>
       <c r="B145" t="n">
-        <v>83300</v>
+        <v>83302</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15549,7 +15549,7 @@
         <v>132688846</v>
       </c>
       <c r="B147" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>

--- a/artfynd/A 41611-2025 artfynd.xlsx
+++ b/artfynd/A 41611-2025 artfynd.xlsx
@@ -11780,7 +11780,7 @@
         <v>132247080</v>
       </c>
       <c r="B111" t="n">
-        <v>97361</v>
+        <v>97362</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11877,7 +11877,7 @@
         <v>132247084</v>
       </c>
       <c r="B112" t="n">
-        <v>81313</v>
+        <v>81314</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11974,7 +11974,7 @@
         <v>132247081</v>
       </c>
       <c r="B113" t="n">
-        <v>97361</v>
+        <v>97362</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12068,45 +12068,49 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>132247087</v>
+        <v>132247086</v>
       </c>
       <c r="B114" t="n">
-        <v>96604</v>
+        <v>99122</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>2170</v>
+        <v>220787</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>632046</v>
+        <v>632060</v>
       </c>
       <c r="R114" t="n">
-        <v>6661591</v>
+        <v>6661605</v>
       </c>
       <c r="S114" t="n">
         <v>15</v>
@@ -12141,12 +12145,18 @@
           <t>2026-04-06</t>
         </is>
       </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>3 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD114" t="b">
         <v>0</v>
       </c>
       <c r="AE114" t="b">
         <v>0</v>
       </c>
+      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
@@ -12168,7 +12178,7 @@
         <v>132247085</v>
       </c>
       <c r="B115" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12267,49 +12277,45 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>132247086</v>
+        <v>132247087</v>
       </c>
       <c r="B116" t="n">
-        <v>99121</v>
+        <v>96605</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>220787</v>
+        <v>2170</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>632060</v>
+        <v>632046</v>
       </c>
       <c r="R116" t="n">
-        <v>6661605</v>
+        <v>6661591</v>
       </c>
       <c r="S116" t="n">
         <v>15</v>
@@ -12344,18 +12350,12 @@
           <t>2026-04-06</t>
         </is>
       </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>3 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD116" t="b">
         <v>0</v>
       </c>
       <c r="AE116" t="b">
         <v>0</v>
       </c>
-      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -12587,7 +12587,7 @@
         <v>132286086</v>
       </c>
       <c r="B119" t="n">
-        <v>101329</v>
+        <v>101330</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12789,7 +12789,7 @@
         <v>132286080</v>
       </c>
       <c r="B121" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12899,7 +12899,7 @@
         <v>132286078</v>
       </c>
       <c r="B122" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13009,7 +13009,7 @@
         <v>132286088</v>
       </c>
       <c r="B123" t="n">
-        <v>101329</v>
+        <v>101330</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13225,7 +13225,7 @@
         <v>132617077</v>
       </c>
       <c r="B125" t="n">
-        <v>80393</v>
+        <v>80394</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13322,7 +13322,7 @@
         <v>132603522</v>
       </c>
       <c r="B126" t="n">
-        <v>80393</v>
+        <v>80394</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13429,7 +13429,7 @@
         <v>132617083</v>
       </c>
       <c r="B127" t="n">
-        <v>96557</v>
+        <v>96558</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13526,7 +13526,7 @@
         <v>132617073</v>
       </c>
       <c r="B128" t="n">
-        <v>92211</v>
+        <v>92212</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13623,7 +13623,7 @@
         <v>132617066</v>
       </c>
       <c r="B129" t="n">
-        <v>97361</v>
+        <v>97362</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13720,7 +13720,7 @@
         <v>132617068</v>
       </c>
       <c r="B130" t="n">
-        <v>91912</v>
+        <v>91913</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13817,7 +13817,7 @@
         <v>132617085</v>
       </c>
       <c r="B131" t="n">
-        <v>91926</v>
+        <v>91927</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13914,7 +13914,7 @@
         <v>132606960</v>
       </c>
       <c r="B132" t="n">
-        <v>97361</v>
+        <v>97362</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14025,7 +14025,7 @@
         <v>132617069</v>
       </c>
       <c r="B133" t="n">
-        <v>91912</v>
+        <v>91913</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14226,32 +14226,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>132622045</v>
+        <v>132622049</v>
       </c>
       <c r="B135" t="n">
-        <v>79947</v>
+        <v>101330</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6453</v>
+        <v>222498</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14261,10 +14261,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>631882</v>
+        <v>631834</v>
       </c>
       <c r="R135" t="n">
-        <v>6661651</v>
+        <v>6661764</v>
       </c>
       <c r="S135" t="n">
         <v>5</v>
@@ -14296,7 +14296,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -14306,7 +14306,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14333,32 +14333,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>132622049</v>
+        <v>132622045</v>
       </c>
       <c r="B136" t="n">
-        <v>101329</v>
+        <v>79948</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>222498</v>
+        <v>6453</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14368,10 +14368,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>631834</v>
+        <v>631882</v>
       </c>
       <c r="R136" t="n">
-        <v>6661764</v>
+        <v>6661651</v>
       </c>
       <c r="S136" t="n">
         <v>5</v>
@@ -14403,7 +14403,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -14413,7 +14413,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14443,7 +14443,7 @@
         <v>132622043</v>
       </c>
       <c r="B137" t="n">
-        <v>97361</v>
+        <v>97362</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14764,7 +14764,7 @@
         <v>132622051</v>
       </c>
       <c r="B140" t="n">
-        <v>91912</v>
+        <v>91913</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14871,7 +14871,7 @@
         <v>132622040</v>
       </c>
       <c r="B141" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14987,7 +14987,7 @@
         <v>132622048</v>
       </c>
       <c r="B142" t="n">
-        <v>101329</v>
+        <v>101330</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15318,7 +15318,7 @@
         <v>132663350</v>
       </c>
       <c r="B145" t="n">
-        <v>83302</v>
+        <v>83303</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15549,7 +15549,7 @@
         <v>132688846</v>
       </c>
       <c r="B147" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>

--- a/artfynd/A 41611-2025 artfynd.xlsx
+++ b/artfynd/A 41611-2025 artfynd.xlsx
@@ -12068,49 +12068,45 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>132247086</v>
+        <v>132247087</v>
       </c>
       <c r="B114" t="n">
-        <v>99122</v>
+        <v>96605</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>220787</v>
+        <v>2170</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
-      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>632060</v>
+        <v>632046</v>
       </c>
       <c r="R114" t="n">
-        <v>6661605</v>
+        <v>6661591</v>
       </c>
       <c r="S114" t="n">
         <v>15</v>
@@ -12145,18 +12141,12 @@
           <t>2026-04-06</t>
         </is>
       </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>3 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD114" t="b">
         <v>0</v>
       </c>
       <c r="AE114" t="b">
         <v>0</v>
       </c>
-      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
@@ -12175,7 +12165,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>132247085</v>
+        <v>132247086</v>
       </c>
       <c r="B115" t="n">
         <v>99122</v>
@@ -12204,16 +12194,20 @@
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>632051</v>
+        <v>632060</v>
       </c>
       <c r="R115" t="n">
-        <v>6661556</v>
+        <v>6661605</v>
       </c>
       <c r="S115" t="n">
         <v>15</v>
@@ -12250,7 +12244,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>20 tal bladrosetter</t>
+          <t>3 bladrosetter</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12259,6 +12253,7 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
+      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
@@ -12277,32 +12272,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>132247087</v>
+        <v>132247085</v>
       </c>
       <c r="B116" t="n">
-        <v>96605</v>
+        <v>99122</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>2170</v>
+        <v>220787</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12312,10 +12307,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>632046</v>
+        <v>632051</v>
       </c>
       <c r="R116" t="n">
-        <v>6661591</v>
+        <v>6661556</v>
       </c>
       <c r="S116" t="n">
         <v>15</v>
@@ -12348,6 +12343,11 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>20 tal bladrosetter</t>
         </is>
       </c>
       <c r="AD116" t="b">

--- a/artfynd/A 41611-2025 artfynd.xlsx
+++ b/artfynd/A 41611-2025 artfynd.xlsx
@@ -14226,32 +14226,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>132622049</v>
+        <v>132622045</v>
       </c>
       <c r="B135" t="n">
-        <v>101330</v>
+        <v>79948</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>222498</v>
+        <v>6453</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14261,10 +14261,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>631834</v>
+        <v>631882</v>
       </c>
       <c r="R135" t="n">
-        <v>6661764</v>
+        <v>6661651</v>
       </c>
       <c r="S135" t="n">
         <v>5</v>
@@ -14296,7 +14296,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -14306,7 +14306,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14333,32 +14333,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>132622045</v>
+        <v>132622049</v>
       </c>
       <c r="B136" t="n">
-        <v>79948</v>
+        <v>101330</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6453</v>
+        <v>222498</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14368,10 +14368,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>631882</v>
+        <v>631834</v>
       </c>
       <c r="R136" t="n">
-        <v>6661651</v>
+        <v>6661764</v>
       </c>
       <c r="S136" t="n">
         <v>5</v>
@@ -14403,7 +14403,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -14413,7 +14413,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD136" t="b">

--- a/artfynd/A 41611-2025 artfynd.xlsx
+++ b/artfynd/A 41611-2025 artfynd.xlsx
@@ -14015,7 +14015,7 @@
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Elvira Klang, Tore Dahlberg, Elias Blad, Filippa Paperin</t>
+          <t>Filippa Paperin, Elias Blad, Tore Dahlberg, Elvira Klang</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>

--- a/artfynd/A 41611-2025 artfynd.xlsx
+++ b/artfynd/A 41611-2025 artfynd.xlsx
@@ -14015,7 +14015,7 @@
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elias Blad, Tore Dahlberg, Elvira Klang</t>
+          <t>Elvira Klang, Tore Dahlberg, Elias Blad, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
@@ -14226,32 +14226,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>132622045</v>
+        <v>132622049</v>
       </c>
       <c r="B135" t="n">
-        <v>79952</v>
+        <v>101338</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6453</v>
+        <v>222498</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14261,10 +14261,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>631882</v>
+        <v>631834</v>
       </c>
       <c r="R135" t="n">
-        <v>6661651</v>
+        <v>6661764</v>
       </c>
       <c r="S135" t="n">
         <v>5</v>
@@ -14296,7 +14296,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -14306,7 +14306,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14333,32 +14333,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>132622049</v>
+        <v>132622045</v>
       </c>
       <c r="B136" t="n">
-        <v>101338</v>
+        <v>79952</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>222498</v>
+        <v>6453</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14368,10 +14368,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>631834</v>
+        <v>631882</v>
       </c>
       <c r="R136" t="n">
-        <v>6661764</v>
+        <v>6661651</v>
       </c>
       <c r="S136" t="n">
         <v>5</v>
@@ -14403,7 +14403,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -14413,7 +14413,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD136" t="b">

--- a/artfynd/A 41611-2025 artfynd.xlsx
+++ b/artfynd/A 41611-2025 artfynd.xlsx
@@ -14226,32 +14226,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>132622049</v>
+        <v>132622045</v>
       </c>
       <c r="B135" t="n">
-        <v>101338</v>
+        <v>79952</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>222498</v>
+        <v>6453</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14261,10 +14261,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>631834</v>
+        <v>631882</v>
       </c>
       <c r="R135" t="n">
-        <v>6661764</v>
+        <v>6661651</v>
       </c>
       <c r="S135" t="n">
         <v>5</v>
@@ -14296,7 +14296,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -14306,7 +14306,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14333,32 +14333,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>132622045</v>
+        <v>132622049</v>
       </c>
       <c r="B136" t="n">
-        <v>79952</v>
+        <v>101338</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6453</v>
+        <v>222498</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14368,10 +14368,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>631882</v>
+        <v>631834</v>
       </c>
       <c r="R136" t="n">
-        <v>6661651</v>
+        <v>6661764</v>
       </c>
       <c r="S136" t="n">
         <v>5</v>
@@ -14403,7 +14403,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -14413,7 +14413,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD136" t="b">

--- a/artfynd/A 41611-2025 artfynd.xlsx
+++ b/artfynd/A 41611-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY151"/>
+  <dimension ref="A1:AY159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16060,6 +16060,895 @@
         </is>
       </c>
     </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>133629193</v>
+      </c>
+      <c r="B152" t="n">
+        <v>91881</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr"/>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>Risboskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q152" t="n">
+        <v>631954</v>
+      </c>
+      <c r="R152" t="n">
+        <v>6661837</v>
+      </c>
+      <c r="S152" t="n">
+        <v>10</v>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W152" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y152" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="Z152" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="AB152" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AD152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT152" t="inlineStr"/>
+      <c r="AW152" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX152" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>133629194</v>
+      </c>
+      <c r="B153" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr"/>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>Risboskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q153" t="n">
+        <v>631943</v>
+      </c>
+      <c r="R153" t="n">
+        <v>6661771</v>
+      </c>
+      <c r="S153" t="n">
+        <v>5</v>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W153" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="Z153" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="AB153" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AD153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT153" t="inlineStr"/>
+      <c r="AW153" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX153" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>133629199</v>
+      </c>
+      <c r="B154" t="n">
+        <v>101338</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr"/>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>Risboskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q154" t="n">
+        <v>631826</v>
+      </c>
+      <c r="R154" t="n">
+        <v>6661771</v>
+      </c>
+      <c r="S154" t="n">
+        <v>5</v>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V154" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W154" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y154" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="Z154" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="AB154" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
+      <c r="AD154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT154" t="inlineStr"/>
+      <c r="AW154" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX154" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>133629203</v>
+      </c>
+      <c r="B155" t="n">
+        <v>80398</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr"/>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>Risboskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q155" t="n">
+        <v>631784</v>
+      </c>
+      <c r="R155" t="n">
+        <v>6661708</v>
+      </c>
+      <c r="S155" t="n">
+        <v>8</v>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W155" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>17:44</t>
+        </is>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="AB155" t="inlineStr">
+        <is>
+          <t>17:44</t>
+        </is>
+      </c>
+      <c r="AC155" t="inlineStr">
+        <is>
+          <t>På asp</t>
+        </is>
+      </c>
+      <c r="AD155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF155" t="inlineStr"/>
+      <c r="AG155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT155" t="inlineStr"/>
+      <c r="AW155" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX155" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>133629201</v>
+      </c>
+      <c r="B156" t="n">
+        <v>57136</v>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr"/>
+      <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>parning/parningsceremonier</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr"/>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>Risboskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q156" t="n">
+        <v>631802</v>
+      </c>
+      <c r="R156" t="n">
+        <v>6661768</v>
+      </c>
+      <c r="S156" t="n">
+        <v>11</v>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V156" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W156" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y156" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="Z156" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="AB156" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AD156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT156" t="inlineStr"/>
+      <c r="AW156" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX156" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>133629206</v>
+      </c>
+      <c r="B157" t="n">
+        <v>57136</v>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr"/>
+      <c r="N157" t="inlineStr"/>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>Risboskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q157" t="n">
+        <v>631802</v>
+      </c>
+      <c r="R157" t="n">
+        <v>6661833</v>
+      </c>
+      <c r="S157" t="n">
+        <v>9</v>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W157" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="AD157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT157" t="inlineStr"/>
+      <c r="AW157" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX157" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>133629207</v>
+      </c>
+      <c r="B158" t="n">
+        <v>91881</v>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr"/>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>Risboskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q158" t="n">
+        <v>632000</v>
+      </c>
+      <c r="R158" t="n">
+        <v>6661786</v>
+      </c>
+      <c r="S158" t="n">
+        <v>16</v>
+      </c>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V158" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W158" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y158" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="Z158" t="inlineStr">
+        <is>
+          <t>18:44</t>
+        </is>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="AB158" t="inlineStr">
+        <is>
+          <t>18:44</t>
+        </is>
+      </c>
+      <c r="AD158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT158" t="inlineStr"/>
+      <c r="AW158" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX158" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>133629205</v>
+      </c>
+      <c r="B159" t="n">
+        <v>102253</v>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr"/>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>Risboskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q159" t="n">
+        <v>631840</v>
+      </c>
+      <c r="R159" t="n">
+        <v>6661705</v>
+      </c>
+      <c r="S159" t="n">
+        <v>5</v>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W159" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>17:59</t>
+        </is>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="AB159" t="inlineStr">
+        <is>
+          <t>17:59</t>
+        </is>
+      </c>
+      <c r="AD159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT159" t="inlineStr"/>
+      <c r="AW159" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX159" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY159" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
